--- a/research/traditional_assets/database/data/hong_kong/hong_kong_utility_general.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_utility_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0775</v>
+        <v>-0.09789999999999999</v>
       </c>
       <c r="E2">
-        <v>-0.0184</v>
+        <v>-0.0005899999999999999</v>
       </c>
       <c r="G2">
-        <v>0.04316312870529738</v>
+        <v>0.05990317827825721</v>
       </c>
       <c r="H2">
-        <v>-0.003882195448460508</v>
+        <v>0.01612292149021259</v>
       </c>
       <c r="I2">
-        <v>-0.05125262956588258</v>
+        <v>-0.01170279941065039</v>
       </c>
       <c r="J2">
-        <v>-0.04333312703820977</v>
+        <v>-0.01073406021718553</v>
       </c>
       <c r="K2">
-        <v>57.2</v>
+        <v>61</v>
       </c>
       <c r="L2">
-        <v>0.1093899407152419</v>
+        <v>0.1283940223110924</v>
       </c>
       <c r="M2">
-        <v>10.7</v>
+        <v>12.2</v>
       </c>
       <c r="N2">
-        <v>0.04574604531851218</v>
+        <v>0.05910852713178294</v>
       </c>
       <c r="O2">
-        <v>0.187062937062937</v>
+        <v>0.2</v>
       </c>
       <c r="P2">
-        <v>10.7</v>
+        <v>12.2</v>
       </c>
       <c r="Q2">
-        <v>0.04574604531851218</v>
+        <v>0.05910852713178294</v>
       </c>
       <c r="R2">
-        <v>0.187062937062937</v>
+        <v>0.2</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>441.4</v>
+        <v>585.5</v>
       </c>
       <c r="V2">
-        <v>1.887131252672082</v>
+        <v>2.83672480620155</v>
       </c>
       <c r="W2">
-        <v>0.0394809497515185</v>
+        <v>0.0378740841922265</v>
       </c>
       <c r="X2">
-        <v>0.06458346557094474</v>
+        <v>0.1069481691800566</v>
       </c>
       <c r="Y2">
-        <v>-0.02510251581942624</v>
+        <v>-0.06907408498783006</v>
       </c>
       <c r="Z2">
-        <v>0.4124142282514394</v>
+        <v>0.3239023725115899</v>
       </c>
       <c r="AA2">
-        <v>-0.01787119814518486</v>
+        <v>-0.003476787571028665</v>
       </c>
       <c r="AB2">
-        <v>0.04174130930166493</v>
+        <v>0.07096133731452076</v>
       </c>
       <c r="AC2">
-        <v>-0.05961250744684979</v>
+        <v>-0.07443812488554942</v>
       </c>
       <c r="AD2">
-        <v>297.6</v>
+        <v>293.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>297.6</v>
+        <v>293.1</v>
       </c>
       <c r="AG2">
-        <v>-143.8</v>
+        <v>-292.4</v>
       </c>
       <c r="AH2">
-        <v>0.5599247412982127</v>
+        <v>0.5867867867867869</v>
       </c>
       <c r="AI2">
-        <v>0.1174566839010143</v>
+        <v>0.1187649418533976</v>
       </c>
       <c r="AJ2">
-        <v>-1.596004439511652</v>
+        <v>3.400000000000001</v>
       </c>
       <c r="AK2">
-        <v>-0.06872819385365385</v>
+        <v>-0.1553336166595835</v>
       </c>
       <c r="AL2">
-        <v>7.38</v>
+        <v>6.3</v>
       </c>
       <c r="AM2">
-        <v>-22.72</v>
+        <v>-35.5</v>
       </c>
       <c r="AN2">
-        <v>66.72645739910314</v>
+        <v>15.67379679144385</v>
       </c>
       <c r="AO2">
-        <v>-3.631436314363144</v>
+        <v>-0.8825396825396825</v>
       </c>
       <c r="AP2">
-        <v>-32.24215246636771</v>
+        <v>-15.63636363636363</v>
       </c>
       <c r="AQ2">
-        <v>1.179577464788732</v>
+        <v>0.1566197183098592</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0775</v>
+        <v>-0.09789999999999999</v>
       </c>
       <c r="E3">
-        <v>-0.0184</v>
+        <v>-0.0005899999999999999</v>
       </c>
       <c r="G3">
-        <v>0.04316312870529738</v>
+        <v>0.05990317827825721</v>
       </c>
       <c r="H3">
-        <v>-0.003882195448460508</v>
+        <v>0.01612292149021259</v>
       </c>
       <c r="I3">
-        <v>-0.05125262956588258</v>
+        <v>-0.01170279941065039</v>
       </c>
       <c r="J3">
-        <v>-0.04333312703820977</v>
+        <v>-0.01073406021718553</v>
       </c>
       <c r="K3">
-        <v>57.2</v>
+        <v>61</v>
       </c>
       <c r="L3">
-        <v>0.1093899407152419</v>
+        <v>0.1283940223110924</v>
       </c>
       <c r="M3">
-        <v>10.7</v>
+        <v>12.2</v>
       </c>
       <c r="N3">
-        <v>0.04574604531851218</v>
+        <v>0.05910852713178294</v>
       </c>
       <c r="O3">
-        <v>0.187062937062937</v>
+        <v>0.2</v>
       </c>
       <c r="P3">
-        <v>10.7</v>
+        <v>12.2</v>
       </c>
       <c r="Q3">
-        <v>0.04574604531851218</v>
+        <v>0.05910852713178294</v>
       </c>
       <c r="R3">
-        <v>0.187062937062937</v>
+        <v>0.2</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>441.4</v>
+        <v>585.5</v>
       </c>
       <c r="V3">
-        <v>1.887131252672082</v>
+        <v>2.83672480620155</v>
       </c>
       <c r="W3">
-        <v>0.0394809497515185</v>
+        <v>0.0378740841922265</v>
       </c>
       <c r="X3">
-        <v>0.06458346557094474</v>
+        <v>0.1069481691800566</v>
       </c>
       <c r="Y3">
-        <v>-0.02510251581942624</v>
+        <v>-0.06907408498783006</v>
       </c>
       <c r="Z3">
-        <v>0.4124142282514394</v>
+        <v>0.3239023725115899</v>
       </c>
       <c r="AA3">
-        <v>-0.01787119814518486</v>
+        <v>-0.003476787571028665</v>
       </c>
       <c r="AB3">
-        <v>0.04174130930166493</v>
+        <v>0.07096133731452076</v>
       </c>
       <c r="AC3">
-        <v>-0.05961250744684979</v>
+        <v>-0.07443812488554942</v>
       </c>
       <c r="AD3">
-        <v>297.6</v>
+        <v>293.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>297.6</v>
+        <v>293.1</v>
       </c>
       <c r="AG3">
-        <v>-143.8</v>
+        <v>-292.4</v>
       </c>
       <c r="AH3">
-        <v>0.5599247412982127</v>
+        <v>0.5867867867867869</v>
       </c>
       <c r="AI3">
-        <v>0.1174566839010143</v>
+        <v>0.1187649418533976</v>
       </c>
       <c r="AJ3">
-        <v>-1.596004439511652</v>
+        <v>3.400000000000001</v>
       </c>
       <c r="AK3">
-        <v>-0.06872819385365385</v>
+        <v>-0.1553336166595835</v>
       </c>
       <c r="AL3">
-        <v>7.38</v>
+        <v>6.3</v>
       </c>
       <c r="AM3">
-        <v>-22.72</v>
+        <v>-35.5</v>
       </c>
       <c r="AN3">
-        <v>66.72645739910314</v>
+        <v>15.67379679144385</v>
       </c>
       <c r="AO3">
-        <v>-3.631436314363144</v>
+        <v>-0.8825396825396825</v>
       </c>
       <c r="AP3">
-        <v>-32.24215246636771</v>
+        <v>-15.63636363636363</v>
       </c>
       <c r="AQ3">
-        <v>1.179577464788732</v>
+        <v>0.1566197183098592</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/hong_kong/hong_kong_utility_general.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_utility_general.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="sehk_882" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,46 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.09789999999999999</v>
+        <v>-0.0262</v>
       </c>
       <c r="E2">
-        <v>-0.0005899999999999999</v>
+        <v>0.0142</v>
       </c>
       <c r="G2">
-        <v>0.05990317827825721</v>
+        <v>0.09126810004387889</v>
       </c>
       <c r="H2">
-        <v>0.01612292149021259</v>
+        <v>0.05046072838964458</v>
       </c>
       <c r="I2">
-        <v>-0.01170279941065039</v>
+        <v>0.006581834137779728</v>
       </c>
       <c r="J2">
-        <v>-0.01073406021718553</v>
+        <v>0.006140694540211872</v>
       </c>
       <c r="K2">
-        <v>61</v>
+        <v>58.3</v>
       </c>
       <c r="L2">
-        <v>0.1283940223110924</v>
+        <v>0.127906976744186</v>
       </c>
       <c r="M2">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="N2">
-        <v>0.05910852713178294</v>
+        <v>0.06092124814264487</v>
       </c>
       <c r="O2">
-        <v>0.2</v>
+        <v>0.2109777015437393</v>
       </c>
       <c r="P2">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="Q2">
-        <v>0.05910852713178294</v>
+        <v>0.06092124814264487</v>
       </c>
       <c r="R2">
-        <v>0.2</v>
+        <v>0.2109777015437393</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>585.5</v>
+        <v>314.8</v>
       </c>
       <c r="V2">
-        <v>2.83672480620155</v>
+        <v>1.559187716691431</v>
       </c>
       <c r="W2">
-        <v>0.0378740841922265</v>
+        <v>0.03673135080645161</v>
       </c>
       <c r="X2">
-        <v>0.1069481691800566</v>
+        <v>0.08652903180986597</v>
       </c>
       <c r="Y2">
-        <v>-0.06907408498783006</v>
+        <v>-0.04979768100341436</v>
       </c>
       <c r="Z2">
-        <v>0.3239023725115899</v>
+        <v>0.3520234785295026</v>
       </c>
       <c r="AA2">
-        <v>-0.003476787571028665</v>
+        <v>0.002161668652632508</v>
       </c>
       <c r="AB2">
-        <v>0.07096133731452076</v>
+        <v>0.06326081752061537</v>
       </c>
       <c r="AC2">
-        <v>-0.07443812488554942</v>
+        <v>-0.06109914886798286</v>
       </c>
       <c r="AD2">
-        <v>293.1</v>
+        <v>232.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>293.1</v>
+        <v>232.6</v>
       </c>
       <c r="AG2">
-        <v>-292.4</v>
+        <v>-82.20000000000002</v>
       </c>
       <c r="AH2">
-        <v>0.5867867867867869</v>
+        <v>0.5353279631760645</v>
       </c>
       <c r="AI2">
-        <v>0.1187649418533976</v>
+        <v>0.09894503998638762</v>
       </c>
       <c r="AJ2">
-        <v>3.400000000000001</v>
+        <v>-0.6867167919799501</v>
       </c>
       <c r="AK2">
-        <v>-0.1553336166595835</v>
+        <v>-0.04037328094302555</v>
       </c>
       <c r="AL2">
-        <v>6.3</v>
+        <v>12.9</v>
       </c>
       <c r="AM2">
-        <v>-35.5</v>
+        <v>-18</v>
       </c>
       <c r="AN2">
-        <v>15.67379679144385</v>
+        <v>8.911877394636015</v>
       </c>
       <c r="AO2">
-        <v>-0.8825396825396825</v>
+        <v>0.2325581395348837</v>
       </c>
       <c r="AP2">
-        <v>-15.63636363636363</v>
+        <v>-3.149425287356322</v>
       </c>
       <c r="AQ2">
-        <v>0.1566197183098592</v>
+        <v>-0.1666666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +724,8893 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.09789999999999999</v>
+        <v>-0.0262</v>
       </c>
       <c r="E3">
-        <v>-0.0005899999999999999</v>
+        <v>0.0142</v>
       </c>
       <c r="G3">
-        <v>0.05990317827825721</v>
+        <v>0.09126810004387889</v>
       </c>
       <c r="H3">
-        <v>0.01612292149021259</v>
+        <v>0.05046072838964458</v>
       </c>
       <c r="I3">
-        <v>-0.01170279941065039</v>
+        <v>0.006581834137779728</v>
       </c>
       <c r="J3">
-        <v>-0.01073406021718553</v>
+        <v>0.006140694540211872</v>
       </c>
       <c r="K3">
-        <v>61</v>
+        <v>58.3</v>
       </c>
       <c r="L3">
-        <v>0.1283940223110924</v>
+        <v>0.127906976744186</v>
       </c>
       <c r="M3">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="N3">
-        <v>0.05910852713178294</v>
+        <v>0.06092124814264487</v>
       </c>
       <c r="O3">
+        <v>0.2109777015437393</v>
+      </c>
+      <c r="P3">
+        <v>12.3</v>
+      </c>
+      <c r="Q3">
+        <v>0.06092124814264487</v>
+      </c>
+      <c r="R3">
+        <v>0.2109777015437393</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>314.8</v>
+      </c>
+      <c r="V3">
+        <v>1.559187716691431</v>
+      </c>
+      <c r="W3">
+        <v>0.03673135080645161</v>
+      </c>
+      <c r="X3">
+        <v>0.08652903180986597</v>
+      </c>
+      <c r="Y3">
+        <v>-0.04979768100341436</v>
+      </c>
+      <c r="Z3">
+        <v>0.3520234785295026</v>
+      </c>
+      <c r="AA3">
+        <v>0.002161668652632508</v>
+      </c>
+      <c r="AB3">
+        <v>0.06326081752061537</v>
+      </c>
+      <c r="AC3">
+        <v>-0.06109914886798286</v>
+      </c>
+      <c r="AD3">
+        <v>232.6</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>232.6</v>
+      </c>
+      <c r="AG3">
+        <v>-82.20000000000002</v>
+      </c>
+      <c r="AH3">
+        <v>0.5353279631760645</v>
+      </c>
+      <c r="AI3">
+        <v>0.09894503998638762</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.6867167919799501</v>
+      </c>
+      <c r="AK3">
+        <v>-0.04037328094302555</v>
+      </c>
+      <c r="AL3">
+        <v>12.9</v>
+      </c>
+      <c r="AM3">
+        <v>-18</v>
+      </c>
+      <c r="AN3">
+        <v>8.911877394636015</v>
+      </c>
+      <c r="AO3">
+        <v>0.2325581395348837</v>
+      </c>
+      <c r="AP3">
+        <v>-3.149425287356322</v>
+      </c>
+      <c r="AQ3">
+        <v>-0.1666666666666667</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Tianjin Development Holdings Limited (SEHK:882)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SEHK:882</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Utility (General)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.232558139534884</v>
+      </c>
+      <c r="F2">
+        <v>10.445030068047</v>
+      </c>
+      <c r="G2">
+        <v>8.91187739463602</v>
+      </c>
+      <c r="H2">
+        <v>2.33065134099617</v>
+      </c>
+      <c r="I2">
+        <v>0.535327963176064</v>
+      </c>
+      <c r="J2">
+        <v>0.14</v>
+      </c>
+      <c r="K2">
+        <v>201.9</v>
+      </c>
+      <c r="L2">
+        <v>377.579347085204</v>
+      </c>
+      <c r="M2">
+        <v>119.7</v>
+      </c>
+      <c r="N2">
+        <v>123.609347085204</v>
+      </c>
+      <c r="O2">
+        <v>232.6</v>
+      </c>
+      <c r="P2">
+        <v>60.83</v>
+      </c>
+      <c r="Q2">
+        <v>0.06326081752061539</v>
+      </c>
+      <c r="R2">
+        <v>0.0624872042953144</v>
+      </c>
+      <c r="S2">
+        <v>0.0430636874045376</v>
+      </c>
+      <c r="T2">
+        <v>0.038243</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.086529031809866</v>
+      </c>
+      <c r="X2">
+        <v>0.06643393522710971</v>
+      </c>
+      <c r="Y2">
+        <v>0.871500428182667</v>
+      </c>
+      <c r="Z2">
+        <v>0.504577307973385</v>
+      </c>
+      <c r="AA2">
+        <v>232.6</v>
+      </c>
+      <c r="AB2">
+        <v>0.0515732783287875</v>
+      </c>
+      <c r="AC2">
+        <v>0.2325581395348837</v>
+      </c>
+      <c r="AD2">
+        <v>232.6</v>
+      </c>
+      <c r="AE2">
+        <v>12.9</v>
+      </c>
+      <c r="AF2">
+        <v>23.1</v>
+      </c>
+      <c r="AG2">
+        <v>26.1</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>201.9</v>
+      </c>
+      <c r="AK2">
+        <v>0.05476650414205181</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.165</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>42.7</v>
+      </c>
+      <c r="AR2">
+        <v>12.9</v>
+      </c>
+      <c r="AS2">
+        <v>232.6</v>
+      </c>
+      <c r="AT2">
+        <v>314.8</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.06312714125838302</v>
+      </c>
+      <c r="C2">
+        <v>435.157744714813</v>
+      </c>
+      <c r="D2">
+        <v>120.357744714813</v>
+      </c>
+      <c r="E2">
+        <v>-232.6</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>314.8</v>
+      </c>
+      <c r="H2">
+        <v>201.9</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>52.2</v>
+      </c>
+      <c r="K2">
+        <v>23.1</v>
+      </c>
+      <c r="L2">
+        <v>29.1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>29.1</v>
+      </c>
+      <c r="O2">
+        <v>4.801500000000001</v>
+      </c>
+      <c r="P2">
+        <v>24.2985</v>
+      </c>
+      <c r="Q2">
+        <v>47.3985</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.06312714125838302</v>
+      </c>
+      <c r="T2">
+        <v>0.4441974458563937</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.165</v>
+      </c>
+      <c r="W2">
+        <v>0.0373245</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.06307224647530668</v>
+      </c>
+      <c r="C3">
+        <v>431.0849491147807</v>
+      </c>
+      <c r="D3">
+        <v>120.6299491147807</v>
+      </c>
+      <c r="E3">
+        <v>-228.255</v>
+      </c>
+      <c r="F3">
+        <v>4.345</v>
+      </c>
+      <c r="G3">
+        <v>314.8</v>
+      </c>
+      <c r="H3">
+        <v>201.9</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>52.2</v>
+      </c>
+      <c r="K3">
+        <v>23.1</v>
+      </c>
+      <c r="L3">
+        <v>29.1</v>
+      </c>
+      <c r="M3">
+        <v>0.1942215</v>
+      </c>
+      <c r="N3">
+        <v>28.9057785</v>
+      </c>
+      <c r="O3">
+        <v>4.769453452500001</v>
+      </c>
+      <c r="P3">
+        <v>24.1363250475</v>
+      </c>
+      <c r="Q3">
+        <v>47.2363250475</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.063332324722532</v>
+      </c>
+      <c r="T3">
+        <v>0.4479439596674047</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.165</v>
+      </c>
+      <c r="W3">
+        <v>0.0373245</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>149.8289324302407</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.06301735169223036</v>
+      </c>
+      <c r="C4">
+        <v>427.0133875556689</v>
+      </c>
+      <c r="D4">
+        <v>120.9033875556688</v>
+      </c>
+      <c r="E4">
+        <v>-223.91</v>
+      </c>
+      <c r="F4">
+        <v>8.69</v>
+      </c>
+      <c r="G4">
+        <v>314.8</v>
+      </c>
+      <c r="H4">
+        <v>201.9</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>52.2</v>
+      </c>
+      <c r="K4">
+        <v>23.1</v>
+      </c>
+      <c r="L4">
+        <v>29.1</v>
+      </c>
+      <c r="M4">
+        <v>0.388443</v>
+      </c>
+      <c r="N4">
+        <v>28.711557</v>
+      </c>
+      <c r="O4">
+        <v>4.737406905</v>
+      </c>
+      <c r="P4">
+        <v>23.974150095</v>
+      </c>
+      <c r="Q4">
+        <v>47.07415009500001</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.06354169560431669</v>
+      </c>
+      <c r="T4">
+        <v>0.4517669329439465</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.165</v>
+      </c>
+      <c r="W4">
+        <v>0.0373245</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>74.91446621512037</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.06296245690915403</v>
+      </c>
+      <c r="C5">
+        <v>422.9430684483452</v>
+      </c>
+      <c r="D5">
+        <v>121.1780684483452</v>
+      </c>
+      <c r="E5">
+        <v>-219.565</v>
+      </c>
+      <c r="F5">
+        <v>13.035</v>
+      </c>
+      <c r="G5">
+        <v>314.8</v>
+      </c>
+      <c r="H5">
+        <v>201.9</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>52.2</v>
+      </c>
+      <c r="K5">
+        <v>23.1</v>
+      </c>
+      <c r="L5">
+        <v>29.1</v>
+      </c>
+      <c r="M5">
+        <v>0.5826645</v>
+      </c>
+      <c r="N5">
+        <v>28.5173355</v>
+      </c>
+      <c r="O5">
+        <v>4.7053603575</v>
+      </c>
+      <c r="P5">
+        <v>23.8119751425</v>
+      </c>
+      <c r="Q5">
+        <v>46.9119751425</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.063755383411499</v>
+      </c>
+      <c r="T5">
+        <v>0.4556687304117573</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.165</v>
+      </c>
+      <c r="W5">
+        <v>0.0373245</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>49.94297747674691</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.06290756212607769</v>
+      </c>
+      <c r="C6">
+        <v>418.8740002802863</v>
+      </c>
+      <c r="D6">
+        <v>121.4540002802863</v>
+      </c>
+      <c r="E6">
+        <v>-215.22</v>
+      </c>
+      <c r="F6">
+        <v>17.38</v>
+      </c>
+      <c r="G6">
+        <v>314.8</v>
+      </c>
+      <c r="H6">
+        <v>201.9</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>52.2</v>
+      </c>
+      <c r="K6">
+        <v>23.1</v>
+      </c>
+      <c r="L6">
+        <v>29.1</v>
+      </c>
+      <c r="M6">
+        <v>0.776886</v>
+      </c>
+      <c r="N6">
+        <v>28.323114</v>
+      </c>
+      <c r="O6">
+        <v>4.673313810000001</v>
+      </c>
+      <c r="P6">
+        <v>23.64980019</v>
+      </c>
+      <c r="Q6">
+        <v>46.74980019</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.0639735230479976</v>
+      </c>
+      <c r="T6">
+        <v>0.4596518153268141</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.165</v>
+      </c>
+      <c r="W6">
+        <v>0.0373245</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>37.45723310756019</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.06285266734300136</v>
+      </c>
+      <c r="C7">
+        <v>414.8061916164513</v>
+      </c>
+      <c r="D7">
+        <v>121.7311916164513</v>
+      </c>
+      <c r="E7">
+        <v>-210.875</v>
+      </c>
+      <c r="F7">
+        <v>21.725</v>
+      </c>
+      <c r="G7">
+        <v>314.8</v>
+      </c>
+      <c r="H7">
+        <v>201.9</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>52.2</v>
+      </c>
+      <c r="K7">
+        <v>23.1</v>
+      </c>
+      <c r="L7">
+        <v>29.1</v>
+      </c>
+      <c r="M7">
+        <v>0.9711075000000001</v>
+      </c>
+      <c r="N7">
+        <v>28.1288925</v>
+      </c>
+      <c r="O7">
+        <v>4.6412672625</v>
+      </c>
+      <c r="P7">
+        <v>23.4876252375</v>
+      </c>
+      <c r="Q7">
+        <v>46.58762523750001</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.06419625509789617</v>
+      </c>
+      <c r="T7">
+        <v>0.4637187546611353</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.165</v>
+      </c>
+      <c r="W7">
+        <v>0.0373245</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>29.96578648604815</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.06279777255992502</v>
+      </c>
+      <c r="C8">
+        <v>410.7396511001689</v>
+      </c>
+      <c r="D8">
+        <v>122.0096511001689</v>
+      </c>
+      <c r="E8">
+        <v>-206.53</v>
+      </c>
+      <c r="F8">
+        <v>26.07</v>
+      </c>
+      <c r="G8">
+        <v>314.8</v>
+      </c>
+      <c r="H8">
+        <v>201.9</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>52.2</v>
+      </c>
+      <c r="K8">
+        <v>23.1</v>
+      </c>
+      <c r="L8">
+        <v>29.1</v>
+      </c>
+      <c r="M8">
+        <v>1.165329</v>
+      </c>
+      <c r="N8">
+        <v>27.934671</v>
+      </c>
+      <c r="O8">
+        <v>4.609220715</v>
+      </c>
+      <c r="P8">
+        <v>23.325450285</v>
+      </c>
+      <c r="Q8">
+        <v>46.425450285</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.06442372612757982</v>
+      </c>
+      <c r="T8">
+        <v>0.4678722246195909</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.165</v>
+      </c>
+      <c r="W8">
+        <v>0.0373245</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>24.97148873837346</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.0627428777768487</v>
+      </c>
+      <c r="C9">
+        <v>406.6743874540352</v>
+      </c>
+      <c r="D9">
+        <v>122.2893874540352</v>
+      </c>
+      <c r="E9">
+        <v>-202.185</v>
+      </c>
+      <c r="F9">
+        <v>30.415</v>
+      </c>
+      <c r="G9">
+        <v>314.8</v>
+      </c>
+      <c r="H9">
+        <v>201.9</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>52.2</v>
+      </c>
+      <c r="K9">
+        <v>23.1</v>
+      </c>
+      <c r="L9">
+        <v>29.1</v>
+      </c>
+      <c r="M9">
+        <v>1.3595505</v>
+      </c>
+      <c r="N9">
+        <v>27.7404495</v>
+      </c>
+      <c r="O9">
+        <v>4.5771741675</v>
+      </c>
+      <c r="P9">
+        <v>23.1632753325</v>
+      </c>
+      <c r="Q9">
+        <v>46.2632753325</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.06465608900736419</v>
+      </c>
+      <c r="T9">
+        <v>0.472115016512637</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.165</v>
+      </c>
+      <c r="W9">
+        <v>0.0373245</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>21.4041332043201</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.06268798299377237</v>
+      </c>
+      <c r="C10">
+        <v>402.6104094808248</v>
+      </c>
+      <c r="D10">
+        <v>122.5704094808248</v>
+      </c>
+      <c r="E10">
+        <v>-197.84</v>
+      </c>
+      <c r="F10">
+        <v>34.76</v>
+      </c>
+      <c r="G10">
+        <v>314.8</v>
+      </c>
+      <c r="H10">
+        <v>201.9</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>52.2</v>
+      </c>
+      <c r="K10">
+        <v>23.1</v>
+      </c>
+      <c r="L10">
+        <v>29.1</v>
+      </c>
+      <c r="M10">
+        <v>1.553772</v>
+      </c>
+      <c r="N10">
+        <v>27.546228</v>
+      </c>
+      <c r="O10">
+        <v>4.545127620000001</v>
+      </c>
+      <c r="P10">
+        <v>23.00110038</v>
+      </c>
+      <c r="Q10">
+        <v>46.10110038000001</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.0648935032541004</v>
+      </c>
+      <c r="T10">
+        <v>0.4764500430120536</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.165</v>
+      </c>
+      <c r="W10">
+        <v>0.0373245</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>18.72861655378009</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.06263308821069603</v>
+      </c>
+      <c r="C11">
+        <v>398.5477260644142</v>
+      </c>
+      <c r="D11">
+        <v>122.8527260644142</v>
+      </c>
+      <c r="E11">
+        <v>-193.495</v>
+      </c>
+      <c r="F11">
+        <v>39.105</v>
+      </c>
+      <c r="G11">
+        <v>314.8</v>
+      </c>
+      <c r="H11">
+        <v>201.9</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>52.2</v>
+      </c>
+      <c r="K11">
+        <v>23.1</v>
+      </c>
+      <c r="L11">
+        <v>29.1</v>
+      </c>
+      <c r="M11">
+        <v>1.7479935</v>
+      </c>
+      <c r="N11">
+        <v>27.3520065</v>
+      </c>
+      <c r="O11">
+        <v>4.5130810725</v>
+      </c>
+      <c r="P11">
+        <v>22.8389254275</v>
+      </c>
+      <c r="Q11">
+        <v>45.9389254275</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.06513613539636927</v>
+      </c>
+      <c r="T11">
+        <v>0.4808803448191497</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.165</v>
+      </c>
+      <c r="W11">
+        <v>0.0373245</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>16.64765915891564</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.06257819342761971</v>
+      </c>
+      <c r="C12">
+        <v>394.4863461707175</v>
+      </c>
+      <c r="D12">
+        <v>123.1363461707175</v>
+      </c>
+      <c r="E12">
+        <v>-189.15</v>
+      </c>
+      <c r="F12">
+        <v>43.45</v>
+      </c>
+      <c r="G12">
+        <v>314.8</v>
+      </c>
+      <c r="H12">
+        <v>201.9</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>52.2</v>
+      </c>
+      <c r="K12">
+        <v>23.1</v>
+      </c>
+      <c r="L12">
+        <v>29.1</v>
+      </c>
+      <c r="M12">
+        <v>1.942215</v>
+      </c>
+      <c r="N12">
+        <v>27.157785</v>
+      </c>
+      <c r="O12">
+        <v>4.481034525</v>
+      </c>
+      <c r="P12">
+        <v>22.676750475</v>
+      </c>
+      <c r="Q12">
+        <v>45.776750475</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.06538415936402189</v>
+      </c>
+      <c r="T12">
+        <v>0.4854090977775147</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.165</v>
+      </c>
+      <c r="W12">
+        <v>0.0373245</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>14.98289324302407</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.06252329864454337</v>
+      </c>
+      <c r="C13">
+        <v>390.4262788486362</v>
+      </c>
+      <c r="D13">
+        <v>123.4212788486361</v>
+      </c>
+      <c r="E13">
+        <v>-184.805</v>
+      </c>
+      <c r="F13">
+        <v>47.795</v>
+      </c>
+      <c r="G13">
+        <v>314.8</v>
+      </c>
+      <c r="H13">
+        <v>201.9</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>52.2</v>
+      </c>
+      <c r="K13">
+        <v>23.1</v>
+      </c>
+      <c r="L13">
+        <v>29.1</v>
+      </c>
+      <c r="M13">
+        <v>2.1364365</v>
+      </c>
+      <c r="N13">
+        <v>26.9635635</v>
+      </c>
+      <c r="O13">
+        <v>4.4489879775</v>
+      </c>
+      <c r="P13">
+        <v>22.5145755225</v>
+      </c>
+      <c r="Q13">
+        <v>45.6145755225</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.06563775690398131</v>
+      </c>
+      <c r="T13">
+        <v>0.4900396204652811</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.165</v>
+      </c>
+      <c r="W13">
+        <v>0.0373245</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>13.62081203911279</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.06257862386146702</v>
+      </c>
+      <c r="C14">
+        <v>385.794117191802</v>
+      </c>
+      <c r="D14">
+        <v>123.134117191802</v>
+      </c>
+      <c r="E14">
+        <v>-180.46</v>
+      </c>
+      <c r="F14">
+        <v>52.14</v>
+      </c>
+      <c r="G14">
+        <v>314.8</v>
+      </c>
+      <c r="H14">
+        <v>201.9</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>52.2</v>
+      </c>
+      <c r="K14">
+        <v>23.1</v>
+      </c>
+      <c r="L14">
+        <v>29.1</v>
+      </c>
+      <c r="M14">
+        <v>2.388012</v>
+      </c>
+      <c r="N14">
+        <v>26.711988</v>
+      </c>
+      <c r="O14">
+        <v>4.40747802</v>
+      </c>
+      <c r="P14">
+        <v>22.30450998</v>
+      </c>
+      <c r="Q14">
+        <v>45.40450998</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.06589711802439435</v>
+      </c>
+      <c r="T14">
+        <v>0.4947753823050421</v>
+      </c>
+      <c r="U14">
+        <v>0.0458</v>
+      </c>
+      <c r="V14">
+        <v>0.165</v>
+      </c>
+      <c r="W14">
+        <v>0.038243</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>12.18586841272154</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.06253291407839071</v>
+      </c>
+      <c r="C15">
+        <v>381.6862744902079</v>
+      </c>
+      <c r="D15">
+        <v>123.3712744902079</v>
+      </c>
+      <c r="E15">
+        <v>-176.115</v>
+      </c>
+      <c r="F15">
+        <v>56.485</v>
+      </c>
+      <c r="G15">
+        <v>314.8</v>
+      </c>
+      <c r="H15">
+        <v>201.9</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>52.2</v>
+      </c>
+      <c r="K15">
+        <v>23.1</v>
+      </c>
+      <c r="L15">
+        <v>29.1</v>
+      </c>
+      <c r="M15">
+        <v>2.587013</v>
+      </c>
+      <c r="N15">
+        <v>26.512987</v>
+      </c>
+      <c r="O15">
+        <v>4.374642855</v>
+      </c>
+      <c r="P15">
+        <v>22.138344145</v>
+      </c>
+      <c r="Q15">
+        <v>45.238344145</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.06616244146941461</v>
+      </c>
+      <c r="T15">
+        <v>0.4996200122330736</v>
+      </c>
+      <c r="U15">
+        <v>0.0458</v>
+      </c>
+      <c r="V15">
+        <v>0.165</v>
+      </c>
+      <c r="W15">
+        <v>0.038243</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>11.24849391943527</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.06248720429531437</v>
+      </c>
+      <c r="C16">
+        <v>377.5793470852045</v>
+      </c>
+      <c r="D16">
+        <v>123.6093470852044</v>
+      </c>
+      <c r="E16">
+        <v>-171.77</v>
+      </c>
+      <c r="F16">
+        <v>60.83000000000001</v>
+      </c>
+      <c r="G16">
+        <v>314.8</v>
+      </c>
+      <c r="H16">
+        <v>201.9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>52.2</v>
+      </c>
+      <c r="K16">
+        <v>23.1</v>
+      </c>
+      <c r="L16">
+        <v>29.1</v>
+      </c>
+      <c r="M16">
+        <v>2.786014</v>
+      </c>
+      <c r="N16">
+        <v>26.313986</v>
+      </c>
+      <c r="O16">
+        <v>4.34180769</v>
+      </c>
+      <c r="P16">
+        <v>21.97217831</v>
+      </c>
+      <c r="Q16">
+        <v>45.07217831</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.06643393522710973</v>
+      </c>
+      <c r="T16">
+        <v>0.5045773079733848</v>
+      </c>
+      <c r="U16">
+        <v>0.0458</v>
+      </c>
+      <c r="V16">
+        <v>0.165</v>
+      </c>
+      <c r="W16">
+        <v>0.038243</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>10.44503006804704</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.06271704451223804</v>
+      </c>
+      <c r="C17">
+        <v>372.0464745981453</v>
+      </c>
+      <c r="D17">
+        <v>122.4214745981453</v>
+      </c>
+      <c r="E17">
+        <v>-167.425</v>
+      </c>
+      <c r="F17">
+        <v>65.175</v>
+      </c>
+      <c r="G17">
+        <v>314.8</v>
+      </c>
+      <c r="H17">
+        <v>201.9</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>52.2</v>
+      </c>
+      <c r="K17">
+        <v>23.1</v>
+      </c>
+      <c r="L17">
+        <v>29.1</v>
+      </c>
+      <c r="M17">
+        <v>3.1284</v>
+      </c>
+      <c r="N17">
+        <v>25.9716</v>
+      </c>
+      <c r="O17">
+        <v>4.285314000000001</v>
+      </c>
+      <c r="P17">
+        <v>21.686286</v>
+      </c>
+      <c r="Q17">
+        <v>44.786286</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.06671181707322123</v>
+      </c>
+      <c r="T17">
+        <v>0.5096512459664094</v>
+      </c>
+      <c r="U17">
+        <v>0.048</v>
+      </c>
+      <c r="V17">
+        <v>0.165</v>
+      </c>
+      <c r="W17">
+        <v>0.04008</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>9.301879555044113</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.06268970472916172</v>
+      </c>
+      <c r="C18">
+        <v>367.841575808995</v>
+      </c>
+      <c r="D18">
+        <v>122.561575808995</v>
+      </c>
+      <c r="E18">
+        <v>-163.08</v>
+      </c>
+      <c r="F18">
+        <v>69.52</v>
+      </c>
+      <c r="G18">
+        <v>314.8</v>
+      </c>
+      <c r="H18">
+        <v>201.9</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>52.2</v>
+      </c>
+      <c r="K18">
+        <v>23.1</v>
+      </c>
+      <c r="L18">
+        <v>29.1</v>
+      </c>
+      <c r="M18">
+        <v>3.33696</v>
+      </c>
+      <c r="N18">
+        <v>25.76304</v>
+      </c>
+      <c r="O18">
+        <v>4.250901600000001</v>
+      </c>
+      <c r="P18">
+        <v>21.5121384</v>
+      </c>
+      <c r="Q18">
+        <v>44.6121384</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.06699631515376395</v>
+      </c>
+      <c r="T18">
+        <v>0.5148459920068869</v>
+      </c>
+      <c r="U18">
+        <v>0.048</v>
+      </c>
+      <c r="V18">
+        <v>0.165</v>
+      </c>
+      <c r="W18">
+        <v>0.04008</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>8.720512082853855</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.06266236494608537</v>
+      </c>
+      <c r="C19">
+        <v>363.636998055645</v>
+      </c>
+      <c r="D19">
+        <v>122.701998055645</v>
+      </c>
+      <c r="E19">
+        <v>-158.735</v>
+      </c>
+      <c r="F19">
+        <v>73.86500000000001</v>
+      </c>
+      <c r="G19">
+        <v>314.8</v>
+      </c>
+      <c r="H19">
+        <v>201.9</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>52.2</v>
+      </c>
+      <c r="K19">
+        <v>23.1</v>
+      </c>
+      <c r="L19">
+        <v>29.1</v>
+      </c>
+      <c r="M19">
+        <v>3.545520000000001</v>
+      </c>
+      <c r="N19">
+        <v>25.55448</v>
+      </c>
+      <c r="O19">
+        <v>4.216489200000001</v>
+      </c>
+      <c r="P19">
+        <v>21.3379908</v>
+      </c>
+      <c r="Q19">
+        <v>44.4379908</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.06728766860974142</v>
+      </c>
+      <c r="T19">
+        <v>0.5201659126507493</v>
+      </c>
+      <c r="U19">
+        <v>0.048</v>
+      </c>
+      <c r="V19">
+        <v>0.165</v>
+      </c>
+      <c r="W19">
+        <v>0.04008</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>8.207540783862452</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.06263502516300906</v>
+      </c>
+      <c r="C20">
+        <v>359.4327424428201</v>
+      </c>
+      <c r="D20">
+        <v>122.8427424428201</v>
+      </c>
+      <c r="E20">
+        <v>-154.39</v>
+      </c>
+      <c r="F20">
+        <v>78.20999999999999</v>
+      </c>
+      <c r="G20">
+        <v>314.8</v>
+      </c>
+      <c r="H20">
+        <v>201.9</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>52.2</v>
+      </c>
+      <c r="K20">
+        <v>23.1</v>
+      </c>
+      <c r="L20">
+        <v>29.1</v>
+      </c>
+      <c r="M20">
+        <v>3.75408</v>
+      </c>
+      <c r="N20">
+        <v>25.34592</v>
+      </c>
+      <c r="O20">
+        <v>4.182076800000001</v>
+      </c>
+      <c r="P20">
+        <v>21.1638432</v>
+      </c>
+      <c r="Q20">
+        <v>44.2638432</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.06758612824757201</v>
+      </c>
+      <c r="T20">
+        <v>0.5256155874566572</v>
+      </c>
+      <c r="U20">
+        <v>0.048</v>
+      </c>
+      <c r="V20">
+        <v>0.165</v>
+      </c>
+      <c r="W20">
+        <v>0.04008</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>7.751566295870095</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.06284566037993271</v>
+      </c>
+      <c r="C21">
+        <v>354.0116643774602</v>
+      </c>
+      <c r="D21">
+        <v>121.7666643774602</v>
+      </c>
+      <c r="E21">
+        <v>-150.045</v>
+      </c>
+      <c r="F21">
+        <v>82.55500000000001</v>
+      </c>
+      <c r="G21">
+        <v>314.8</v>
+      </c>
+      <c r="H21">
+        <v>201.9</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>52.2</v>
+      </c>
+      <c r="K21">
+        <v>23.1</v>
+      </c>
+      <c r="L21">
+        <v>29.1</v>
+      </c>
+      <c r="M21">
+        <v>4.0864725</v>
+      </c>
+      <c r="N21">
+        <v>25.0135275</v>
+      </c>
+      <c r="O21">
+        <v>4.127232037500001</v>
+      </c>
+      <c r="P21">
+        <v>20.8862954625</v>
+      </c>
+      <c r="Q21">
+        <v>43.9862954625</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.06789195725917618</v>
+      </c>
+      <c r="T21">
+        <v>0.5311998221343157</v>
+      </c>
+      <c r="U21">
+        <v>0.0495</v>
+      </c>
+      <c r="V21">
+        <v>0.165</v>
+      </c>
+      <c r="W21">
+        <v>0.0413325</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>7.121056118694058</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
         <v>0.2</v>
       </c>
-      <c r="P3">
-        <v>12.2</v>
-      </c>
-      <c r="Q3">
-        <v>0.05910852713178294</v>
-      </c>
-      <c r="R3">
-        <v>0.2</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>585.5</v>
-      </c>
-      <c r="V3">
-        <v>2.83672480620155</v>
-      </c>
-      <c r="W3">
-        <v>0.0378740841922265</v>
-      </c>
-      <c r="X3">
-        <v>0.1069481691800566</v>
-      </c>
-      <c r="Y3">
-        <v>-0.06907408498783006</v>
-      </c>
-      <c r="Z3">
-        <v>0.3239023725115899</v>
-      </c>
-      <c r="AA3">
-        <v>-0.003476787571028665</v>
-      </c>
-      <c r="AB3">
-        <v>0.07096133731452076</v>
-      </c>
-      <c r="AC3">
-        <v>-0.07443812488554942</v>
-      </c>
-      <c r="AD3">
-        <v>293.1</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>293.1</v>
-      </c>
-      <c r="AG3">
-        <v>-292.4</v>
-      </c>
-      <c r="AH3">
-        <v>0.5867867867867869</v>
-      </c>
-      <c r="AI3">
-        <v>0.1187649418533976</v>
-      </c>
-      <c r="AJ3">
-        <v>3.400000000000001</v>
-      </c>
-      <c r="AK3">
-        <v>-0.1553336166595835</v>
-      </c>
-      <c r="AL3">
-        <v>6.3</v>
-      </c>
-      <c r="AM3">
-        <v>-35.5</v>
-      </c>
-      <c r="AN3">
-        <v>15.67379679144385</v>
-      </c>
-      <c r="AO3">
-        <v>-0.8825396825396825</v>
-      </c>
-      <c r="AP3">
-        <v>-15.63636363636363</v>
-      </c>
-      <c r="AQ3">
-        <v>0.1566197183098592</v>
+      <c r="B22">
+        <v>0.06283084559685638</v>
+      </c>
+      <c r="C22">
+        <v>349.7417323442286</v>
+      </c>
+      <c r="D22">
+        <v>121.8417323442286</v>
+      </c>
+      <c r="E22">
+        <v>-145.7</v>
+      </c>
+      <c r="F22">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="G22">
+        <v>314.8</v>
+      </c>
+      <c r="H22">
+        <v>201.9</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>52.2</v>
+      </c>
+      <c r="K22">
+        <v>23.1</v>
+      </c>
+      <c r="L22">
+        <v>29.1</v>
+      </c>
+      <c r="M22">
+        <v>4.301550000000001</v>
+      </c>
+      <c r="N22">
+        <v>24.79845</v>
+      </c>
+      <c r="O22">
+        <v>4.091744250000001</v>
+      </c>
+      <c r="P22">
+        <v>20.70670575</v>
+      </c>
+      <c r="Q22">
+        <v>43.80670575000001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.06820543199607047</v>
+      </c>
+      <c r="T22">
+        <v>0.5369236626789159</v>
+      </c>
+      <c r="U22">
+        <v>0.0495</v>
+      </c>
+      <c r="V22">
+        <v>0.165</v>
+      </c>
+      <c r="W22">
+        <v>0.0413325</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>6.765003312759354</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.06281603081378005</v>
+      </c>
+      <c r="C23">
+        <v>345.4718929254387</v>
+      </c>
+      <c r="D23">
+        <v>121.9168929254387</v>
+      </c>
+      <c r="E23">
+        <v>-141.355</v>
+      </c>
+      <c r="F23">
+        <v>91.24499999999999</v>
+      </c>
+      <c r="G23">
+        <v>314.8</v>
+      </c>
+      <c r="H23">
+        <v>201.9</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>52.2</v>
+      </c>
+      <c r="K23">
+        <v>23.1</v>
+      </c>
+      <c r="L23">
+        <v>29.1</v>
+      </c>
+      <c r="M23">
+        <v>4.516627499999999</v>
+      </c>
+      <c r="N23">
+        <v>24.5833725</v>
+      </c>
+      <c r="O23">
+        <v>4.0562564625</v>
+      </c>
+      <c r="P23">
+        <v>20.5271160375</v>
+      </c>
+      <c r="Q23">
+        <v>43.6271160375</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.06852684280225323</v>
+      </c>
+      <c r="T23">
+        <v>0.5427924105790755</v>
+      </c>
+      <c r="U23">
+        <v>0.0495</v>
+      </c>
+      <c r="V23">
+        <v>0.165</v>
+      </c>
+      <c r="W23">
+        <v>0.0413325</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>6.442860297866053</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.06305839603070372</v>
+      </c>
+      <c r="C24">
+        <v>339.9088233480794</v>
+      </c>
+      <c r="D24">
+        <v>120.6988233480794</v>
+      </c>
+      <c r="E24">
+        <v>-137.01</v>
+      </c>
+      <c r="F24">
+        <v>95.59</v>
+      </c>
+      <c r="G24">
+        <v>314.8</v>
+      </c>
+      <c r="H24">
+        <v>201.9</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>52.2</v>
+      </c>
+      <c r="K24">
+        <v>23.1</v>
+      </c>
+      <c r="L24">
+        <v>29.1</v>
+      </c>
+      <c r="M24">
+        <v>4.865531</v>
+      </c>
+      <c r="N24">
+        <v>24.234469</v>
+      </c>
+      <c r="O24">
+        <v>3.998687385</v>
+      </c>
+      <c r="P24">
+        <v>20.235781615</v>
+      </c>
+      <c r="Q24">
+        <v>43.335781615</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.06885649491115861</v>
+      </c>
+      <c r="T24">
+        <v>0.5488116391946238</v>
+      </c>
+      <c r="U24">
+        <v>0.0509</v>
+      </c>
+      <c r="V24">
+        <v>0.165</v>
+      </c>
+      <c r="W24">
+        <v>0.0425015</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>5.980847722478801</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.06305527124762739</v>
+      </c>
+      <c r="C25">
+        <v>335.5793728604588</v>
+      </c>
+      <c r="D25">
+        <v>120.7143728604588</v>
+      </c>
+      <c r="E25">
+        <v>-132.665</v>
+      </c>
+      <c r="F25">
+        <v>99.935</v>
+      </c>
+      <c r="G25">
+        <v>314.8</v>
+      </c>
+      <c r="H25">
+        <v>201.9</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>52.2</v>
+      </c>
+      <c r="K25">
+        <v>23.1</v>
+      </c>
+      <c r="L25">
+        <v>29.1</v>
+      </c>
+      <c r="M25">
+        <v>5.086691500000001</v>
+      </c>
+      <c r="N25">
+        <v>24.0133085</v>
+      </c>
+      <c r="O25">
+        <v>3.9621959025</v>
+      </c>
+      <c r="P25">
+        <v>20.0511125975</v>
+      </c>
+      <c r="Q25">
+        <v>43.1511125975</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.06919470941250309</v>
+      </c>
+      <c r="T25">
+        <v>0.5549872114105761</v>
+      </c>
+      <c r="U25">
+        <v>0.0509</v>
+      </c>
+      <c r="V25">
+        <v>0.165</v>
+      </c>
+      <c r="W25">
+        <v>0.0425015</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>5.720810864979722</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.06305214646455104</v>
+      </c>
+      <c r="C26">
+        <v>331.2499263798118</v>
+      </c>
+      <c r="D26">
+        <v>120.7299263798118</v>
+      </c>
+      <c r="E26">
+        <v>-128.32</v>
+      </c>
+      <c r="F26">
+        <v>104.28</v>
+      </c>
+      <c r="G26">
+        <v>314.8</v>
+      </c>
+      <c r="H26">
+        <v>201.9</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>52.2</v>
+      </c>
+      <c r="K26">
+        <v>23.1</v>
+      </c>
+      <c r="L26">
+        <v>29.1</v>
+      </c>
+      <c r="M26">
+        <v>5.307852</v>
+      </c>
+      <c r="N26">
+        <v>23.792148</v>
+      </c>
+      <c r="O26">
+        <v>3.92570442</v>
+      </c>
+      <c r="P26">
+        <v>19.86644358</v>
+      </c>
+      <c r="Q26">
+        <v>42.96644358</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.06954182429546191</v>
+      </c>
+      <c r="T26">
+        <v>0.5613252986848427</v>
+      </c>
+      <c r="U26">
+        <v>0.0509</v>
+      </c>
+      <c r="V26">
+        <v>0.165</v>
+      </c>
+      <c r="W26">
+        <v>0.0425015</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>5.482443745605567</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.06304902168147472</v>
+      </c>
+      <c r="C27">
+        <v>326.920483907687</v>
+      </c>
+      <c r="D27">
+        <v>120.745483907687</v>
+      </c>
+      <c r="E27">
+        <v>-123.975</v>
+      </c>
+      <c r="F27">
+        <v>108.625</v>
+      </c>
+      <c r="G27">
+        <v>314.8</v>
+      </c>
+      <c r="H27">
+        <v>201.9</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>52.2</v>
+      </c>
+      <c r="K27">
+        <v>23.1</v>
+      </c>
+      <c r="L27">
+        <v>29.1</v>
+      </c>
+      <c r="M27">
+        <v>5.5290125</v>
+      </c>
+      <c r="N27">
+        <v>23.5709875</v>
+      </c>
+      <c r="O27">
+        <v>3.8892129375</v>
+      </c>
+      <c r="P27">
+        <v>19.6817745625</v>
+      </c>
+      <c r="Q27">
+        <v>42.7817745625</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.06989819557529962</v>
+      </c>
+      <c r="T27">
+        <v>0.5678324016197566</v>
+      </c>
+      <c r="U27">
+        <v>0.0509</v>
+      </c>
+      <c r="V27">
+        <v>0.165</v>
+      </c>
+      <c r="W27">
+        <v>0.0425015</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>5.263145995781344</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.06304589689839839</v>
+      </c>
+      <c r="C28">
+        <v>322.5910454456347</v>
+      </c>
+      <c r="D28">
+        <v>120.7610454456346</v>
+      </c>
+      <c r="E28">
+        <v>-119.63</v>
+      </c>
+      <c r="F28">
+        <v>112.97</v>
+      </c>
+      <c r="G28">
+        <v>314.8</v>
+      </c>
+      <c r="H28">
+        <v>201.9</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>52.2</v>
+      </c>
+      <c r="K28">
+        <v>23.1</v>
+      </c>
+      <c r="L28">
+        <v>29.1</v>
+      </c>
+      <c r="M28">
+        <v>5.750173</v>
+      </c>
+      <c r="N28">
+        <v>23.349827</v>
+      </c>
+      <c r="O28">
+        <v>3.852721455</v>
+      </c>
+      <c r="P28">
+        <v>19.497105545</v>
+      </c>
+      <c r="Q28">
+        <v>42.59710554500001</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.07026419851134917</v>
+      </c>
+      <c r="T28">
+        <v>0.57451537220156</v>
+      </c>
+      <c r="U28">
+        <v>0.0509</v>
+      </c>
+      <c r="V28">
+        <v>0.165</v>
+      </c>
+      <c r="W28">
+        <v>0.0425015</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>5.060717303635908</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.06304277211532205</v>
+      </c>
+      <c r="C29">
+        <v>318.2616109952052</v>
+      </c>
+      <c r="D29">
+        <v>120.7766109952052</v>
+      </c>
+      <c r="E29">
+        <v>-115.285</v>
+      </c>
+      <c r="F29">
+        <v>117.315</v>
+      </c>
+      <c r="G29">
+        <v>314.8</v>
+      </c>
+      <c r="H29">
+        <v>201.9</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>52.2</v>
+      </c>
+      <c r="K29">
+        <v>23.1</v>
+      </c>
+      <c r="L29">
+        <v>29.1</v>
+      </c>
+      <c r="M29">
+        <v>5.971333500000001</v>
+      </c>
+      <c r="N29">
+        <v>23.1286665</v>
+      </c>
+      <c r="O29">
+        <v>3.8162299725</v>
+      </c>
+      <c r="P29">
+        <v>19.3124365275</v>
+      </c>
+      <c r="Q29">
+        <v>42.41243652750001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.07064022892509871</v>
+      </c>
+      <c r="T29">
+        <v>0.5813814378677964</v>
+      </c>
+      <c r="U29">
+        <v>0.0509</v>
+      </c>
+      <c r="V29">
+        <v>0.165</v>
+      </c>
+      <c r="W29">
+        <v>0.0425015</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>4.873283329427171</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.06303964733224572</v>
+      </c>
+      <c r="C30">
+        <v>313.9321805579501</v>
+      </c>
+      <c r="D30">
+        <v>120.7921805579501</v>
+      </c>
+      <c r="E30">
+        <v>-110.94</v>
+      </c>
+      <c r="F30">
+        <v>121.66</v>
+      </c>
+      <c r="G30">
+        <v>314.8</v>
+      </c>
+      <c r="H30">
+        <v>201.9</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>52.2</v>
+      </c>
+      <c r="K30">
+        <v>23.1</v>
+      </c>
+      <c r="L30">
+        <v>29.1</v>
+      </c>
+      <c r="M30">
+        <v>6.192494000000001</v>
+      </c>
+      <c r="N30">
+        <v>22.907506</v>
+      </c>
+      <c r="O30">
+        <v>3.779738490000001</v>
+      </c>
+      <c r="P30">
+        <v>19.12776751</v>
+      </c>
+      <c r="Q30">
+        <v>42.22776751000001</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.07102670462811907</v>
+      </c>
+      <c r="T30">
+        <v>0.5884382275803172</v>
+      </c>
+      <c r="U30">
+        <v>0.0509</v>
+      </c>
+      <c r="V30">
+        <v>0.165</v>
+      </c>
+      <c r="W30">
+        <v>0.0425015</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>4.699237496233343</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.06303652254916939</v>
+      </c>
+      <c r="C31">
+        <v>309.6027541354217</v>
+      </c>
+      <c r="D31">
+        <v>120.8077541354217</v>
+      </c>
+      <c r="E31">
+        <v>-106.595</v>
+      </c>
+      <c r="F31">
+        <v>126.005</v>
+      </c>
+      <c r="G31">
+        <v>314.8</v>
+      </c>
+      <c r="H31">
+        <v>201.9</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>52.2</v>
+      </c>
+      <c r="K31">
+        <v>23.1</v>
+      </c>
+      <c r="L31">
+        <v>29.1</v>
+      </c>
+      <c r="M31">
+        <v>6.4136545</v>
+      </c>
+      <c r="N31">
+        <v>22.6863455</v>
+      </c>
+      <c r="O31">
+        <v>3.7432470075</v>
+      </c>
+      <c r="P31">
+        <v>18.9430984925</v>
+      </c>
+      <c r="Q31">
+        <v>42.04309849250001</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.07142406697066112</v>
+      </c>
+      <c r="T31">
+        <v>0.5956938001016412</v>
+      </c>
+      <c r="U31">
+        <v>0.0509</v>
+      </c>
+      <c r="V31">
+        <v>0.165</v>
+      </c>
+      <c r="W31">
+        <v>0.0425015</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>4.537194823949435</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.06368469776609306</v>
+      </c>
+      <c r="C32">
+        <v>302.1110576001122</v>
+      </c>
+      <c r="D32">
+        <v>117.6610576001122</v>
+      </c>
+      <c r="E32">
+        <v>-102.25</v>
+      </c>
+      <c r="F32">
+        <v>130.35</v>
+      </c>
+      <c r="G32">
+        <v>314.8</v>
+      </c>
+      <c r="H32">
+        <v>201.9</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>52.2</v>
+      </c>
+      <c r="K32">
+        <v>23.1</v>
+      </c>
+      <c r="L32">
+        <v>29.1</v>
+      </c>
+      <c r="M32">
+        <v>6.973725</v>
+      </c>
+      <c r="N32">
+        <v>22.126275</v>
+      </c>
+      <c r="O32">
+        <v>3.650835375</v>
+      </c>
+      <c r="P32">
+        <v>18.475439625</v>
+      </c>
+      <c r="Q32">
+        <v>41.575439625</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.07183278252299009</v>
+      </c>
+      <c r="T32">
+        <v>0.6031566746950032</v>
+      </c>
+      <c r="U32">
+        <v>0.0535</v>
+      </c>
+      <c r="V32">
+        <v>0.165</v>
+      </c>
+      <c r="W32">
+        <v>0.0446725</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>4.172805781702031</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.06370328298301672</v>
+      </c>
+      <c r="C33">
+        <v>297.6782476402585</v>
+      </c>
+      <c r="D33">
+        <v>117.5732476402584</v>
+      </c>
+      <c r="E33">
+        <v>-97.905</v>
+      </c>
+      <c r="F33">
+        <v>134.695</v>
+      </c>
+      <c r="G33">
+        <v>314.8</v>
+      </c>
+      <c r="H33">
+        <v>201.9</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>52.2</v>
+      </c>
+      <c r="K33">
+        <v>23.1</v>
+      </c>
+      <c r="L33">
+        <v>29.1</v>
+      </c>
+      <c r="M33">
+        <v>7.2061825</v>
+      </c>
+      <c r="N33">
+        <v>21.8938175</v>
+      </c>
+      <c r="O33">
+        <v>3.6124798875</v>
+      </c>
+      <c r="P33">
+        <v>18.2813376125</v>
+      </c>
+      <c r="Q33">
+        <v>41.3813376125</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.07225334490292279</v>
+      </c>
+      <c r="T33">
+        <v>0.6108358644939699</v>
+      </c>
+      <c r="U33">
+        <v>0.0535</v>
+      </c>
+      <c r="V33">
+        <v>0.165</v>
+      </c>
+      <c r="W33">
+        <v>0.0446725</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>4.038199143582611</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.06444330819994039</v>
+      </c>
+      <c r="C34">
+        <v>289.9402701269436</v>
+      </c>
+      <c r="D34">
+        <v>114.1802701269435</v>
+      </c>
+      <c r="E34">
+        <v>-93.56</v>
+      </c>
+      <c r="F34">
+        <v>139.04</v>
+      </c>
+      <c r="G34">
+        <v>314.8</v>
+      </c>
+      <c r="H34">
+        <v>201.9</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>52.2</v>
+      </c>
+      <c r="K34">
+        <v>23.1</v>
+      </c>
+      <c r="L34">
+        <v>29.1</v>
+      </c>
+      <c r="M34">
+        <v>7.814048</v>
+      </c>
+      <c r="N34">
+        <v>21.285952</v>
+      </c>
+      <c r="O34">
+        <v>3.512182080000001</v>
+      </c>
+      <c r="P34">
+        <v>17.77376992</v>
+      </c>
+      <c r="Q34">
+        <v>40.87376992</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.07268627676461822</v>
+      </c>
+      <c r="T34">
+        <v>0.6187409128164355</v>
+      </c>
+      <c r="U34">
+        <v>0.0562</v>
+      </c>
+      <c r="V34">
+        <v>0.165</v>
+      </c>
+      <c r="W34">
+        <v>0.046927</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>3.724062099439369</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.06448443841686406</v>
+      </c>
+      <c r="C35">
+        <v>285.4124255888421</v>
+      </c>
+      <c r="D35">
+        <v>113.9974255888421</v>
+      </c>
+      <c r="E35">
+        <v>-89.21499999999997</v>
+      </c>
+      <c r="F35">
+        <v>143.385</v>
+      </c>
+      <c r="G35">
+        <v>314.8</v>
+      </c>
+      <c r="H35">
+        <v>201.9</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>52.2</v>
+      </c>
+      <c r="K35">
+        <v>23.1</v>
+      </c>
+      <c r="L35">
+        <v>29.1</v>
+      </c>
+      <c r="M35">
+        <v>8.058237000000002</v>
+      </c>
+      <c r="N35">
+        <v>21.041763</v>
+      </c>
+      <c r="O35">
+        <v>3.471890895</v>
+      </c>
+      <c r="P35">
+        <v>17.569872105</v>
+      </c>
+      <c r="Q35">
+        <v>40.669872105</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.07313213196546875</v>
+      </c>
+      <c r="T35">
+        <v>0.6268819327306165</v>
+      </c>
+      <c r="U35">
+        <v>0.0562</v>
+      </c>
+      <c r="V35">
+        <v>0.165</v>
+      </c>
+      <c r="W35">
+        <v>0.046927</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>3.61121173278969</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.06452556863378772</v>
+      </c>
+      <c r="C36">
+        <v>280.8851657169632</v>
+      </c>
+      <c r="D36">
+        <v>113.8151657169632</v>
+      </c>
+      <c r="E36">
+        <v>-84.86999999999998</v>
+      </c>
+      <c r="F36">
+        <v>147.73</v>
+      </c>
+      <c r="G36">
+        <v>314.8</v>
+      </c>
+      <c r="H36">
+        <v>201.9</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>52.2</v>
+      </c>
+      <c r="K36">
+        <v>23.1</v>
+      </c>
+      <c r="L36">
+        <v>29.1</v>
+      </c>
+      <c r="M36">
+        <v>8.302426000000001</v>
+      </c>
+      <c r="N36">
+        <v>20.797574</v>
+      </c>
+      <c r="O36">
+        <v>3.43159971</v>
+      </c>
+      <c r="P36">
+        <v>17.36597429</v>
+      </c>
+      <c r="Q36">
+        <v>40.46597429000001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.0735914979299814</v>
+      </c>
+      <c r="T36">
+        <v>0.6352696502179546</v>
+      </c>
+      <c r="U36">
+        <v>0.0562</v>
+      </c>
+      <c r="V36">
+        <v>0.165</v>
+      </c>
+      <c r="W36">
+        <v>0.046927</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>3.504999623001759</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.06594027385071138</v>
+      </c>
+      <c r="C37">
+        <v>270.6074728638806</v>
+      </c>
+      <c r="D37">
+        <v>107.8824728638806</v>
+      </c>
+      <c r="E37">
+        <v>-80.52499999999998</v>
+      </c>
+      <c r="F37">
+        <v>152.075</v>
+      </c>
+      <c r="G37">
+        <v>314.8</v>
+      </c>
+      <c r="H37">
+        <v>201.9</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>52.2</v>
+      </c>
+      <c r="K37">
+        <v>23.1</v>
+      </c>
+      <c r="L37">
+        <v>29.1</v>
+      </c>
+      <c r="M37">
+        <v>9.261367500000002</v>
+      </c>
+      <c r="N37">
+        <v>19.8386325</v>
+      </c>
+      <c r="O37">
+        <v>3.2733743625</v>
+      </c>
+      <c r="P37">
+        <v>16.5652581375</v>
+      </c>
+      <c r="Q37">
+        <v>39.6652581375</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.07406499823186369</v>
+      </c>
+      <c r="T37">
+        <v>0.6439154513202877</v>
+      </c>
+      <c r="U37">
+        <v>0.0609</v>
+      </c>
+      <c r="V37">
+        <v>0.165</v>
+      </c>
+      <c r="W37">
+        <v>0.0508515</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>3.142084578762261</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.06602064906763506</v>
+      </c>
+      <c r="C38">
+        <v>265.9439250901978</v>
+      </c>
+      <c r="D38">
+        <v>107.5639250901977</v>
+      </c>
+      <c r="E38">
+        <v>-76.18000000000001</v>
+      </c>
+      <c r="F38">
+        <v>156.42</v>
+      </c>
+      <c r="G38">
+        <v>314.8</v>
+      </c>
+      <c r="H38">
+        <v>201.9</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>52.2</v>
+      </c>
+      <c r="K38">
+        <v>23.1</v>
+      </c>
+      <c r="L38">
+        <v>29.1</v>
+      </c>
+      <c r="M38">
+        <v>9.525978</v>
+      </c>
+      <c r="N38">
+        <v>19.574022</v>
+      </c>
+      <c r="O38">
+        <v>3.22971363</v>
+      </c>
+      <c r="P38">
+        <v>16.34430837</v>
+      </c>
+      <c r="Q38">
+        <v>39.44430837</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.07455329541817979</v>
+      </c>
+      <c r="T38">
+        <v>0.6528314337070686</v>
+      </c>
+      <c r="U38">
+        <v>0.0609</v>
+      </c>
+      <c r="V38">
+        <v>0.165</v>
+      </c>
+      <c r="W38">
+        <v>0.0508515</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>3.054804451574421</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.06897425928455873</v>
+      </c>
+      <c r="C39">
+        <v>251.0700201343966</v>
+      </c>
+      <c r="D39">
+        <v>97.03502013439656</v>
+      </c>
+      <c r="E39">
+        <v>-71.83500000000001</v>
+      </c>
+      <c r="F39">
+        <v>160.765</v>
+      </c>
+      <c r="G39">
+        <v>314.8</v>
+      </c>
+      <c r="H39">
+        <v>201.9</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>52.2</v>
+      </c>
+      <c r="K39">
+        <v>23.1</v>
+      </c>
+      <c r="L39">
+        <v>29.1</v>
+      </c>
+      <c r="M39">
+        <v>11.285703</v>
+      </c>
+      <c r="N39">
+        <v>17.814297</v>
+      </c>
+      <c r="O39">
+        <v>2.939359005000001</v>
+      </c>
+      <c r="P39">
+        <v>14.874937995</v>
+      </c>
+      <c r="Q39">
+        <v>37.974937995</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.07505709410247419</v>
+      </c>
+      <c r="T39">
+        <v>0.6620304631537474</v>
+      </c>
+      <c r="U39">
+        <v>0.0702</v>
+      </c>
+      <c r="V39">
+        <v>0.165</v>
+      </c>
+      <c r="W39">
+        <v>0.058617</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>2.578483591141819</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.0691322895014824</v>
+      </c>
+      <c r="C40">
+        <v>246.2194709149655</v>
+      </c>
+      <c r="D40">
+        <v>96.52947091496553</v>
+      </c>
+      <c r="E40">
+        <v>-67.48999999999998</v>
+      </c>
+      <c r="F40">
+        <v>165.11</v>
+      </c>
+      <c r="G40">
+        <v>314.8</v>
+      </c>
+      <c r="H40">
+        <v>201.9</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>52.2</v>
+      </c>
+      <c r="K40">
+        <v>23.1</v>
+      </c>
+      <c r="L40">
+        <v>29.1</v>
+      </c>
+      <c r="M40">
+        <v>11.590722</v>
+      </c>
+      <c r="N40">
+        <v>17.509278</v>
+      </c>
+      <c r="O40">
+        <v>2.88903087</v>
+      </c>
+      <c r="P40">
+        <v>14.62024713</v>
+      </c>
+      <c r="Q40">
+        <v>37.72024713</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.07557714435722968</v>
+      </c>
+      <c r="T40">
+        <v>0.6715262354858029</v>
+      </c>
+      <c r="U40">
+        <v>0.0702</v>
+      </c>
+      <c r="V40">
+        <v>0.165</v>
+      </c>
+      <c r="W40">
+        <v>0.058617</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>2.510628759795981</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.07082087471840606</v>
+      </c>
+      <c r="C41">
+        <v>236.7840966195132</v>
+      </c>
+      <c r="D41">
+        <v>91.43909661951319</v>
+      </c>
+      <c r="E41">
+        <v>-63.14499999999998</v>
+      </c>
+      <c r="F41">
+        <v>169.455</v>
+      </c>
+      <c r="G41">
+        <v>314.8</v>
+      </c>
+      <c r="H41">
+        <v>201.9</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>52.2</v>
+      </c>
+      <c r="K41">
+        <v>23.1</v>
+      </c>
+      <c r="L41">
+        <v>29.1</v>
+      </c>
+      <c r="M41">
+        <v>12.6921795</v>
+      </c>
+      <c r="N41">
+        <v>16.4078205</v>
+      </c>
+      <c r="O41">
+        <v>2.7072903825</v>
+      </c>
+      <c r="P41">
+        <v>13.7005301175</v>
+      </c>
+      <c r="Q41">
+        <v>36.8005301175</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.07611424544000994</v>
+      </c>
+      <c r="T41">
+        <v>0.6813333446156307</v>
+      </c>
+      <c r="U41">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V41">
+        <v>0.165</v>
+      </c>
+      <c r="W41">
+        <v>0.06254149999999999</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>2.292750429506611</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.07101814993532973</v>
+      </c>
+      <c r="C42">
+        <v>231.8792051404206</v>
+      </c>
+      <c r="D42">
+        <v>90.87920514042059</v>
+      </c>
+      <c r="E42">
+        <v>-58.79999999999998</v>
+      </c>
+      <c r="F42">
+        <v>173.8</v>
+      </c>
+      <c r="G42">
+        <v>314.8</v>
+      </c>
+      <c r="H42">
+        <v>201.9</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>52.2</v>
+      </c>
+      <c r="K42">
+        <v>23.1</v>
+      </c>
+      <c r="L42">
+        <v>29.1</v>
+      </c>
+      <c r="M42">
+        <v>13.01762</v>
+      </c>
+      <c r="N42">
+        <v>16.08238</v>
+      </c>
+      <c r="O42">
+        <v>2.6535927</v>
+      </c>
+      <c r="P42">
+        <v>13.4287873</v>
+      </c>
+      <c r="Q42">
+        <v>36.5287873</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.07666924989221624</v>
+      </c>
+      <c r="T42">
+        <v>0.6914673573831195</v>
+      </c>
+      <c r="U42">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V42">
+        <v>0.165</v>
+      </c>
+      <c r="W42">
+        <v>0.06254149999999999</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>2.235431668768945</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.0712154251522534</v>
+      </c>
+      <c r="C43">
+        <v>226.9811284855959</v>
+      </c>
+      <c r="D43">
+        <v>90.32612848559594</v>
+      </c>
+      <c r="E43">
+        <v>-54.45499999999998</v>
+      </c>
+      <c r="F43">
+        <v>178.145</v>
+      </c>
+      <c r="G43">
+        <v>314.8</v>
+      </c>
+      <c r="H43">
+        <v>201.9</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>52.2</v>
+      </c>
+      <c r="K43">
+        <v>23.1</v>
+      </c>
+      <c r="L43">
+        <v>29.1</v>
+      </c>
+      <c r="M43">
+        <v>13.3430605</v>
+      </c>
+      <c r="N43">
+        <v>15.7569395</v>
+      </c>
+      <c r="O43">
+        <v>2.5998950175</v>
+      </c>
+      <c r="P43">
+        <v>13.1570444825</v>
+      </c>
+      <c r="Q43">
+        <v>36.25704448250001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.0772430680546668</v>
+      </c>
+      <c r="T43">
+        <v>0.7019448960071334</v>
+      </c>
+      <c r="U43">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V43">
+        <v>0.165</v>
+      </c>
+      <c r="W43">
+        <v>0.06254149999999999</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>2.180908945140435</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.07141270036917707</v>
+      </c>
+      <c r="C44">
+        <v>222.0897429858012</v>
+      </c>
+      <c r="D44">
+        <v>89.77974298580112</v>
+      </c>
+      <c r="E44">
+        <v>-50.11000000000001</v>
+      </c>
+      <c r="F44">
+        <v>182.49</v>
+      </c>
+      <c r="G44">
+        <v>314.8</v>
+      </c>
+      <c r="H44">
+        <v>201.9</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>52.2</v>
+      </c>
+      <c r="K44">
+        <v>23.1</v>
+      </c>
+      <c r="L44">
+        <v>29.1</v>
+      </c>
+      <c r="M44">
+        <v>13.668501</v>
+      </c>
+      <c r="N44">
+        <v>15.431499</v>
+      </c>
+      <c r="O44">
+        <v>2.546197335000001</v>
+      </c>
+      <c r="P44">
+        <v>12.885301665</v>
+      </c>
+      <c r="Q44">
+        <v>35.98530166500001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.07783667305030531</v>
+      </c>
+      <c r="T44">
+        <v>0.7127837290664579</v>
+      </c>
+      <c r="U44">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V44">
+        <v>0.165</v>
+      </c>
+      <c r="W44">
+        <v>0.06254149999999999</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>2.128982541684711</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.07160997558610074</v>
+      </c>
+      <c r="C45">
+        <v>217.2049279461222</v>
+      </c>
+      <c r="D45">
+        <v>89.23992794612221</v>
+      </c>
+      <c r="E45">
+        <v>-45.76499999999999</v>
+      </c>
+      <c r="F45">
+        <v>186.835</v>
+      </c>
+      <c r="G45">
+        <v>314.8</v>
+      </c>
+      <c r="H45">
+        <v>201.9</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>52.2</v>
+      </c>
+      <c r="K45">
+        <v>23.1</v>
+      </c>
+      <c r="L45">
+        <v>29.1</v>
+      </c>
+      <c r="M45">
+        <v>13.9939415</v>
+      </c>
+      <c r="N45">
+        <v>15.1060585</v>
+      </c>
+      <c r="O45">
+        <v>2.4924996525</v>
+      </c>
+      <c r="P45">
+        <v>12.6135588475</v>
+      </c>
+      <c r="Q45">
+        <v>35.7135588475</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.07845110629140481</v>
+      </c>
+      <c r="T45">
+        <v>0.7240028720576887</v>
+      </c>
+      <c r="U45">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V45">
+        <v>0.165</v>
+      </c>
+      <c r="W45">
+        <v>0.06254149999999999</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>2.079471319785066</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.07180725080302441</v>
+      </c>
+      <c r="C46">
+        <v>212.3265655570858</v>
+      </c>
+      <c r="D46">
+        <v>88.70656555708582</v>
+      </c>
+      <c r="E46">
+        <v>-41.41999999999999</v>
+      </c>
+      <c r="F46">
+        <v>191.18</v>
+      </c>
+      <c r="G46">
+        <v>314.8</v>
+      </c>
+      <c r="H46">
+        <v>201.9</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>52.2</v>
+      </c>
+      <c r="K46">
+        <v>23.1</v>
+      </c>
+      <c r="L46">
+        <v>29.1</v>
+      </c>
+      <c r="M46">
+        <v>14.319382</v>
+      </c>
+      <c r="N46">
+        <v>14.780618</v>
+      </c>
+      <c r="O46">
+        <v>2.438801970000001</v>
+      </c>
+      <c r="P46">
+        <v>12.34181603</v>
+      </c>
+      <c r="Q46">
+        <v>35.44181603000001</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.07908748357682931</v>
+      </c>
+      <c r="T46">
+        <v>0.7356226987271777</v>
+      </c>
+      <c r="U46">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V46">
+        <v>0.165</v>
+      </c>
+      <c r="W46">
+        <v>0.06254149999999999</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>2.032210607971769</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.07812925101994808</v>
+      </c>
+      <c r="C47">
+        <v>193.7223841043293</v>
+      </c>
+      <c r="D47">
+        <v>74.44738410432929</v>
+      </c>
+      <c r="E47">
+        <v>-37.07499999999999</v>
+      </c>
+      <c r="F47">
+        <v>195.525</v>
+      </c>
+      <c r="G47">
+        <v>314.8</v>
+      </c>
+      <c r="H47">
+        <v>201.9</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>52.2</v>
+      </c>
+      <c r="K47">
+        <v>23.1</v>
+      </c>
+      <c r="L47">
+        <v>29.1</v>
+      </c>
+      <c r="M47">
+        <v>17.83188</v>
+      </c>
+      <c r="N47">
+        <v>11.26812</v>
+      </c>
+      <c r="O47">
+        <v>1.8592398</v>
+      </c>
+      <c r="P47">
+        <v>9.408880199999999</v>
+      </c>
+      <c r="Q47">
+        <v>32.5088802</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.07974700185445105</v>
+      </c>
+      <c r="T47">
+        <v>0.7476650645482844</v>
+      </c>
+      <c r="U47">
+        <v>0.0912</v>
+      </c>
+      <c r="V47">
+        <v>0.165</v>
+      </c>
+      <c r="W47">
+        <v>0.076152</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>1.631908693867388</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.07846263123687175</v>
+      </c>
+      <c r="C48">
+        <v>188.7516241814973</v>
+      </c>
+      <c r="D48">
+        <v>73.82162418149724</v>
+      </c>
+      <c r="E48">
+        <v>-32.72999999999999</v>
+      </c>
+      <c r="F48">
+        <v>199.87</v>
+      </c>
+      <c r="G48">
+        <v>314.8</v>
+      </c>
+      <c r="H48">
+        <v>201.9</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>52.2</v>
+      </c>
+      <c r="K48">
+        <v>23.1</v>
+      </c>
+      <c r="L48">
+        <v>29.1</v>
+      </c>
+      <c r="M48">
+        <v>18.228144</v>
+      </c>
+      <c r="N48">
+        <v>10.871856</v>
+      </c>
+      <c r="O48">
+        <v>1.79385624</v>
+      </c>
+      <c r="P48">
+        <v>9.077999760000001</v>
+      </c>
+      <c r="Q48">
+        <v>32.17799976000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.08043094673494769</v>
+      </c>
+      <c r="T48">
+        <v>0.7601534439183212</v>
+      </c>
+      <c r="U48">
+        <v>0.0912</v>
+      </c>
+      <c r="V48">
+        <v>0.165</v>
+      </c>
+      <c r="W48">
+        <v>0.076152</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>1.596432417913749</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.07879601145379542</v>
+      </c>
+      <c r="C49">
+        <v>183.7912960978028</v>
+      </c>
+      <c r="D49">
+        <v>73.20629609780278</v>
+      </c>
+      <c r="E49">
+        <v>-28.38499999999999</v>
+      </c>
+      <c r="F49">
+        <v>204.215</v>
+      </c>
+      <c r="G49">
+        <v>314.8</v>
+      </c>
+      <c r="H49">
+        <v>201.9</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>52.2</v>
+      </c>
+      <c r="K49">
+        <v>23.1</v>
+      </c>
+      <c r="L49">
+        <v>29.1</v>
+      </c>
+      <c r="M49">
+        <v>18.624408</v>
+      </c>
+      <c r="N49">
+        <v>10.475592</v>
+      </c>
+      <c r="O49">
+        <v>1.72847268</v>
+      </c>
+      <c r="P49">
+        <v>8.747119319999999</v>
+      </c>
+      <c r="Q49">
+        <v>31.84711932</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.08114070085621777</v>
+      </c>
+      <c r="T49">
+        <v>0.7731130828872271</v>
+      </c>
+      <c r="U49">
+        <v>0.0912</v>
+      </c>
+      <c r="V49">
+        <v>0.165</v>
+      </c>
+      <c r="W49">
+        <v>0.076152</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>1.562465770724095</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.07912939167071908</v>
+      </c>
+      <c r="C50">
+        <v>178.8411411509459</v>
+      </c>
+      <c r="D50">
+        <v>72.60114115094592</v>
+      </c>
+      <c r="E50">
+        <v>-24.03999999999999</v>
+      </c>
+      <c r="F50">
+        <v>208.56</v>
+      </c>
+      <c r="G50">
+        <v>314.8</v>
+      </c>
+      <c r="H50">
+        <v>201.9</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>52.2</v>
+      </c>
+      <c r="K50">
+        <v>23.1</v>
+      </c>
+      <c r="L50">
+        <v>29.1</v>
+      </c>
+      <c r="M50">
+        <v>19.020672</v>
+      </c>
+      <c r="N50">
+        <v>10.079328</v>
+      </c>
+      <c r="O50">
+        <v>1.66308912</v>
+      </c>
+      <c r="P50">
+        <v>8.41623888</v>
+      </c>
+      <c r="Q50">
+        <v>31.51623888</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.08187775321292132</v>
+      </c>
+      <c r="T50">
+        <v>0.7865711695087833</v>
+      </c>
+      <c r="U50">
+        <v>0.0912</v>
+      </c>
+      <c r="V50">
+        <v>0.165</v>
+      </c>
+      <c r="W50">
+        <v>0.076152</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>1.529914400500676</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1080818397146153</v>
+      </c>
+      <c r="C51">
+        <v>144.1565777710071</v>
+      </c>
+      <c r="D51">
+        <v>42.26157777100707</v>
+      </c>
+      <c r="E51">
+        <v>-19.69499999999999</v>
+      </c>
+      <c r="F51">
+        <v>212.905</v>
+      </c>
+      <c r="G51">
+        <v>314.8</v>
+      </c>
+      <c r="H51">
+        <v>201.9</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>52.2</v>
+      </c>
+      <c r="K51">
+        <v>23.1</v>
+      </c>
+      <c r="L51">
+        <v>29.1</v>
+      </c>
+      <c r="M51">
+        <v>33.340923</v>
+      </c>
+      <c r="N51">
+        <v>-4.240923000000002</v>
+      </c>
+      <c r="O51">
+        <v>-0.6997522950000004</v>
+      </c>
+      <c r="P51">
+        <v>-3.541170705000002</v>
+      </c>
+      <c r="Q51">
+        <v>19.558829295</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.08313426005099543</v>
+      </c>
+      <c r="T51">
+        <v>0.809514150035987</v>
+      </c>
+      <c r="U51">
+        <v>0.1566</v>
+      </c>
+      <c r="V51">
+        <v>0.144012209859937</v>
+      </c>
+      <c r="W51">
+        <v>0.1340476879359339</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.8728012718784059</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1092598397146153</v>
+      </c>
+      <c r="C52">
+        <v>139.1050172846948</v>
+      </c>
+      <c r="D52">
+        <v>41.55501728469476</v>
+      </c>
+      <c r="E52">
+        <v>-15.34999999999999</v>
+      </c>
+      <c r="F52">
+        <v>217.25</v>
+      </c>
+      <c r="G52">
+        <v>314.8</v>
+      </c>
+      <c r="H52">
+        <v>201.9</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>52.2</v>
+      </c>
+      <c r="K52">
+        <v>23.1</v>
+      </c>
+      <c r="L52">
+        <v>29.1</v>
+      </c>
+      <c r="M52">
+        <v>34.02135000000001</v>
+      </c>
+      <c r="N52">
+        <v>-4.921350000000004</v>
+      </c>
+      <c r="O52">
+        <v>-0.8120227500000007</v>
+      </c>
+      <c r="P52">
+        <v>-4.109327250000003</v>
+      </c>
+      <c r="Q52">
+        <v>18.99067275</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.08402094525201534</v>
+      </c>
+      <c r="T52">
+        <v>0.8257044330367068</v>
+      </c>
+      <c r="U52">
+        <v>0.1566</v>
+      </c>
+      <c r="V52">
+        <v>0.1411319656627382</v>
+      </c>
+      <c r="W52">
+        <v>0.1344987341772152</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.8553452464408378</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1104378397146153</v>
+      </c>
+      <c r="C53">
+        <v>134.0766939103945</v>
+      </c>
+      <c r="D53">
+        <v>40.87169391039451</v>
+      </c>
+      <c r="E53">
+        <v>-11.005</v>
+      </c>
+      <c r="F53">
+        <v>221.595</v>
+      </c>
+      <c r="G53">
+        <v>314.8</v>
+      </c>
+      <c r="H53">
+        <v>201.9</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>52.2</v>
+      </c>
+      <c r="K53">
+        <v>23.1</v>
+      </c>
+      <c r="L53">
+        <v>29.1</v>
+      </c>
+      <c r="M53">
+        <v>34.70177700000001</v>
+      </c>
+      <c r="N53">
+        <v>-5.601777000000006</v>
+      </c>
+      <c r="O53">
+        <v>-0.924293205000001</v>
+      </c>
+      <c r="P53">
+        <v>-4.677483795000004</v>
+      </c>
+      <c r="Q53">
+        <v>18.422516205</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.08494382168572995</v>
+      </c>
+      <c r="T53">
+        <v>0.842555543915007</v>
+      </c>
+      <c r="U53">
+        <v>0.1566</v>
+      </c>
+      <c r="V53">
+        <v>0.1383646722183708</v>
+      </c>
+      <c r="W53">
+        <v>0.1349320923306032</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.8385737710204292</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1116158397146153</v>
+      </c>
+      <c r="C54">
+        <v>129.0704798721421</v>
+      </c>
+      <c r="D54">
+        <v>40.21047987214204</v>
+      </c>
+      <c r="E54">
+        <v>-6.659999999999997</v>
+      </c>
+      <c r="F54">
+        <v>225.94</v>
+      </c>
+      <c r="G54">
+        <v>314.8</v>
+      </c>
+      <c r="H54">
+        <v>201.9</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>52.2</v>
+      </c>
+      <c r="K54">
+        <v>23.1</v>
+      </c>
+      <c r="L54">
+        <v>29.1</v>
+      </c>
+      <c r="M54">
+        <v>35.382204</v>
+      </c>
+      <c r="N54">
+        <v>-6.282204</v>
+      </c>
+      <c r="O54">
+        <v>-1.03656366</v>
+      </c>
+      <c r="P54">
+        <v>-5.24564034</v>
+      </c>
+      <c r="Q54">
+        <v>17.85435966</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.08590515130418265</v>
+      </c>
+      <c r="T54">
+        <v>0.8601087844132362</v>
+      </c>
+      <c r="U54">
+        <v>0.1566</v>
+      </c>
+      <c r="V54">
+        <v>0.1357038131372483</v>
+      </c>
+      <c r="W54">
+        <v>0.1353487828627069</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.8224473523469595</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1127938397146153</v>
+      </c>
+      <c r="C55">
+        <v>124.0853192118482</v>
+      </c>
+      <c r="D55">
+        <v>39.57031921184823</v>
+      </c>
+      <c r="E55">
+        <v>-2.314999999999969</v>
+      </c>
+      <c r="F55">
+        <v>230.285</v>
+      </c>
+      <c r="G55">
+        <v>314.8</v>
+      </c>
+      <c r="H55">
+        <v>201.9</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>52.2</v>
+      </c>
+      <c r="K55">
+        <v>23.1</v>
+      </c>
+      <c r="L55">
+        <v>29.1</v>
+      </c>
+      <c r="M55">
+        <v>36.06263100000001</v>
+      </c>
+      <c r="N55">
+        <v>-6.962631000000009</v>
+      </c>
+      <c r="O55">
+        <v>-1.148834115000001</v>
+      </c>
+      <c r="P55">
+        <v>-5.813796885000007</v>
+      </c>
+      <c r="Q55">
+        <v>17.28620311499999</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.08690738856597377</v>
+      </c>
+      <c r="T55">
+        <v>0.8784089713156455</v>
+      </c>
+      <c r="U55">
+        <v>0.1566</v>
+      </c>
+      <c r="V55">
+        <v>0.1331433638327719</v>
+      </c>
+      <c r="W55">
+        <v>0.1357497492237879</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.8069294777743752</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1425890068727091</v>
+      </c>
+      <c r="C56">
+        <v>108.3806934582063</v>
+      </c>
+      <c r="D56">
+        <v>28.21069345820626</v>
+      </c>
+      <c r="E56">
+        <v>2.03000000000003</v>
+      </c>
+      <c r="F56">
+        <v>234.63</v>
+      </c>
+      <c r="G56">
+        <v>314.8</v>
+      </c>
+      <c r="H56">
+        <v>201.9</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>52.2</v>
+      </c>
+      <c r="K56">
+        <v>23.1</v>
+      </c>
+      <c r="L56">
+        <v>29.1</v>
+      </c>
+      <c r="M56">
+        <v>48.99074400000001</v>
+      </c>
+      <c r="N56">
+        <v>-19.89074400000001</v>
+      </c>
+      <c r="O56">
+        <v>-3.281972760000001</v>
+      </c>
+      <c r="P56">
+        <v>-16.60877124</v>
+      </c>
+      <c r="Q56">
+        <v>6.491228759999998</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.08888617344369895</v>
+      </c>
+      <c r="T56">
+        <v>0.9145402692453556</v>
+      </c>
+      <c r="U56">
+        <v>0.2088</v>
+      </c>
+      <c r="V56">
+        <v>0.09800830948801266</v>
+      </c>
+      <c r="W56">
+        <v>0.188335864978903</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.5939897544728041</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1442890068727091</v>
+      </c>
+      <c r="C57">
+        <v>103.5810661913402</v>
+      </c>
+      <c r="D57">
+        <v>27.75606619134023</v>
+      </c>
+      <c r="E57">
+        <v>6.375000000000028</v>
+      </c>
+      <c r="F57">
+        <v>238.975</v>
+      </c>
+      <c r="G57">
+        <v>314.8</v>
+      </c>
+      <c r="H57">
+        <v>201.9</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>52.2</v>
+      </c>
+      <c r="K57">
+        <v>23.1</v>
+      </c>
+      <c r="L57">
+        <v>29.1</v>
+      </c>
+      <c r="M57">
+        <v>49.89798000000001</v>
+      </c>
+      <c r="N57">
+        <v>-20.79798000000001</v>
+      </c>
+      <c r="O57">
+        <v>-3.431666700000002</v>
+      </c>
+      <c r="P57">
+        <v>-17.36631330000001</v>
+      </c>
+      <c r="Q57">
+        <v>5.733686699999993</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.08999919952022559</v>
+      </c>
+      <c r="T57">
+        <v>0.9348633863396968</v>
+      </c>
+      <c r="U57">
+        <v>0.2088</v>
+      </c>
+      <c r="V57">
+        <v>0.09622634022459425</v>
+      </c>
+      <c r="W57">
+        <v>0.1887079401611047</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.5831899407551167</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1459890068727091</v>
+      </c>
+      <c r="C58">
+        <v>98.79585955166763</v>
+      </c>
+      <c r="D58">
+        <v>27.31585955166763</v>
+      </c>
+      <c r="E58">
+        <v>10.72000000000003</v>
+      </c>
+      <c r="F58">
+        <v>243.32</v>
+      </c>
+      <c r="G58">
+        <v>314.8</v>
+      </c>
+      <c r="H58">
+        <v>201.9</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>52.2</v>
+      </c>
+      <c r="K58">
+        <v>23.1</v>
+      </c>
+      <c r="L58">
+        <v>29.1</v>
+      </c>
+      <c r="M58">
+        <v>50.80521600000001</v>
+      </c>
+      <c r="N58">
+        <v>-21.70521600000001</v>
+      </c>
+      <c r="O58">
+        <v>-3.581360640000002</v>
+      </c>
+      <c r="P58">
+        <v>-18.12385536000001</v>
+      </c>
+      <c r="Q58">
+        <v>4.976144639999994</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.09116281769113979</v>
+      </c>
+      <c r="T58">
+        <v>0.9561102814837807</v>
+      </c>
+      <c r="U58">
+        <v>0.2088</v>
+      </c>
+      <c r="V58">
+        <v>0.09450801272058365</v>
+      </c>
+      <c r="W58">
+        <v>0.1890667269439422</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.5727758346702039</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1476890068727091</v>
+      </c>
+      <c r="C59">
+        <v>94.02439812483027</v>
+      </c>
+      <c r="D59">
+        <v>26.88939812483031</v>
+      </c>
+      <c r="E59">
+        <v>15.06500000000003</v>
+      </c>
+      <c r="F59">
+        <v>247.665</v>
+      </c>
+      <c r="G59">
+        <v>314.8</v>
+      </c>
+      <c r="H59">
+        <v>201.9</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>52.2</v>
+      </c>
+      <c r="K59">
+        <v>23.1</v>
+      </c>
+      <c r="L59">
+        <v>29.1</v>
+      </c>
+      <c r="M59">
+        <v>51.71245200000001</v>
+      </c>
+      <c r="N59">
+        <v>-22.612452</v>
+      </c>
+      <c r="O59">
+        <v>-3.731054580000001</v>
+      </c>
+      <c r="P59">
+        <v>-18.88139742</v>
+      </c>
+      <c r="Q59">
+        <v>4.218602579999999</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.09238055763744538</v>
+      </c>
+      <c r="T59">
+        <v>0.978345404308985</v>
+      </c>
+      <c r="U59">
+        <v>0.2088</v>
+      </c>
+      <c r="V59">
+        <v>0.09284997740969622</v>
+      </c>
+      <c r="W59">
+        <v>0.1894129247168554</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.5627271358163406</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1493890068727091</v>
+      </c>
+      <c r="C60">
+        <v>89.26604802697813</v>
+      </c>
+      <c r="D60">
+        <v>26.47604802697812</v>
+      </c>
+      <c r="E60">
+        <v>19.41</v>
+      </c>
+      <c r="F60">
+        <v>252.01</v>
+      </c>
+      <c r="G60">
+        <v>314.8</v>
+      </c>
+      <c r="H60">
+        <v>201.9</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>52.2</v>
+      </c>
+      <c r="K60">
+        <v>23.1</v>
+      </c>
+      <c r="L60">
+        <v>29.1</v>
+      </c>
+      <c r="M60">
+        <v>52.619688</v>
+      </c>
+      <c r="N60">
+        <v>-23.519688</v>
+      </c>
+      <c r="O60">
+        <v>-3.88074852</v>
+      </c>
+      <c r="P60">
+        <v>-19.63893948</v>
+      </c>
+      <c r="Q60">
+        <v>3.46106052</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.09365628520024169</v>
+      </c>
+      <c r="T60">
+        <v>1.001639342506818</v>
+      </c>
+      <c r="U60">
+        <v>0.2088</v>
+      </c>
+      <c r="V60">
+        <v>0.09124911573021871</v>
+      </c>
+      <c r="W60">
+        <v>0.1897471846355304</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.5530249438195072</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1510890068727091</v>
+      </c>
+      <c r="C61">
+        <v>84.52021376101226</v>
+      </c>
+      <c r="D61">
+        <v>26.07521376101221</v>
+      </c>
+      <c r="E61">
+        <v>23.75499999999997</v>
+      </c>
+      <c r="F61">
+        <v>256.355</v>
+      </c>
+      <c r="G61">
+        <v>314.8</v>
+      </c>
+      <c r="H61">
+        <v>201.9</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>52.2</v>
+      </c>
+      <c r="K61">
+        <v>23.1</v>
+      </c>
+      <c r="L61">
+        <v>29.1</v>
+      </c>
+      <c r="M61">
+        <v>53.52692399999999</v>
+      </c>
+      <c r="N61">
+        <v>-24.42692399999999</v>
+      </c>
+      <c r="O61">
+        <v>-4.030442459999999</v>
+      </c>
+      <c r="P61">
+        <v>-20.39648153999999</v>
+      </c>
+      <c r="Q61">
+        <v>2.703518460000009</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.09499424337585732</v>
+      </c>
+      <c r="T61">
+        <v>1.026069570372838</v>
+      </c>
+      <c r="U61">
+        <v>0.2088</v>
+      </c>
+      <c r="V61">
+        <v>0.08970252054835059</v>
+      </c>
+      <c r="W61">
+        <v>0.1900701137095044</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.5436516396869733</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1527890068727091</v>
+      </c>
+      <c r="C62">
+        <v>79.786335354139</v>
+      </c>
+      <c r="D62">
+        <v>25.68633535413898</v>
+      </c>
+      <c r="E62">
+        <v>28.09999999999999</v>
+      </c>
+      <c r="F62">
+        <v>260.7</v>
+      </c>
+      <c r="G62">
+        <v>314.8</v>
+      </c>
+      <c r="H62">
+        <v>201.9</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>52.2</v>
+      </c>
+      <c r="K62">
+        <v>23.1</v>
+      </c>
+      <c r="L62">
+        <v>29.1</v>
+      </c>
+      <c r="M62">
+        <v>54.43416</v>
+      </c>
+      <c r="N62">
+        <v>-25.33416</v>
+      </c>
+      <c r="O62">
+        <v>-4.180136399999999</v>
+      </c>
+      <c r="P62">
+        <v>-21.1540236</v>
+      </c>
+      <c r="Q62">
+        <v>1.945976400000003</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.09639909946025377</v>
+      </c>
+      <c r="T62">
+        <v>1.051721309632159</v>
+      </c>
+      <c r="U62">
+        <v>0.2088</v>
+      </c>
+      <c r="V62">
+        <v>0.08820747853921143</v>
+      </c>
+      <c r="W62">
+        <v>0.1903822784810127</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.5345907790255238</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1544890068727091</v>
+      </c>
+      <c r="C63">
+        <v>75.06388574779839</v>
+      </c>
+      <c r="D63">
+        <v>25.3088857477984</v>
+      </c>
+      <c r="E63">
+        <v>32.44500000000002</v>
+      </c>
+      <c r="F63">
+        <v>265.045</v>
+      </c>
+      <c r="G63">
+        <v>314.8</v>
+      </c>
+      <c r="H63">
+        <v>201.9</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>52.2</v>
+      </c>
+      <c r="K63">
+        <v>23.1</v>
+      </c>
+      <c r="L63">
+        <v>29.1</v>
+      </c>
+      <c r="M63">
+        <v>55.34139600000001</v>
+      </c>
+      <c r="N63">
+        <v>-26.24139600000001</v>
+      </c>
+      <c r="O63">
+        <v>-4.329830340000002</v>
+      </c>
+      <c r="P63">
+        <v>-21.91156566000001</v>
+      </c>
+      <c r="Q63">
+        <v>1.188434339999993</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.09787599944641412</v>
+      </c>
+      <c r="T63">
+        <v>1.07868852269965</v>
+      </c>
+      <c r="U63">
+        <v>0.2088</v>
+      </c>
+      <c r="V63">
+        <v>0.08676145430086367</v>
+      </c>
+      <c r="W63">
+        <v>0.1906842083419797</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.5258269957628101</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1561890068727091</v>
+      </c>
+      <c r="C64">
+        <v>70.35236841438314</v>
+      </c>
+      <c r="D64">
+        <v>24.94236841438308</v>
+      </c>
+      <c r="E64">
+        <v>36.78999999999999</v>
+      </c>
+      <c r="F64">
+        <v>269.39</v>
+      </c>
+      <c r="G64">
+        <v>314.8</v>
+      </c>
+      <c r="H64">
+        <v>201.9</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>52.2</v>
+      </c>
+      <c r="K64">
+        <v>23.1</v>
+      </c>
+      <c r="L64">
+        <v>29.1</v>
+      </c>
+      <c r="M64">
+        <v>56.248632</v>
+      </c>
+      <c r="N64">
+        <v>-27.148632</v>
+      </c>
+      <c r="O64">
+        <v>-4.47952428</v>
+      </c>
+      <c r="P64">
+        <v>-22.66910772</v>
+      </c>
+      <c r="Q64">
+        <v>0.4308922800000019</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.09943063101079345</v>
+      </c>
+      <c r="T64">
+        <v>1.107075062770694</v>
+      </c>
+      <c r="U64">
+        <v>0.2088</v>
+      </c>
+      <c r="V64">
+        <v>0.08536207600568847</v>
+      </c>
+      <c r="W64">
+        <v>0.1909763985300123</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.5173459151859907</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1578890068727091</v>
+      </c>
+      <c r="C65">
+        <v>65.65131517808584</v>
+      </c>
+      <c r="D65">
+        <v>24.58631517808586</v>
+      </c>
+      <c r="E65">
+        <v>41.13500000000002</v>
+      </c>
+      <c r="F65">
+        <v>273.735</v>
+      </c>
+      <c r="G65">
+        <v>314.8</v>
+      </c>
+      <c r="H65">
+        <v>201.9</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>52.2</v>
+      </c>
+      <c r="K65">
+        <v>23.1</v>
+      </c>
+      <c r="L65">
+        <v>29.1</v>
+      </c>
+      <c r="M65">
+        <v>57.15586800000001</v>
+      </c>
+      <c r="N65">
+        <v>-28.055868</v>
+      </c>
+      <c r="O65">
+        <v>-4.629218220000001</v>
+      </c>
+      <c r="P65">
+        <v>-23.42664978</v>
+      </c>
+      <c r="Q65">
+        <v>-0.3266497800000003</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1010692967137879</v>
+      </c>
+      <c r="T65">
+        <v>1.136996010413144</v>
+      </c>
+      <c r="U65">
+        <v>0.2088</v>
+      </c>
+      <c r="V65">
+        <v>0.08400712241829658</v>
+      </c>
+      <c r="W65">
+        <v>0.1912593128390597</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.5091340752624035</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1595890068727091</v>
+      </c>
+      <c r="C66">
+        <v>60.96028421976536</v>
+      </c>
+      <c r="D66">
+        <v>24.24028421976536</v>
+      </c>
+      <c r="E66">
+        <v>45.47999999999999</v>
+      </c>
+      <c r="F66">
+        <v>278.08</v>
+      </c>
+      <c r="G66">
+        <v>314.8</v>
+      </c>
+      <c r="H66">
+        <v>201.9</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>52.2</v>
+      </c>
+      <c r="K66">
+        <v>23.1</v>
+      </c>
+      <c r="L66">
+        <v>29.1</v>
+      </c>
+      <c r="M66">
+        <v>58.063104</v>
+      </c>
+      <c r="N66">
+        <v>-28.963104</v>
+      </c>
+      <c r="O66">
+        <v>-4.778912160000001</v>
+      </c>
+      <c r="P66">
+        <v>-24.18419184</v>
+      </c>
+      <c r="Q66">
+        <v>-1.084191839999999</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.102798999400282</v>
+      </c>
+      <c r="T66">
+        <v>1.168579232924621</v>
+      </c>
+      <c r="U66">
+        <v>0.2088</v>
+      </c>
+      <c r="V66">
+        <v>0.0826945111305107</v>
+      </c>
+      <c r="W66">
+        <v>0.1915333860759494</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.5011788553364285</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1809507532890761</v>
+      </c>
+      <c r="C67">
+        <v>52.97256835240535</v>
+      </c>
+      <c r="D67">
+        <v>20.59756835240537</v>
+      </c>
+      <c r="E67">
+        <v>49.82500000000002</v>
+      </c>
+      <c r="F67">
+        <v>282.425</v>
+      </c>
+      <c r="G67">
+        <v>314.8</v>
+      </c>
+      <c r="H67">
+        <v>201.9</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>52.2</v>
+      </c>
+      <c r="K67">
+        <v>23.1</v>
+      </c>
+      <c r="L67">
+        <v>29.1</v>
+      </c>
+      <c r="M67">
+        <v>67.44309000000001</v>
+      </c>
+      <c r="N67">
+        <v>-38.34309000000001</v>
+      </c>
+      <c r="O67">
+        <v>-6.326609850000002</v>
+      </c>
+      <c r="P67">
+        <v>-32.01648015000001</v>
+      </c>
+      <c r="Q67">
+        <v>-8.916480150000005</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1050896748584815</v>
+      </c>
+      <c r="T67">
+        <v>1.210405445754603</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.07119335724386293</v>
+      </c>
+      <c r="W67">
+        <v>0.2217990262901655</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.4314748923870481</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1829507532890761</v>
+      </c>
+      <c r="C68">
+        <v>48.34179019471372</v>
+      </c>
+      <c r="D68">
+        <v>20.31179019471377</v>
+      </c>
+      <c r="E68">
+        <v>54.17000000000004</v>
+      </c>
+      <c r="F68">
+        <v>286.77</v>
+      </c>
+      <c r="G68">
+        <v>314.8</v>
+      </c>
+      <c r="H68">
+        <v>201.9</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>52.2</v>
+      </c>
+      <c r="K68">
+        <v>23.1</v>
+      </c>
+      <c r="L68">
+        <v>29.1</v>
+      </c>
+      <c r="M68">
+        <v>68.48067600000002</v>
+      </c>
+      <c r="N68">
+        <v>-39.38067600000002</v>
+      </c>
+      <c r="O68">
+        <v>-6.497811540000002</v>
+      </c>
+      <c r="P68">
+        <v>-32.88286446000001</v>
+      </c>
+      <c r="Q68">
+        <v>-9.782864460000013</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1070393711778486</v>
+      </c>
+      <c r="T68">
+        <v>1.246005605923856</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.0701146700128953</v>
+      </c>
+      <c r="W68">
+        <v>0.2220566168009206</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.4249373940175473</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1849507532890761</v>
+      </c>
+      <c r="C69">
+        <v>43.71883349948502</v>
+      </c>
+      <c r="D69">
+        <v>20.03383349948499</v>
+      </c>
+      <c r="E69">
+        <v>58.51500000000001</v>
+      </c>
+      <c r="F69">
+        <v>291.115</v>
+      </c>
+      <c r="G69">
+        <v>314.8</v>
+      </c>
+      <c r="H69">
+        <v>201.9</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>52.2</v>
+      </c>
+      <c r="K69">
+        <v>23.1</v>
+      </c>
+      <c r="L69">
+        <v>29.1</v>
+      </c>
+      <c r="M69">
+        <v>69.51826200000001</v>
+      </c>
+      <c r="N69">
+        <v>-40.41826200000001</v>
+      </c>
+      <c r="O69">
+        <v>-6.669013230000001</v>
+      </c>
+      <c r="P69">
+        <v>-33.74924877000001</v>
+      </c>
+      <c r="Q69">
+        <v>-10.64924877000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1091072309105107</v>
+      </c>
+      <c r="T69">
+        <v>1.283763351557912</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.06906818240076255</v>
+      </c>
+      <c r="W69">
+        <v>0.2223065180426979</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.4185950448531064</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1869507532890761</v>
+      </c>
+      <c r="C70">
+        <v>39.1033815030595</v>
+      </c>
+      <c r="D70">
+        <v>19.76338150305951</v>
+      </c>
+      <c r="E70">
+        <v>62.86000000000004</v>
+      </c>
+      <c r="F70">
+        <v>295.46</v>
+      </c>
+      <c r="G70">
+        <v>314.8</v>
+      </c>
+      <c r="H70">
+        <v>201.9</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>52.2</v>
+      </c>
+      <c r="K70">
+        <v>23.1</v>
+      </c>
+      <c r="L70">
+        <v>29.1</v>
+      </c>
+      <c r="M70">
+        <v>70.55584800000001</v>
+      </c>
+      <c r="N70">
+        <v>-41.45584800000001</v>
+      </c>
+      <c r="O70">
+        <v>-6.840214920000002</v>
+      </c>
+      <c r="P70">
+        <v>-34.61563308000001</v>
+      </c>
+      <c r="Q70">
+        <v>-11.51563308000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1113043318764642</v>
+      </c>
+      <c r="T70">
+        <v>1.323880956294097</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.06805247383604544</v>
+      </c>
+      <c r="W70">
+        <v>0.2225490692479524</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.4124392353699724</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1889507532890762</v>
+      </c>
+      <c r="C71">
+        <v>34.49513431887777</v>
+      </c>
+      <c r="D71">
+        <v>19.50013431887775</v>
+      </c>
+      <c r="E71">
+        <v>67.20500000000001</v>
+      </c>
+      <c r="F71">
+        <v>299.805</v>
+      </c>
+      <c r="G71">
+        <v>314.8</v>
+      </c>
+      <c r="H71">
+        <v>201.9</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>52.2</v>
+      </c>
+      <c r="K71">
+        <v>23.1</v>
+      </c>
+      <c r="L71">
+        <v>29.1</v>
+      </c>
+      <c r="M71">
+        <v>71.593434</v>
+      </c>
+      <c r="N71">
+        <v>-42.493434</v>
+      </c>
+      <c r="O71">
+        <v>-7.01141661</v>
+      </c>
+      <c r="P71">
+        <v>-35.48201739</v>
+      </c>
+      <c r="Q71">
+        <v>-12.38201739</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.113643181291834</v>
+      </c>
+      <c r="T71">
+        <v>1.366586793593907</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.06706620609929118</v>
+      </c>
+      <c r="W71">
+        <v>0.2227845899834893</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.4064618551472192</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1909507532890762</v>
+      </c>
+      <c r="C72">
+        <v>29.89380782824475</v>
+      </c>
+      <c r="D72">
+        <v>19.24380782824477</v>
+      </c>
+      <c r="E72">
+        <v>71.55000000000004</v>
+      </c>
+      <c r="F72">
+        <v>304.15</v>
+      </c>
+      <c r="G72">
+        <v>314.8</v>
+      </c>
+      <c r="H72">
+        <v>201.9</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>52.2</v>
+      </c>
+      <c r="K72">
+        <v>23.1</v>
+      </c>
+      <c r="L72">
+        <v>29.1</v>
+      </c>
+      <c r="M72">
+        <v>72.63102000000001</v>
+      </c>
+      <c r="N72">
+        <v>-43.53102000000001</v>
+      </c>
+      <c r="O72">
+        <v>-7.182618300000001</v>
+      </c>
+      <c r="P72">
+        <v>-36.3484017</v>
+      </c>
+      <c r="Q72">
+        <v>-13.2484017</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1161379540015618</v>
+      </c>
+      <c r="T72">
+        <v>1.412139686713703</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.06610811744072988</v>
+      </c>
+      <c r="W72">
+        <v>0.2230133815551537</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.4006552572165446</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1929507532890761</v>
+      </c>
+      <c r="C73">
+        <v>25.29913265744415</v>
+      </c>
+      <c r="D73">
+        <v>18.99413265744415</v>
+      </c>
+      <c r="E73">
+        <v>75.89500000000001</v>
+      </c>
+      <c r="F73">
+        <v>308.495</v>
+      </c>
+      <c r="G73">
+        <v>314.8</v>
+      </c>
+      <c r="H73">
+        <v>201.9</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>52.2</v>
+      </c>
+      <c r="K73">
+        <v>23.1</v>
+      </c>
+      <c r="L73">
+        <v>29.1</v>
+      </c>
+      <c r="M73">
+        <v>73.66860600000001</v>
+      </c>
+      <c r="N73">
+        <v>-44.56860600000001</v>
+      </c>
+      <c r="O73">
+        <v>-7.353819990000002</v>
+      </c>
+      <c r="P73">
+        <v>-37.21478601000001</v>
+      </c>
+      <c r="Q73">
+        <v>-14.11478601000001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1188047800016156</v>
+      </c>
+      <c r="T73">
+        <v>1.460834158669348</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.06517701719508578</v>
+      </c>
+      <c r="W73">
+        <v>0.2232357282938135</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3950122254247623</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1949507532890761</v>
+      </c>
+      <c r="C74">
+        <v>20.71085323345983</v>
+      </c>
+      <c r="D74">
+        <v>18.7508532334598</v>
+      </c>
+      <c r="E74">
+        <v>80.23999999999998</v>
+      </c>
+      <c r="F74">
+        <v>312.84</v>
+      </c>
+      <c r="G74">
+        <v>314.8</v>
+      </c>
+      <c r="H74">
+        <v>201.9</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>52.2</v>
+      </c>
+      <c r="K74">
+        <v>23.1</v>
+      </c>
+      <c r="L74">
+        <v>29.1</v>
+      </c>
+      <c r="M74">
+        <v>74.706192</v>
+      </c>
+      <c r="N74">
+        <v>-45.606192</v>
+      </c>
+      <c r="O74">
+        <v>-7.52502168</v>
+      </c>
+      <c r="P74">
+        <v>-38.08117032</v>
+      </c>
+      <c r="Q74">
+        <v>-14.98117032</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1216620935731019</v>
+      </c>
+      <c r="T74">
+        <v>1.513006807193253</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.06427178084515404</v>
+      </c>
+      <c r="W74">
+        <v>0.2234518987341772</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3895259445160851</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1969507532890761</v>
+      </c>
+      <c r="C75">
+        <v>16.12872691134629</v>
+      </c>
+      <c r="D75">
+        <v>18.5137269113463</v>
+      </c>
+      <c r="E75">
+        <v>84.58500000000001</v>
+      </c>
+      <c r="F75">
+        <v>317.185</v>
+      </c>
+      <c r="G75">
+        <v>314.8</v>
+      </c>
+      <c r="H75">
+        <v>201.9</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>52.2</v>
+      </c>
+      <c r="K75">
+        <v>23.1</v>
+      </c>
+      <c r="L75">
+        <v>29.1</v>
+      </c>
+      <c r="M75">
+        <v>75.74377800000001</v>
+      </c>
+      <c r="N75">
+        <v>-46.643778</v>
+      </c>
+      <c r="O75">
+        <v>-7.696223370000001</v>
+      </c>
+      <c r="P75">
+        <v>-38.94755463000001</v>
+      </c>
+      <c r="Q75">
+        <v>-15.84755463</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1247310600017353</v>
+      </c>
+      <c r="T75">
+        <v>1.569044096348559</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.06339134549111083</v>
+      </c>
+      <c r="W75">
+        <v>0.2236621466967227</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3841899726733989</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1989507532890761</v>
+      </c>
+      <c r="C76">
+        <v>11.55252316698517</v>
+      </c>
+      <c r="D76">
+        <v>18.28252316698515</v>
+      </c>
+      <c r="E76">
+        <v>88.92999999999998</v>
+      </c>
+      <c r="F76">
+        <v>321.53</v>
+      </c>
+      <c r="G76">
+        <v>314.8</v>
+      </c>
+      <c r="H76">
+        <v>201.9</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>52.2</v>
+      </c>
+      <c r="K76">
+        <v>23.1</v>
+      </c>
+      <c r="L76">
+        <v>29.1</v>
+      </c>
+      <c r="M76">
+        <v>76.781364</v>
+      </c>
+      <c r="N76">
+        <v>-47.68136399999999</v>
+      </c>
+      <c r="O76">
+        <v>-7.86742506</v>
+      </c>
+      <c r="P76">
+        <v>-39.81393893999999</v>
+      </c>
+      <c r="Q76">
+        <v>-16.71393893999999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1280361007710328</v>
+      </c>
+      <c r="T76">
+        <v>1.629391946208119</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.06253470568717691</v>
+      </c>
+      <c r="W76">
+        <v>0.2238667122819022</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.3789982162859207</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2009507532890761</v>
+      </c>
+      <c r="C77">
+        <v>6.982022849581256</v>
+      </c>
+      <c r="D77">
+        <v>18.05702284958123</v>
+      </c>
+      <c r="E77">
+        <v>93.27500000000001</v>
+      </c>
+      <c r="F77">
+        <v>325.875</v>
+      </c>
+      <c r="G77">
+        <v>314.8</v>
+      </c>
+      <c r="H77">
+        <v>201.9</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>52.2</v>
+      </c>
+      <c r="K77">
+        <v>23.1</v>
+      </c>
+      <c r="L77">
+        <v>29.1</v>
+      </c>
+      <c r="M77">
+        <v>77.81895</v>
+      </c>
+      <c r="N77">
+        <v>-48.71895</v>
+      </c>
+      <c r="O77">
+        <v>-8.038626750000001</v>
+      </c>
+      <c r="P77">
+        <v>-40.68032325</v>
+      </c>
+      <c r="Q77">
+        <v>-17.58032325</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1316055448018741</v>
+      </c>
+      <c r="T77">
+        <v>1.694567624056444</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.06170090961134789</v>
+      </c>
+      <c r="W77">
+        <v>0.2240658227848101</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3739449067354417</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2029507532890761</v>
+      </c>
+      <c r="C78">
+        <v>2.417017488804333</v>
+      </c>
+      <c r="D78">
+        <v>17.83701748880434</v>
+      </c>
+      <c r="E78">
+        <v>97.62000000000003</v>
+      </c>
+      <c r="F78">
+        <v>330.22</v>
+      </c>
+      <c r="G78">
+        <v>314.8</v>
+      </c>
+      <c r="H78">
+        <v>201.9</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>52.2</v>
+      </c>
+      <c r="K78">
+        <v>23.1</v>
+      </c>
+      <c r="L78">
+        <v>29.1</v>
+      </c>
+      <c r="M78">
+        <v>78.85653600000001</v>
+      </c>
+      <c r="N78">
+        <v>-49.756536</v>
+      </c>
+      <c r="O78">
+        <v>-8.209828440000001</v>
+      </c>
+      <c r="P78">
+        <v>-41.54670756</v>
+      </c>
+      <c r="Q78">
+        <v>-18.44670756</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.1354724425019522</v>
+      </c>
+      <c r="T78">
+        <v>1.765174608392129</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.06088905553751436</v>
+      </c>
+      <c r="W78">
+        <v>0.2242596935376416</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3690245790152386</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2049507532890761</v>
+      </c>
+      <c r="C79">
+        <v>-2.142691348028563</v>
+      </c>
+      <c r="D79">
+        <v>17.62230865197143</v>
+      </c>
+      <c r="E79">
+        <v>101.965</v>
+      </c>
+      <c r="F79">
+        <v>334.565</v>
+      </c>
+      <c r="G79">
+        <v>314.8</v>
+      </c>
+      <c r="H79">
+        <v>201.9</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>52.2</v>
+      </c>
+      <c r="K79">
+        <v>23.1</v>
+      </c>
+      <c r="L79">
+        <v>29.1</v>
+      </c>
+      <c r="M79">
+        <v>79.89412200000001</v>
+      </c>
+      <c r="N79">
+        <v>-50.79412200000001</v>
+      </c>
+      <c r="O79">
+        <v>-8.381030130000001</v>
+      </c>
+      <c r="P79">
+        <v>-42.41309187000001</v>
+      </c>
+      <c r="Q79">
+        <v>-19.31309187000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.1396755921759502</v>
+      </c>
+      <c r="T79">
+        <v>1.841921330496135</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.06009828858248169</v>
+      </c>
+      <c r="W79">
+        <v>0.2244485286865034</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3642320520150406</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2069507532890761</v>
+      </c>
+      <c r="C80">
+        <v>-6.697292652896692</v>
+      </c>
+      <c r="D80">
+        <v>17.41270734710334</v>
+      </c>
+      <c r="E80">
+        <v>106.31</v>
+      </c>
+      <c r="F80">
+        <v>338.91</v>
+      </c>
+      <c r="G80">
+        <v>314.8</v>
+      </c>
+      <c r="H80">
+        <v>201.9</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>52.2</v>
+      </c>
+      <c r="K80">
+        <v>23.1</v>
+      </c>
+      <c r="L80">
+        <v>29.1</v>
+      </c>
+      <c r="M80">
+        <v>80.93170800000001</v>
+      </c>
+      <c r="N80">
+        <v>-51.83170800000001</v>
+      </c>
+      <c r="O80">
+        <v>-8.552231820000003</v>
+      </c>
+      <c r="P80">
+        <v>-43.27947618000001</v>
+      </c>
+      <c r="Q80">
+        <v>-20.17947618000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.1442608463657661</v>
+      </c>
+      <c r="T80">
+        <v>1.925645027336868</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.05932779770321911</v>
+      </c>
+      <c r="W80">
+        <v>0.2246325219084713</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.35956241032254</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2089507532890761</v>
+      </c>
+      <c r="C81">
+        <v>-11.24696653191876</v>
+      </c>
+      <c r="D81">
+        <v>17.20803346808124</v>
+      </c>
+      <c r="E81">
+        <v>110.655</v>
+      </c>
+      <c r="F81">
+        <v>343.255</v>
+      </c>
+      <c r="G81">
+        <v>314.8</v>
+      </c>
+      <c r="H81">
+        <v>201.9</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>52.2</v>
+      </c>
+      <c r="K81">
+        <v>23.1</v>
+      </c>
+      <c r="L81">
+        <v>29.1</v>
+      </c>
+      <c r="M81">
+        <v>81.969294</v>
+      </c>
+      <c r="N81">
+        <v>-52.869294</v>
+      </c>
+      <c r="O81">
+        <v>-8.723433510000001</v>
+      </c>
+      <c r="P81">
+        <v>-44.14586049</v>
+      </c>
+      <c r="Q81">
+        <v>-21.04586049</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.1492827914308025</v>
+      </c>
+      <c r="T81">
+        <v>2.017342409591005</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.05857681292216571</v>
+      </c>
+      <c r="W81">
+        <v>0.2248118570741868</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3550109874070649</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2109507532890761</v>
+      </c>
+      <c r="C82">
+        <v>-15.79188472152072</v>
+      </c>
+      <c r="D82">
+        <v>17.00811527847931</v>
+      </c>
+      <c r="E82">
+        <v>115</v>
+      </c>
+      <c r="F82">
+        <v>347.6</v>
+      </c>
+      <c r="G82">
+        <v>314.8</v>
+      </c>
+      <c r="H82">
+        <v>201.9</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>52.2</v>
+      </c>
+      <c r="K82">
+        <v>23.1</v>
+      </c>
+      <c r="L82">
+        <v>29.1</v>
+      </c>
+      <c r="M82">
+        <v>83.00688000000001</v>
+      </c>
+      <c r="N82">
+        <v>-53.90688000000001</v>
+      </c>
+      <c r="O82">
+        <v>-8.894635200000002</v>
+      </c>
+      <c r="P82">
+        <v>-45.0122448</v>
+      </c>
+      <c r="Q82">
+        <v>-21.9122448</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.1548069310023427</v>
+      </c>
+      <c r="T82">
+        <v>2.118209530070555</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.05784460276063863</v>
+      </c>
+      <c r="W82">
+        <v>0.2249867088607595</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3505733500644765</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2129507532890762</v>
+      </c>
+      <c r="C83">
+        <v>-20.33221106903579</v>
+      </c>
+      <c r="D83">
+        <v>16.81278893096422</v>
+      </c>
+      <c r="E83">
+        <v>119.3450000000001</v>
+      </c>
+      <c r="F83">
+        <v>351.9450000000001</v>
+      </c>
+      <c r="G83">
+        <v>314.8</v>
+      </c>
+      <c r="H83">
+        <v>201.9</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>52.2</v>
+      </c>
+      <c r="K83">
+        <v>23.1</v>
+      </c>
+      <c r="L83">
+        <v>29.1</v>
+      </c>
+      <c r="M83">
+        <v>84.04446600000001</v>
+      </c>
+      <c r="N83">
+        <v>-54.94446600000001</v>
+      </c>
+      <c r="O83">
+        <v>-9.065836890000002</v>
+      </c>
+      <c r="P83">
+        <v>-45.87862911000001</v>
+      </c>
+      <c r="Q83">
+        <v>-22.77862911000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.1609125589498344</v>
+      </c>
+      <c r="T83">
+        <v>2.229694242179532</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.05713047186235914</v>
+      </c>
+      <c r="W83">
+        <v>0.2251572433192687</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3462452840142978</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2149507532890761</v>
+      </c>
+      <c r="C84">
+        <v>-24.86810198056514</v>
+      </c>
+      <c r="D84">
+        <v>16.62189801943488</v>
+      </c>
+      <c r="E84">
+        <v>123.69</v>
+      </c>
+      <c r="F84">
+        <v>356.29</v>
+      </c>
+      <c r="G84">
+        <v>314.8</v>
+      </c>
+      <c r="H84">
+        <v>201.9</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>52.2</v>
+      </c>
+      <c r="K84">
+        <v>23.1</v>
+      </c>
+      <c r="L84">
+        <v>29.1</v>
+      </c>
+      <c r="M84">
+        <v>85.082052</v>
+      </c>
+      <c r="N84">
+        <v>-55.982052</v>
+      </c>
+      <c r="O84">
+        <v>-9.23703858</v>
+      </c>
+      <c r="P84">
+        <v>-46.74501342000001</v>
+      </c>
+      <c r="Q84">
+        <v>-23.64501342000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.167696590002603</v>
+      </c>
+      <c r="T84">
+        <v>2.35356614452284</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.05643375879086696</v>
+      </c>
+      <c r="W84">
+        <v>0.225323618400741</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3420227805507089</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2169507532890761</v>
+      </c>
+      <c r="C85">
+        <v>-29.39970683867051</v>
+      </c>
+      <c r="D85">
+        <v>16.43529316132953</v>
+      </c>
+      <c r="E85">
+        <v>128.0350000000001</v>
+      </c>
+      <c r="F85">
+        <v>360.635</v>
+      </c>
+      <c r="G85">
+        <v>314.8</v>
+      </c>
+      <c r="H85">
+        <v>201.9</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>52.2</v>
+      </c>
+      <c r="K85">
+        <v>23.1</v>
+      </c>
+      <c r="L85">
+        <v>29.1</v>
+      </c>
+      <c r="M85">
+        <v>86.11963800000001</v>
+      </c>
+      <c r="N85">
+        <v>-57.01963800000001</v>
+      </c>
+      <c r="O85">
+        <v>-9.408240270000002</v>
+      </c>
+      <c r="P85">
+        <v>-47.61139773000001</v>
+      </c>
+      <c r="Q85">
+        <v>-24.51139773000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.1752787423556973</v>
+      </c>
+      <c r="T85">
+        <v>2.492011211847712</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.05575383398615771</v>
+      </c>
+      <c r="W85">
+        <v>0.2254859844441055</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.3379020241585317</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2189507532890761</v>
+      </c>
+      <c r="C86">
+        <v>-33.92716839224443</v>
+      </c>
+      <c r="D86">
+        <v>16.25283160775551</v>
+      </c>
+      <c r="E86">
+        <v>132.38</v>
+      </c>
+      <c r="F86">
+        <v>364.98</v>
+      </c>
+      <c r="G86">
+        <v>314.8</v>
+      </c>
+      <c r="H86">
+        <v>201.9</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>52.2</v>
+      </c>
+      <c r="K86">
+        <v>23.1</v>
+      </c>
+      <c r="L86">
+        <v>29.1</v>
+      </c>
+      <c r="M86">
+        <v>87.157224</v>
+      </c>
+      <c r="N86">
+        <v>-58.057224</v>
+      </c>
+      <c r="O86">
+        <v>-9.57944196</v>
+      </c>
+      <c r="P86">
+        <v>-48.47778203999999</v>
+      </c>
+      <c r="Q86">
+        <v>-25.37778203999999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.1838086637529283</v>
+      </c>
+      <c r="T86">
+        <v>2.647761912588193</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.0550900978672749</v>
+      </c>
+      <c r="W86">
+        <v>0.2256444846292948</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3338793810137872</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2209507532890761</v>
+      </c>
+      <c r="C87">
+        <v>-38.45062312069638</v>
+      </c>
+      <c r="D87">
+        <v>16.07437687930361</v>
+      </c>
+      <c r="E87">
+        <v>136.725</v>
+      </c>
+      <c r="F87">
+        <v>369.325</v>
+      </c>
+      <c r="G87">
+        <v>314.8</v>
+      </c>
+      <c r="H87">
+        <v>201.9</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>52.2</v>
+      </c>
+      <c r="K87">
+        <v>23.1</v>
+      </c>
+      <c r="L87">
+        <v>29.1</v>
+      </c>
+      <c r="M87">
+        <v>88.19481</v>
+      </c>
+      <c r="N87">
+        <v>-59.09481</v>
+      </c>
+      <c r="O87">
+        <v>-9.750643650000001</v>
+      </c>
+      <c r="P87">
+        <v>-49.34416635</v>
+      </c>
+      <c r="Q87">
+        <v>-26.24416635</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.1934759080031235</v>
+      </c>
+      <c r="T87">
+        <v>2.824279373427406</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.05444197906883637</v>
+      </c>
+      <c r="W87">
+        <v>0.2257992553983619</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3299513882959779</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2229507532890761</v>
+      </c>
+      <c r="C88">
+        <v>-42.97020157440568</v>
+      </c>
+      <c r="D88">
+        <v>15.89979842559433</v>
+      </c>
+      <c r="E88">
+        <v>141.07</v>
+      </c>
+      <c r="F88">
+        <v>373.67</v>
+      </c>
+      <c r="G88">
+        <v>314.8</v>
+      </c>
+      <c r="H88">
+        <v>201.9</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>52.2</v>
+      </c>
+      <c r="K88">
+        <v>23.1</v>
+      </c>
+      <c r="L88">
+        <v>29.1</v>
+      </c>
+      <c r="M88">
+        <v>89.23239600000001</v>
+      </c>
+      <c r="N88">
+        <v>-60.13239600000001</v>
+      </c>
+      <c r="O88">
+        <v>-9.921845340000001</v>
+      </c>
+      <c r="P88">
+        <v>-50.21055066000001</v>
+      </c>
+      <c r="Q88">
+        <v>-27.11055066000001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.2045241871462038</v>
+      </c>
+      <c r="T88">
+        <v>3.026013614386507</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.05380893280059408</v>
+      </c>
+      <c r="W88">
+        <v>0.2259504268472181</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3261147442460247</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2249507532890762</v>
+      </c>
+      <c r="C89">
+        <v>-47.48602869322912</v>
+      </c>
+      <c r="D89">
+        <v>15.72897130677084</v>
+      </c>
+      <c r="E89">
+        <v>145.415</v>
+      </c>
+      <c r="F89">
+        <v>378.015</v>
+      </c>
+      <c r="G89">
+        <v>314.8</v>
+      </c>
+      <c r="H89">
+        <v>201.9</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>52.2</v>
+      </c>
+      <c r="K89">
+        <v>23.1</v>
+      </c>
+      <c r="L89">
+        <v>29.1</v>
+      </c>
+      <c r="M89">
+        <v>90.269982</v>
+      </c>
+      <c r="N89">
+        <v>-61.169982</v>
+      </c>
+      <c r="O89">
+        <v>-10.09304703</v>
+      </c>
+      <c r="P89">
+        <v>-51.07693497</v>
+      </c>
+      <c r="Q89">
+        <v>-27.97693496999999</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.2172722015420656</v>
+      </c>
+      <c r="T89">
+        <v>3.258783892416238</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.05319043932012749</v>
+      </c>
+      <c r="W89">
+        <v>0.2260981230903536</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.3223662989098636</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2269507532890761</v>
+      </c>
+      <c r="C90">
+        <v>-51.99822410469375</v>
+      </c>
+      <c r="D90">
+        <v>15.56177589530627</v>
+      </c>
+      <c r="E90">
+        <v>149.76</v>
+      </c>
+      <c r="F90">
+        <v>382.36</v>
+      </c>
+      <c r="G90">
+        <v>314.8</v>
+      </c>
+      <c r="H90">
+        <v>201.9</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>52.2</v>
+      </c>
+      <c r="K90">
+        <v>23.1</v>
+      </c>
+      <c r="L90">
+        <v>29.1</v>
+      </c>
+      <c r="M90">
+        <v>91.307568</v>
+      </c>
+      <c r="N90">
+        <v>-62.207568</v>
+      </c>
+      <c r="O90">
+        <v>-10.26424872</v>
+      </c>
+      <c r="P90">
+        <v>-51.94331928</v>
+      </c>
+      <c r="Q90">
+        <v>-28.84331928</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.2321448850039045</v>
+      </c>
+      <c r="T90">
+        <v>3.530349216784259</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.05258600250967149</v>
+      </c>
+      <c r="W90">
+        <v>0.2262424626006904</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3187030455131605</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2289507532890761</v>
+      </c>
+      <c r="C91">
+        <v>-56.50690240337127</v>
+      </c>
+      <c r="D91">
+        <v>15.39809759662869</v>
+      </c>
+      <c r="E91">
+        <v>154.105</v>
+      </c>
+      <c r="F91">
+        <v>386.705</v>
+      </c>
+      <c r="G91">
+        <v>314.8</v>
+      </c>
+      <c r="H91">
+        <v>201.9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>52.2</v>
+      </c>
+      <c r="K91">
+        <v>23.1</v>
+      </c>
+      <c r="L91">
+        <v>29.1</v>
+      </c>
+      <c r="M91">
+        <v>92.34515400000001</v>
+      </c>
+      <c r="N91">
+        <v>-63.24515400000001</v>
+      </c>
+      <c r="O91">
+        <v>-10.43545041</v>
+      </c>
+      <c r="P91">
+        <v>-52.80970359000001</v>
+      </c>
+      <c r="Q91">
+        <v>-29.70970359</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.2497216927315321</v>
+      </c>
+      <c r="T91">
+        <v>3.851290054673736</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.05199514854888866</v>
+      </c>
+      <c r="W91">
+        <v>0.2263835585265254</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.315122112417507</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2309507532890762</v>
+      </c>
+      <c r="C92">
+        <v>-61.01217341280591</v>
+      </c>
+      <c r="D92">
+        <v>15.2378265871941</v>
+      </c>
+      <c r="E92">
+        <v>158.45</v>
+      </c>
+      <c r="F92">
+        <v>391.05</v>
+      </c>
+      <c r="G92">
+        <v>314.8</v>
+      </c>
+      <c r="H92">
+        <v>201.9</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>52.2</v>
+      </c>
+      <c r="K92">
+        <v>23.1</v>
+      </c>
+      <c r="L92">
+        <v>29.1</v>
+      </c>
+      <c r="M92">
+        <v>93.38274000000001</v>
+      </c>
+      <c r="N92">
+        <v>-64.28274000000002</v>
+      </c>
+      <c r="O92">
+        <v>-10.6066521</v>
+      </c>
+      <c r="P92">
+        <v>-53.67608790000001</v>
+      </c>
+      <c r="Q92">
+        <v>-30.57608790000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.2708138620046854</v>
+      </c>
+      <c r="T92">
+        <v>4.236419060141111</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.05141742467612323</v>
+      </c>
+      <c r="W92">
+        <v>0.2265215189873418</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.311620755612868</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2329507532890762</v>
+      </c>
+      <c r="C93">
+        <v>-65.5141424312522</v>
+      </c>
+      <c r="D93">
+        <v>15.08085756874784</v>
+      </c>
+      <c r="E93">
+        <v>162.795</v>
+      </c>
+      <c r="F93">
+        <v>395.395</v>
+      </c>
+      <c r="G93">
+        <v>314.8</v>
+      </c>
+      <c r="H93">
+        <v>201.9</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>52.2</v>
+      </c>
+      <c r="K93">
+        <v>23.1</v>
+      </c>
+      <c r="L93">
+        <v>29.1</v>
+      </c>
+      <c r="M93">
+        <v>94.42032600000002</v>
+      </c>
+      <c r="N93">
+        <v>-65.32032600000002</v>
+      </c>
+      <c r="O93">
+        <v>-10.77785379</v>
+      </c>
+      <c r="P93">
+        <v>-54.54247221000002</v>
+      </c>
+      <c r="Q93">
+        <v>-31.44247221000002</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.296593180005206</v>
+      </c>
+      <c r="T93">
+        <v>4.707132289045679</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.05085239803133067</v>
+      </c>
+      <c r="W93">
+        <v>0.2266564473501183</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.3081963517050342</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2349507532890762</v>
+      </c>
+      <c r="C94">
+        <v>-70.01291046237998</v>
+      </c>
+      <c r="D94">
+        <v>14.92708953762004</v>
+      </c>
+      <c r="E94">
+        <v>167.14</v>
+      </c>
+      <c r="F94">
+        <v>399.74</v>
+      </c>
+      <c r="G94">
+        <v>314.8</v>
+      </c>
+      <c r="H94">
+        <v>201.9</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>52.2</v>
+      </c>
+      <c r="K94">
+        <v>23.1</v>
+      </c>
+      <c r="L94">
+        <v>29.1</v>
+      </c>
+      <c r="M94">
+        <v>95.45791200000001</v>
+      </c>
+      <c r="N94">
+        <v>-66.357912</v>
+      </c>
+      <c r="O94">
+        <v>-10.94905548</v>
+      </c>
+      <c r="P94">
+        <v>-55.40885652</v>
+      </c>
+      <c r="Q94">
+        <v>-32.30885652</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.3288173275058568</v>
+      </c>
+      <c r="T94">
+        <v>5.295523825176391</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.05029965457446838</v>
+      </c>
+      <c r="W94">
+        <v>0.226788442487617</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3048463913604145</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2369507532890761</v>
+      </c>
+      <c r="C95">
+        <v>-74.50857443200761</v>
+      </c>
+      <c r="D95">
+        <v>14.7764255679924</v>
+      </c>
+      <c r="E95">
+        <v>171.485</v>
+      </c>
+      <c r="F95">
+        <v>404.085</v>
+      </c>
+      <c r="G95">
+        <v>314.8</v>
+      </c>
+      <c r="H95">
+        <v>201.9</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>52.2</v>
+      </c>
+      <c r="K95">
+        <v>23.1</v>
+      </c>
+      <c r="L95">
+        <v>29.1</v>
+      </c>
+      <c r="M95">
+        <v>96.49549800000001</v>
+      </c>
+      <c r="N95">
+        <v>-67.395498</v>
+      </c>
+      <c r="O95">
+        <v>-11.12025717</v>
+      </c>
+      <c r="P95">
+        <v>-56.27524083</v>
+      </c>
+      <c r="Q95">
+        <v>-33.17524083</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.3702483742924078</v>
+      </c>
+      <c r="T95">
+        <v>6.052027228773018</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.04975879807366765</v>
+      </c>
+      <c r="W95">
+        <v>0.2269175990200082</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3015684731737434</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2389507532890761</v>
+      </c>
+      <c r="C96">
+        <v>-79.00122739184081</v>
+      </c>
+      <c r="D96">
+        <v>14.62877260815917</v>
+      </c>
+      <c r="E96">
+        <v>175.83</v>
+      </c>
+      <c r="F96">
+        <v>408.43</v>
+      </c>
+      <c r="G96">
+        <v>314.8</v>
+      </c>
+      <c r="H96">
+        <v>201.9</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>52.2</v>
+      </c>
+      <c r="K96">
+        <v>23.1</v>
+      </c>
+      <c r="L96">
+        <v>29.1</v>
+      </c>
+      <c r="M96">
+        <v>97.533084</v>
+      </c>
+      <c r="N96">
+        <v>-68.43308400000001</v>
+      </c>
+      <c r="O96">
+        <v>-11.29145886</v>
+      </c>
+      <c r="P96">
+        <v>-57.14162514</v>
+      </c>
+      <c r="Q96">
+        <v>-34.04162514</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.4254897700078092</v>
+      </c>
+      <c r="T96">
+        <v>7.060698433568524</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.04922944915799034</v>
+      </c>
+      <c r="W96">
+        <v>0.2270440075410719</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2983602979272141</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2409507532890761</v>
+      </c>
+      <c r="C97">
+        <v>-83.49095871111763</v>
+      </c>
+      <c r="D97">
+        <v>14.48404128888239</v>
+      </c>
+      <c r="E97">
+        <v>180.175</v>
+      </c>
+      <c r="F97">
+        <v>412.775</v>
+      </c>
+      <c r="G97">
+        <v>314.8</v>
+      </c>
+      <c r="H97">
+        <v>201.9</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>52.2</v>
+      </c>
+      <c r="K97">
+        <v>23.1</v>
+      </c>
+      <c r="L97">
+        <v>29.1</v>
+      </c>
+      <c r="M97">
+        <v>98.57067000000001</v>
+      </c>
+      <c r="N97">
+        <v>-69.47067000000001</v>
+      </c>
+      <c r="O97">
+        <v>-11.46266055</v>
+      </c>
+      <c r="P97">
+        <v>-58.00800945000001</v>
+      </c>
+      <c r="Q97">
+        <v>-34.90800945000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.5028277240093713</v>
+      </c>
+      <c r="T97">
+        <v>8.472838120282232</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.04871124443001148</v>
+      </c>
+      <c r="W97">
+        <v>0.2271677548301133</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2952196632121907</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2429507532890761</v>
+      </c>
+      <c r="C98">
+        <v>-87.97785425698777</v>
+      </c>
+      <c r="D98">
+        <v>14.34214574301221</v>
+      </c>
+      <c r="E98">
+        <v>184.52</v>
+      </c>
+      <c r="F98">
+        <v>417.12</v>
+      </c>
+      <c r="G98">
+        <v>314.8</v>
+      </c>
+      <c r="H98">
+        <v>201.9</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>52.2</v>
+      </c>
+      <c r="K98">
+        <v>23.1</v>
+      </c>
+      <c r="L98">
+        <v>29.1</v>
+      </c>
+      <c r="M98">
+        <v>99.60825600000001</v>
+      </c>
+      <c r="N98">
+        <v>-70.50825600000002</v>
+      </c>
+      <c r="O98">
+        <v>-11.63386224</v>
+      </c>
+      <c r="P98">
+        <v>-58.87439376000002</v>
+      </c>
+      <c r="Q98">
+        <v>-35.77439376000002</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>0.6188346550117128</v>
+      </c>
+      <c r="T98">
+        <v>10.59104765035277</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.04820383563386553</v>
+      </c>
+      <c r="W98">
+        <v>0.2272889240506329</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2921444583870637</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2449507532890761</v>
+      </c>
+      <c r="C99">
+        <v>-92.46199656439325</v>
+      </c>
+      <c r="D99">
+        <v>14.2030034356067</v>
+      </c>
+      <c r="E99">
+        <v>188.865</v>
+      </c>
+      <c r="F99">
+        <v>421.465</v>
+      </c>
+      <c r="G99">
+        <v>314.8</v>
+      </c>
+      <c r="H99">
+        <v>201.9</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>52.2</v>
+      </c>
+      <c r="K99">
+        <v>23.1</v>
+      </c>
+      <c r="L99">
+        <v>29.1</v>
+      </c>
+      <c r="M99">
+        <v>100.645842</v>
+      </c>
+      <c r="N99">
+        <v>-71.54584199999999</v>
+      </c>
+      <c r="O99">
+        <v>-11.80506393</v>
+      </c>
+      <c r="P99">
+        <v>-59.74077806999999</v>
+      </c>
+      <c r="Q99">
+        <v>-36.64077806999999</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>0.8121795400156171</v>
+      </c>
+      <c r="T99">
+        <v>14.12139686713702</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.04770688887475352</v>
+      </c>
+      <c r="W99">
+        <v>0.2274075949367089</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2891326598469911</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2469507532890761</v>
+      </c>
+      <c r="C100">
+        <v>-96.9434649961542</v>
+      </c>
+      <c r="D100">
+        <v>14.06653500384578</v>
+      </c>
+      <c r="E100">
+        <v>193.21</v>
+      </c>
+      <c r="F100">
+        <v>425.81</v>
+      </c>
+      <c r="G100">
+        <v>314.8</v>
+      </c>
+      <c r="H100">
+        <v>201.9</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>52.2</v>
+      </c>
+      <c r="K100">
+        <v>23.1</v>
+      </c>
+      <c r="L100">
+        <v>29.1</v>
+      </c>
+      <c r="M100">
+        <v>101.683428</v>
+      </c>
+      <c r="N100">
+        <v>-72.583428</v>
+      </c>
+      <c r="O100">
+        <v>-11.97626562</v>
+      </c>
+      <c r="P100">
+        <v>-60.60716238</v>
+      </c>
+      <c r="Q100">
+        <v>-37.50716238</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>1.198869310023426</v>
+      </c>
+      <c r="T100">
+        <v>21.18209530070553</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.04722008388623562</v>
+      </c>
+      <c r="W100">
+        <v>0.2275238439679669</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2861823265832463</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2489507532890761</v>
+      </c>
+      <c r="C101">
+        <v>-101.4223358939139</v>
+      </c>
+      <c r="D101">
+        <v>13.93266410608605</v>
+      </c>
+      <c r="E101">
+        <v>197.555</v>
+      </c>
+      <c r="F101">
+        <v>430.155</v>
+      </c>
+      <c r="G101">
+        <v>314.8</v>
+      </c>
+      <c r="H101">
+        <v>201.9</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>52.2</v>
+      </c>
+      <c r="K101">
+        <v>23.1</v>
+      </c>
+      <c r="L101">
+        <v>29.1</v>
+      </c>
+      <c r="M101">
+        <v>102.721014</v>
+      </c>
+      <c r="N101">
+        <v>-73.621014</v>
+      </c>
+      <c r="O101">
+        <v>-12.14746731</v>
+      </c>
+      <c r="P101">
+        <v>-61.47354669</v>
+      </c>
+      <c r="Q101">
+        <v>-38.37354669</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>2.358938620046851</v>
+      </c>
+      <c r="T101">
+        <v>42.36419060141106</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.04674311334193022</v>
+      </c>
+      <c r="W101">
+        <v>0.2276377445339471</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2832915960116982</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/hong_kong/hong_kong_utility_general.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_utility_general.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06858886757103588</v>
+        <v>0.06851327093954368</v>
       </c>
       <c r="C2">
-        <v>524.8538341094188</v>
+        <v>519.7028517888494</v>
       </c>
       <c r="D2">
-        <v>32.15383410941882</v>
+        <v>32.26085178884954</v>
       </c>
       <c r="E2">
-        <v>-253.7</v>
+        <v>-248.442</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.258</v>
       </c>
       <c r="G2">
         <v>492.7</v>
@@ -1451,28 +1451,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2644774</v>
       </c>
       <c r="N2">
-        <v>37.03333333333333</v>
+        <v>36.76885593333333</v>
       </c>
       <c r="O2">
-        <v>6.1105</v>
+        <v>6.066861229000001</v>
       </c>
       <c r="P2">
-        <v>30.92283333333333</v>
+        <v>30.70199470433333</v>
       </c>
       <c r="Q2">
-        <v>55.72283333333333</v>
+        <v>55.50199470433333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06858886757103588</v>
+        <v>0.06878107670660978</v>
       </c>
       <c r="T2">
-        <v>0.4441974458563936</v>
+        <v>0.4479439596674046</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>140.0245666863533</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06851327093954368</v>
+        <v>0.06843767430805146</v>
       </c>
       <c r="C3">
-        <v>519.7028517888494</v>
+        <v>514.5525842215685</v>
       </c>
       <c r="D3">
-        <v>32.26085178884954</v>
+        <v>32.36858422156853</v>
       </c>
       <c r="E3">
-        <v>-248.442</v>
+        <v>-243.184</v>
       </c>
       <c r="F3">
-        <v>5.258</v>
+        <v>10.516</v>
       </c>
       <c r="G3">
         <v>492.7</v>
@@ -1533,28 +1533,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M3">
-        <v>0.2644774</v>
+        <v>0.5289547999999999</v>
       </c>
       <c r="N3">
-        <v>36.76885593333333</v>
+        <v>36.50437853333333</v>
       </c>
       <c r="O3">
-        <v>6.066861229000001</v>
+        <v>6.023222458</v>
       </c>
       <c r="P3">
-        <v>30.70199470433333</v>
+        <v>30.48115607533333</v>
       </c>
       <c r="Q3">
-        <v>55.50199470433333</v>
+        <v>55.28115607533333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06878107670660978</v>
+        <v>0.06897720847760354</v>
       </c>
       <c r="T3">
-        <v>0.4479439596674046</v>
+        <v>0.4517669329439464</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>140.0245666863533</v>
+        <v>70.01228334317665</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06843767430805146</v>
+        <v>0.06836207767655926</v>
       </c>
       <c r="C4">
-        <v>514.5525842215685</v>
+        <v>509.4030385921455</v>
       </c>
       <c r="D4">
-        <v>32.36858422156853</v>
+        <v>32.4770385921456</v>
       </c>
       <c r="E4">
-        <v>-243.184</v>
+        <v>-237.926</v>
       </c>
       <c r="F4">
-        <v>10.516</v>
+        <v>15.774</v>
       </c>
       <c r="G4">
         <v>492.7</v>
@@ -1615,28 +1615,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M4">
-        <v>0.5289547999999999</v>
+        <v>0.7934321999999998</v>
       </c>
       <c r="N4">
-        <v>36.50437853333333</v>
+        <v>36.23990113333333</v>
       </c>
       <c r="O4">
-        <v>6.023222458</v>
+        <v>5.979583687</v>
       </c>
       <c r="P4">
-        <v>30.48115607533333</v>
+        <v>30.26031744633333</v>
       </c>
       <c r="Q4">
-        <v>55.28115607533333</v>
+        <v>55.06031744633333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06897720847760354</v>
+        <v>0.06917738420263841</v>
       </c>
       <c r="T4">
-        <v>0.4517669329439464</v>
+        <v>0.4556687304117573</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>70.01228334317665</v>
+        <v>46.67485556211778</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06836207767655926</v>
+        <v>0.06828648104506706</v>
       </c>
       <c r="C5">
-        <v>509.4030385921455</v>
+        <v>504.254222181765</v>
       </c>
       <c r="D5">
-        <v>32.4770385921456</v>
+        <v>32.58622218176498</v>
       </c>
       <c r="E5">
-        <v>-237.926</v>
+        <v>-232.668</v>
       </c>
       <c r="F5">
-        <v>15.774</v>
+        <v>21.032</v>
       </c>
       <c r="G5">
         <v>492.7</v>
@@ -1697,28 +1697,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M5">
-        <v>0.7934321999999998</v>
+        <v>1.0579096</v>
       </c>
       <c r="N5">
-        <v>36.23990113333333</v>
+        <v>35.97542373333333</v>
       </c>
       <c r="O5">
-        <v>5.979583687</v>
+        <v>5.935944916</v>
       </c>
       <c r="P5">
-        <v>30.26031744633333</v>
+        <v>30.03947881733333</v>
       </c>
       <c r="Q5">
-        <v>55.06031744633333</v>
+        <v>54.83947881733333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06917738420263841</v>
+        <v>0.06938173025527818</v>
       </c>
       <c r="T5">
-        <v>0.4556687304117573</v>
+        <v>0.459651815326814</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>46.67485556211778</v>
+        <v>35.00614167158832</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06828648104506706</v>
+        <v>0.06821088441357484</v>
       </c>
       <c r="C6">
-        <v>504.254222181765</v>
+        <v>499.1061423698547</v>
       </c>
       <c r="D6">
-        <v>32.58622218176498</v>
+        <v>32.69614236985475</v>
       </c>
       <c r="E6">
-        <v>-232.668</v>
+        <v>-227.41</v>
       </c>
       <c r="F6">
-        <v>21.032</v>
+        <v>26.29</v>
       </c>
       <c r="G6">
         <v>492.7</v>
@@ -1779,28 +1779,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M6">
-        <v>1.0579096</v>
+        <v>1.322387</v>
       </c>
       <c r="N6">
-        <v>35.97542373333333</v>
+        <v>35.71094633333333</v>
       </c>
       <c r="O6">
-        <v>5.935944916</v>
+        <v>5.892306145</v>
       </c>
       <c r="P6">
-        <v>30.03947881733333</v>
+        <v>29.81864018833333</v>
       </c>
       <c r="Q6">
-        <v>54.83947881733333</v>
+        <v>54.61864018833333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06938173025527818</v>
+        <v>0.06959037833007878</v>
       </c>
       <c r="T6">
-        <v>0.459651815326814</v>
+        <v>0.4637187546611352</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>35.00614167158832</v>
+        <v>28.00491333727066</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06821088441357484</v>
+        <v>0.06813528778208264</v>
       </c>
       <c r="C7">
-        <v>499.1061423698547</v>
+        <v>493.9588066357494</v>
       </c>
       <c r="D7">
-        <v>32.69614236985475</v>
+        <v>32.80680663574943</v>
       </c>
       <c r="E7">
-        <v>-227.41</v>
+        <v>-222.152</v>
       </c>
       <c r="F7">
-        <v>26.29</v>
+        <v>31.548</v>
       </c>
       <c r="G7">
         <v>492.7</v>
@@ -1861,28 +1861,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M7">
-        <v>1.322387</v>
+        <v>1.5868644</v>
       </c>
       <c r="N7">
-        <v>35.71094633333333</v>
+        <v>35.44646893333333</v>
       </c>
       <c r="O7">
-        <v>5.892306145</v>
+        <v>5.848667374</v>
       </c>
       <c r="P7">
-        <v>29.81864018833333</v>
+        <v>29.59780155933333</v>
       </c>
       <c r="Q7">
-        <v>54.61864018833333</v>
+        <v>54.39780155933333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06959037833007878</v>
+        <v>0.06980346572561982</v>
       </c>
       <c r="T7">
-        <v>0.4637187546611352</v>
+        <v>0.4678722246195908</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.00491333727066</v>
+        <v>23.33742778105888</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06813528778208264</v>
+        <v>0.06805969115059042</v>
       </c>
       <c r="C8">
-        <v>493.9588066357494</v>
+        <v>488.8122225603865</v>
       </c>
       <c r="D8">
-        <v>32.80680663574943</v>
+        <v>32.91822256038652</v>
       </c>
       <c r="E8">
-        <v>-222.152</v>
+        <v>-216.894</v>
       </c>
       <c r="F8">
-        <v>31.54799999999999</v>
+        <v>36.80599999999999</v>
       </c>
       <c r="G8">
         <v>492.7</v>
@@ -1943,28 +1943,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M8">
-        <v>1.5868644</v>
+        <v>1.851341799999999</v>
       </c>
       <c r="N8">
-        <v>35.44646893333334</v>
+        <v>35.18199153333333</v>
       </c>
       <c r="O8">
-        <v>5.848667374000001</v>
+        <v>5.805028603</v>
       </c>
       <c r="P8">
-        <v>29.59780155933333</v>
+        <v>29.37696293033333</v>
       </c>
       <c r="Q8">
-        <v>54.39780155933333</v>
+        <v>54.17696293033333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06980346572561982</v>
+        <v>0.07002113564579615</v>
       </c>
       <c r="T8">
-        <v>0.4678722246195908</v>
+        <v>0.4721150165126368</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.33742778105889</v>
+        <v>20.0035095266219</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06805969115059041</v>
+        <v>0.06798409451909822</v>
       </c>
       <c r="C9">
-        <v>488.8122225603866</v>
+        <v>483.6663978280375</v>
       </c>
       <c r="D9">
-        <v>32.91822256038655</v>
+        <v>33.03039782803756</v>
       </c>
       <c r="E9">
-        <v>-216.894</v>
+        <v>-211.636</v>
       </c>
       <c r="F9">
-        <v>36.806</v>
+        <v>42.064</v>
       </c>
       <c r="G9">
         <v>492.7</v>
@@ -2025,28 +2025,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M9">
-        <v>1.8513418</v>
+        <v>2.1158192</v>
       </c>
       <c r="N9">
-        <v>35.18199153333333</v>
+        <v>34.91751413333333</v>
       </c>
       <c r="O9">
-        <v>5.805028603</v>
+        <v>5.761389832000001</v>
       </c>
       <c r="P9">
-        <v>29.37696293033333</v>
+        <v>29.15612430133334</v>
       </c>
       <c r="Q9">
-        <v>54.17696293033333</v>
+        <v>53.95612430133333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07002113564579615</v>
+        <v>0.07024353752075893</v>
       </c>
       <c r="T9">
-        <v>0.4721150165126369</v>
+        <v>0.4764500430120535</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.0035095266219</v>
+        <v>17.50307083579416</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06798409451909822</v>
+        <v>0.067908497887606</v>
       </c>
       <c r="C10">
-        <v>483.6663978280375</v>
+        <v>478.5213402280749</v>
       </c>
       <c r="D10">
-        <v>33.03039782803756</v>
+        <v>33.14334022807494</v>
       </c>
       <c r="E10">
-        <v>-211.636</v>
+        <v>-206.378</v>
       </c>
       <c r="F10">
-        <v>42.064</v>
+        <v>47.322</v>
       </c>
       <c r="G10">
         <v>492.7</v>
@@ -2107,28 +2107,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M10">
-        <v>2.1158192</v>
+        <v>2.3802966</v>
       </c>
       <c r="N10">
-        <v>34.91751413333333</v>
+        <v>34.65303673333333</v>
       </c>
       <c r="O10">
-        <v>5.761389832000001</v>
+        <v>5.717751061</v>
       </c>
       <c r="P10">
-        <v>29.15612430133334</v>
+        <v>28.93528567233333</v>
       </c>
       <c r="Q10">
-        <v>53.95612430133333</v>
+        <v>53.73528567233333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07024353752075893</v>
+        <v>0.07047082734901758</v>
       </c>
       <c r="T10">
-        <v>0.4764500430120535</v>
+        <v>0.4808803448191496</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.50307083579416</v>
+        <v>15.55828518737259</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.067908497887606</v>
+        <v>0.0678329012561138</v>
       </c>
       <c r="C11">
-        <v>478.5213402280749</v>
+        <v>473.3770576567748</v>
       </c>
       <c r="D11">
-        <v>33.14334022807494</v>
+        <v>33.25705765677477</v>
       </c>
       <c r="E11">
-        <v>-206.378</v>
+        <v>-201.12</v>
       </c>
       <c r="F11">
-        <v>47.322</v>
+        <v>52.57999999999999</v>
       </c>
       <c r="G11">
         <v>492.7</v>
@@ -2189,28 +2189,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M11">
-        <v>2.3802966</v>
+        <v>2.644774</v>
       </c>
       <c r="N11">
-        <v>34.65303673333333</v>
+        <v>34.38855933333333</v>
       </c>
       <c r="O11">
-        <v>5.717751061</v>
+        <v>5.67411229</v>
       </c>
       <c r="P11">
-        <v>28.93528567233333</v>
+        <v>28.71444704333333</v>
       </c>
       <c r="Q11">
-        <v>53.73528567233333</v>
+        <v>53.51444704333333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07047082734901758</v>
+        <v>0.07070316806234866</v>
       </c>
       <c r="T11">
-        <v>0.4808803448191496</v>
+        <v>0.4854090977775146</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.55828518737259</v>
+        <v>14.00245666863533</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0678329012561138</v>
+        <v>0.06789507962462159</v>
       </c>
       <c r="C12">
-        <v>473.3770576567748</v>
+        <v>468.0254680602854</v>
       </c>
       <c r="D12">
-        <v>33.25705765677477</v>
+        <v>33.16346806028545</v>
       </c>
       <c r="E12">
-        <v>-201.12</v>
+        <v>-195.862</v>
       </c>
       <c r="F12">
-        <v>52.58</v>
+        <v>57.83799999999999</v>
       </c>
       <c r="G12">
         <v>492.7</v>
@@ -2271,45 +2271,45 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M12">
-        <v>2.644774</v>
+        <v>2.9960084</v>
       </c>
       <c r="N12">
-        <v>34.38855933333333</v>
+        <v>34.03732493333333</v>
       </c>
       <c r="O12">
-        <v>5.67411229</v>
+        <v>5.616158614</v>
       </c>
       <c r="P12">
-        <v>28.71444704333333</v>
+        <v>28.42116631933333</v>
       </c>
       <c r="Q12">
-        <v>53.51444704333333</v>
+        <v>53.22116631933334</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07070316806234866</v>
+        <v>0.07094072991530515</v>
       </c>
       <c r="T12">
-        <v>0.4854090977775146</v>
+        <v>0.490039620465281</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.165</v>
       </c>
       <c r="W12">
-        <v>0.0420005</v>
+        <v>0.043253</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>14.00245666863533</v>
+        <v>12.36089102197889</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06789507962462159</v>
+        <v>0.06783200799312937</v>
       </c>
       <c r="C13">
-        <v>468.0254680602854</v>
+        <v>462.8624060267729</v>
       </c>
       <c r="D13">
-        <v>33.16346806028545</v>
+        <v>33.25840602677287</v>
       </c>
       <c r="E13">
-        <v>-195.862</v>
+        <v>-190.604</v>
       </c>
       <c r="F13">
-        <v>57.83799999999999</v>
+        <v>63.09599999999999</v>
       </c>
       <c r="G13">
         <v>492.7</v>
@@ -2353,28 +2353,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M13">
-        <v>2.9960084</v>
+        <v>3.268372799999999</v>
       </c>
       <c r="N13">
-        <v>34.03732493333333</v>
+        <v>33.76496053333333</v>
       </c>
       <c r="O13">
-        <v>5.616158614</v>
+        <v>5.571218488</v>
       </c>
       <c r="P13">
-        <v>28.42116631933333</v>
+        <v>28.19374204533333</v>
       </c>
       <c r="Q13">
-        <v>53.22116631933334</v>
+        <v>52.99374204533333</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07094072991530515</v>
+        <v>0.07118369090128338</v>
       </c>
       <c r="T13">
-        <v>0.490039620465281</v>
+        <v>0.4947753823050421</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.36089102197889</v>
+        <v>11.33081677014732</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06783200799312937</v>
+        <v>0.06776893636163717</v>
       </c>
       <c r="C14">
-        <v>462.8624060267729</v>
+        <v>457.6998891168237</v>
       </c>
       <c r="D14">
-        <v>33.25840602677287</v>
+        <v>33.35388911682368</v>
       </c>
       <c r="E14">
-        <v>-190.604</v>
+        <v>-185.346</v>
       </c>
       <c r="F14">
-        <v>63.09599999999999</v>
+        <v>68.354</v>
       </c>
       <c r="G14">
         <v>492.7</v>
@@ -2435,28 +2435,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M14">
-        <v>3.268372799999999</v>
+        <v>3.5407372</v>
       </c>
       <c r="N14">
-        <v>33.76496053333333</v>
+        <v>33.49259613333333</v>
       </c>
       <c r="O14">
-        <v>5.571218488</v>
+        <v>5.526278361999999</v>
       </c>
       <c r="P14">
-        <v>28.19374204533333</v>
+        <v>27.96631777133333</v>
       </c>
       <c r="Q14">
-        <v>52.99374204533333</v>
+        <v>52.76631777133333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07118369090128338</v>
+        <v>0.0714322371972841</v>
       </c>
       <c r="T14">
-        <v>0.4947753823050421</v>
+        <v>0.4996200122330735</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.33081677014732</v>
+        <v>10.45921548013598</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06776893636163717</v>
+        <v>0.06790459473014496</v>
       </c>
       <c r="C15">
-        <v>457.6998891168237</v>
+        <v>452.2371925713219</v>
       </c>
       <c r="D15">
-        <v>33.35388911682368</v>
+        <v>33.14919257132188</v>
       </c>
       <c r="E15">
-        <v>-185.346</v>
+        <v>-180.088</v>
       </c>
       <c r="F15">
-        <v>68.354</v>
+        <v>73.61199999999999</v>
       </c>
       <c r="G15">
         <v>492.7</v>
@@ -2517,45 +2517,45 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M15">
-        <v>3.5407372</v>
+        <v>3.938242</v>
       </c>
       <c r="N15">
-        <v>33.49259613333333</v>
+        <v>33.09509133333333</v>
       </c>
       <c r="O15">
-        <v>5.526278361999999</v>
+        <v>5.460690069999999</v>
       </c>
       <c r="P15">
-        <v>27.96631777133333</v>
+        <v>27.63440126333333</v>
       </c>
       <c r="Q15">
-        <v>52.76631777133333</v>
+        <v>52.43440126333333</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0714322371972841</v>
+        <v>0.07168656363970344</v>
       </c>
       <c r="T15">
-        <v>0.4996200122330735</v>
+        <v>0.5045773079733848</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.165</v>
       </c>
       <c r="W15">
-        <v>0.043253</v>
+        <v>0.0446725</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.45921548013598</v>
+        <v>9.403518964383938</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06790459473014496</v>
+        <v>0.06785571809865275</v>
       </c>
       <c r="C16">
-        <v>452.2371925713219</v>
+        <v>447.0526529257899</v>
       </c>
       <c r="D16">
-        <v>33.14919257132188</v>
+        <v>33.22265292578985</v>
       </c>
       <c r="E16">
-        <v>-180.088</v>
+        <v>-174.83</v>
       </c>
       <c r="F16">
-        <v>73.61199999999999</v>
+        <v>78.87</v>
       </c>
       <c r="G16">
         <v>492.7</v>
@@ -2599,28 +2599,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M16">
-        <v>3.938242</v>
+        <v>4.219545</v>
       </c>
       <c r="N16">
-        <v>33.09509133333333</v>
+        <v>32.81378833333333</v>
       </c>
       <c r="O16">
-        <v>5.460690069999999</v>
+        <v>5.414275075000001</v>
       </c>
       <c r="P16">
-        <v>27.63440126333333</v>
+        <v>27.39951325833334</v>
       </c>
       <c r="Q16">
-        <v>52.43440126333333</v>
+        <v>52.19951325833334</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07168656363970344</v>
+        <v>0.07194687423370912</v>
       </c>
       <c r="T16">
-        <v>0.5045773079733848</v>
+        <v>0.5096512459664093</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.403518964383938</v>
+        <v>8.776617700091677</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06785571809865275</v>
+        <v>0.06780684146716054</v>
       </c>
       <c r="C17">
-        <v>447.0526529257899</v>
+        <v>441.868439587391</v>
       </c>
       <c r="D17">
-        <v>33.22265292578985</v>
+        <v>33.29643958739099</v>
       </c>
       <c r="E17">
-        <v>-174.83</v>
+        <v>-169.572</v>
       </c>
       <c r="F17">
-        <v>78.86999999999999</v>
+        <v>84.128</v>
       </c>
       <c r="G17">
         <v>492.7</v>
@@ -2681,28 +2681,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M17">
-        <v>4.219544999999999</v>
+        <v>4.500848</v>
       </c>
       <c r="N17">
-        <v>32.81378833333333</v>
+        <v>32.53248533333333</v>
       </c>
       <c r="O17">
-        <v>5.414275075000001</v>
+        <v>5.367860080000001</v>
       </c>
       <c r="P17">
-        <v>27.39951325833334</v>
+        <v>27.16462525333333</v>
       </c>
       <c r="Q17">
-        <v>52.19951325833334</v>
+        <v>51.96462525333334</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07194687423370912</v>
+        <v>0.07221338269900064</v>
       </c>
       <c r="T17">
-        <v>0.5096512459664093</v>
+        <v>0.5148459920068867</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.776617700091679</v>
+        <v>8.228079093835948</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06780684146716054</v>
+        <v>0.06775796483566834</v>
       </c>
       <c r="C18">
-        <v>441.868439587391</v>
+        <v>436.6845547351242</v>
       </c>
       <c r="D18">
-        <v>33.29643958739099</v>
+        <v>33.37055473512415</v>
       </c>
       <c r="E18">
-        <v>-169.572</v>
+        <v>-164.314</v>
       </c>
       <c r="F18">
-        <v>84.128</v>
+        <v>89.386</v>
       </c>
       <c r="G18">
         <v>492.7</v>
@@ -2763,28 +2763,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M18">
-        <v>4.500848</v>
+        <v>4.782151</v>
       </c>
       <c r="N18">
-        <v>32.53248533333333</v>
+        <v>32.25118233333333</v>
       </c>
       <c r="O18">
-        <v>5.367860080000001</v>
+        <v>5.321445085</v>
       </c>
       <c r="P18">
-        <v>27.16462525333333</v>
+        <v>26.92973724833333</v>
       </c>
       <c r="Q18">
-        <v>51.96462525333334</v>
+        <v>51.72973724833334</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07221338269900064</v>
+        <v>0.07248631305502209</v>
       </c>
       <c r="T18">
-        <v>0.5148459920068867</v>
+        <v>0.5201659126507492</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.228079093835948</v>
+        <v>7.744074441257362</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06775796483566834</v>
+        <v>0.06782932820417613</v>
       </c>
       <c r="C19">
-        <v>436.6845547351242</v>
+        <v>431.3184517928646</v>
       </c>
       <c r="D19">
-        <v>33.37055473512415</v>
+        <v>33.26245179286464</v>
       </c>
       <c r="E19">
-        <v>-164.314</v>
+        <v>-159.056</v>
       </c>
       <c r="F19">
-        <v>89.386</v>
+        <v>94.64400000000001</v>
       </c>
       <c r="G19">
         <v>492.7</v>
@@ -2845,45 +2845,45 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M19">
-        <v>4.782151</v>
+        <v>5.1391692</v>
       </c>
       <c r="N19">
-        <v>32.25118233333333</v>
+        <v>31.89416413333333</v>
       </c>
       <c r="O19">
-        <v>5.321445085</v>
+        <v>5.262537082</v>
       </c>
       <c r="P19">
-        <v>26.92973724833333</v>
+        <v>26.63162705133333</v>
       </c>
       <c r="Q19">
-        <v>51.72973724833334</v>
+        <v>51.43162705133334</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07248631305502209</v>
+        <v>0.07276590024899528</v>
       </c>
       <c r="T19">
-        <v>0.5201659126507492</v>
+        <v>0.525615587456657</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.165</v>
       </c>
       <c r="W19">
-        <v>0.0446725</v>
+        <v>0.0453405</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.744074441257362</v>
+        <v>7.20609341551419</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06782932820417613</v>
+        <v>0.06778713157268391</v>
       </c>
       <c r="C20">
-        <v>431.3184517928646</v>
+        <v>426.1242874694827</v>
       </c>
       <c r="D20">
-        <v>33.26245179286464</v>
+        <v>33.32628746948264</v>
       </c>
       <c r="E20">
-        <v>-159.056</v>
+        <v>-153.798</v>
       </c>
       <c r="F20">
-        <v>94.64399999999999</v>
+        <v>99.90199999999999</v>
       </c>
       <c r="G20">
         <v>492.7</v>
@@ -2927,28 +2927,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M20">
-        <v>5.1391692</v>
+        <v>5.424678599999999</v>
       </c>
       <c r="N20">
-        <v>31.89416413333333</v>
+        <v>31.60865473333333</v>
       </c>
       <c r="O20">
-        <v>5.262537082000001</v>
+        <v>5.215428031</v>
       </c>
       <c r="P20">
-        <v>26.63162705133333</v>
+        <v>26.39322670233333</v>
       </c>
       <c r="Q20">
-        <v>51.43162705133334</v>
+        <v>51.19322670233333</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07276590024899528</v>
+        <v>0.07305239083047396</v>
       </c>
       <c r="T20">
-        <v>0.525615587456657</v>
+        <v>0.5311998221343157</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.206093415514192</v>
+        <v>6.826825341013445</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06778713157268391</v>
+        <v>0.0677449349411917</v>
       </c>
       <c r="C21">
-        <v>426.1242874694827</v>
+        <v>420.9303686378763</v>
       </c>
       <c r="D21">
-        <v>33.32628746948264</v>
+        <v>33.39036863787624</v>
       </c>
       <c r="E21">
-        <v>-153.798</v>
+        <v>-148.54</v>
       </c>
       <c r="F21">
-        <v>99.90199999999999</v>
+        <v>105.16</v>
       </c>
       <c r="G21">
         <v>492.7</v>
@@ -3009,28 +3009,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M21">
-        <v>5.424678599999999</v>
+        <v>5.710188</v>
       </c>
       <c r="N21">
-        <v>31.60865473333333</v>
+        <v>31.32314533333333</v>
       </c>
       <c r="O21">
-        <v>5.215428031</v>
+        <v>5.16831898</v>
       </c>
       <c r="P21">
-        <v>26.39322670233333</v>
+        <v>26.15482635333333</v>
       </c>
       <c r="Q21">
-        <v>51.19322670233333</v>
+        <v>50.95482635333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07305239083047396</v>
+        <v>0.07334604367648963</v>
       </c>
       <c r="T21">
-        <v>0.5311998221343157</v>
+        <v>0.5369236626789158</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.826825341013445</v>
+        <v>6.485484073962772</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0677449349411917</v>
+        <v>0.0677027383096995</v>
       </c>
       <c r="C22">
-        <v>420.9303686378763</v>
+        <v>415.736696716899</v>
       </c>
       <c r="D22">
-        <v>33.39036863787624</v>
+        <v>33.454696716899</v>
       </c>
       <c r="E22">
-        <v>-148.54</v>
+        <v>-143.282</v>
       </c>
       <c r="F22">
-        <v>105.16</v>
+        <v>110.418</v>
       </c>
       <c r="G22">
         <v>492.7</v>
@@ -3091,28 +3091,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M22">
-        <v>5.710188</v>
+        <v>5.9956974</v>
       </c>
       <c r="N22">
-        <v>31.32314533333333</v>
+        <v>31.03763593333333</v>
       </c>
       <c r="O22">
-        <v>5.16831898</v>
+        <v>5.121209929</v>
       </c>
       <c r="P22">
-        <v>26.15482635333333</v>
+        <v>25.91642600433333</v>
       </c>
       <c r="Q22">
-        <v>50.95482635333333</v>
+        <v>50.71642600433333</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07334604367648963</v>
+        <v>0.07364713077177151</v>
       </c>
       <c r="T22">
-        <v>0.5369236626789158</v>
+        <v>0.5427924105790755</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.485484073962772</v>
+        <v>6.176651499012164</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0677027383096995</v>
+        <v>0.0678442416782073</v>
       </c>
       <c r="C23">
-        <v>415.736696716899</v>
+        <v>410.2639489225792</v>
       </c>
       <c r="D23">
-        <v>33.454696716899</v>
+        <v>33.2399489225792</v>
       </c>
       <c r="E23">
-        <v>-143.282</v>
+        <v>-138.024</v>
       </c>
       <c r="F23">
-        <v>110.418</v>
+        <v>115.676</v>
       </c>
       <c r="G23">
         <v>492.7</v>
@@ -3173,45 +3173,45 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M23">
-        <v>5.9956974</v>
+        <v>6.396882799999999</v>
       </c>
       <c r="N23">
-        <v>31.03763593333333</v>
+        <v>30.63645053333333</v>
       </c>
       <c r="O23">
-        <v>5.121209929</v>
+        <v>5.055014338</v>
       </c>
       <c r="P23">
-        <v>25.91642600433333</v>
+        <v>25.58143619533333</v>
       </c>
       <c r="Q23">
-        <v>50.71642600433333</v>
+        <v>50.38143619533334</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07364713077177151</v>
+        <v>0.0739559380489837</v>
       </c>
       <c r="T23">
-        <v>0.5427924105790755</v>
+        <v>0.5488116391946238</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.165</v>
       </c>
       <c r="W23">
-        <v>0.0453405</v>
+        <v>0.0461755</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.176651499012164</v>
+        <v>5.789278073585049</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0678442416782073</v>
+        <v>0.06781039504671507</v>
       </c>
       <c r="C24">
-        <v>410.2639489225792</v>
+        <v>405.057063875292</v>
       </c>
       <c r="D24">
-        <v>33.2399489225792</v>
+        <v>33.29106387529199</v>
       </c>
       <c r="E24">
-        <v>-138.024</v>
+        <v>-132.766</v>
       </c>
       <c r="F24">
-        <v>115.676</v>
+        <v>120.934</v>
       </c>
       <c r="G24">
         <v>492.7</v>
@@ -3255,28 +3255,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M24">
-        <v>6.396882799999999</v>
+        <v>6.6876502</v>
       </c>
       <c r="N24">
-        <v>30.63645053333333</v>
+        <v>30.34568313333333</v>
       </c>
       <c r="O24">
-        <v>5.055014338</v>
+        <v>5.007037717</v>
       </c>
       <c r="P24">
-        <v>25.58143619533333</v>
+        <v>25.33864541633333</v>
       </c>
       <c r="Q24">
-        <v>50.38143619533334</v>
+        <v>50.13864541633333</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0739559380489837</v>
+        <v>0.07427276629443516</v>
       </c>
       <c r="T24">
-        <v>0.5488116391946238</v>
+        <v>0.5549872114105759</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.789278073585049</v>
+        <v>5.537570331255264</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06781039504671507</v>
+        <v>0.06777654841522288</v>
       </c>
       <c r="C25">
-        <v>405.057063875292</v>
+        <v>399.8503362748372</v>
       </c>
       <c r="D25">
-        <v>33.29106387529199</v>
+        <v>33.34233627483722</v>
       </c>
       <c r="E25">
-        <v>-132.766</v>
+        <v>-127.508</v>
       </c>
       <c r="F25">
-        <v>120.934</v>
+        <v>126.192</v>
       </c>
       <c r="G25">
         <v>492.7</v>
@@ -3337,28 +3337,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M25">
-        <v>6.6876502</v>
+        <v>6.9784176</v>
       </c>
       <c r="N25">
-        <v>30.34568313333333</v>
+        <v>30.05491573333333</v>
       </c>
       <c r="O25">
-        <v>5.007037717</v>
+        <v>4.959061096</v>
       </c>
       <c r="P25">
-        <v>25.33864541633333</v>
+        <v>25.09585463733333</v>
       </c>
       <c r="Q25">
-        <v>50.13864541633333</v>
+        <v>49.89585463733333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07427276629443516</v>
+        <v>0.07459793212529325</v>
       </c>
       <c r="T25">
-        <v>0.5549872114105759</v>
+        <v>0.5613252986848427</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.537570331255264</v>
+        <v>5.306838234119628</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06777654841522288</v>
+        <v>0.06774270178373065</v>
       </c>
       <c r="C26">
-        <v>399.8503362748372</v>
+        <v>394.6437668498004</v>
       </c>
       <c r="D26">
-        <v>33.34233627483722</v>
+        <v>33.39376684980045</v>
       </c>
       <c r="E26">
-        <v>-127.508</v>
+        <v>-122.25</v>
       </c>
       <c r="F26">
-        <v>126.192</v>
+        <v>131.45</v>
       </c>
       <c r="G26">
         <v>492.7</v>
@@ -3419,28 +3419,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M26">
-        <v>6.978417599999999</v>
+        <v>7.269184999999999</v>
       </c>
       <c r="N26">
-        <v>30.05491573333333</v>
+        <v>29.76414833333333</v>
       </c>
       <c r="O26">
-        <v>4.959061096</v>
+        <v>4.911084475</v>
       </c>
       <c r="P26">
-        <v>25.09585463733333</v>
+        <v>24.85306385833333</v>
       </c>
       <c r="Q26">
-        <v>49.89585463733333</v>
+        <v>49.65306385833333</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07459793212529325</v>
+        <v>0.07493176904497421</v>
       </c>
       <c r="T26">
-        <v>0.5613252986848427</v>
+        <v>0.5678324016197566</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.306838234119629</v>
+        <v>5.094564704754843</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06774270178373065</v>
+        <v>0.06770885515223844</v>
       </c>
       <c r="C27">
-        <v>394.6437668498004</v>
+        <v>389.4373563332695</v>
       </c>
       <c r="D27">
-        <v>33.39376684980045</v>
+        <v>33.44535633326949</v>
       </c>
       <c r="E27">
-        <v>-122.25</v>
+        <v>-116.992</v>
       </c>
       <c r="F27">
-        <v>131.45</v>
+        <v>136.708</v>
       </c>
       <c r="G27">
         <v>492.7</v>
@@ -3501,28 +3501,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M27">
-        <v>7.269184999999999</v>
+        <v>7.5599524</v>
       </c>
       <c r="N27">
-        <v>29.76414833333333</v>
+        <v>29.47338093333333</v>
       </c>
       <c r="O27">
-        <v>4.911084475</v>
+        <v>4.863107854</v>
       </c>
       <c r="P27">
-        <v>24.85306385833333</v>
+        <v>24.61027307933333</v>
       </c>
       <c r="Q27">
-        <v>49.65306385833333</v>
+        <v>49.41027307933334</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07493176904497421</v>
+        <v>0.07527462858410601</v>
       </c>
       <c r="T27">
-        <v>0.5678324016197566</v>
+        <v>0.5745153722015599</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.094564704754843</v>
+        <v>4.898619908418118</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06770885515223844</v>
+        <v>0.06767500852074625</v>
       </c>
       <c r="C28">
-        <v>389.4373563332695</v>
+        <v>384.2311054628693</v>
       </c>
       <c r="D28">
-        <v>33.44535633326949</v>
+        <v>33.49710546286931</v>
       </c>
       <c r="E28">
-        <v>-116.992</v>
+        <v>-111.734</v>
       </c>
       <c r="F28">
-        <v>136.708</v>
+        <v>141.966</v>
       </c>
       <c r="G28">
         <v>492.7</v>
@@ -3583,28 +3583,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M28">
-        <v>7.5599524</v>
+        <v>7.850719800000001</v>
       </c>
       <c r="N28">
-        <v>29.47338093333333</v>
+        <v>29.18261353333333</v>
       </c>
       <c r="O28">
-        <v>4.863107854</v>
+        <v>4.815131233</v>
       </c>
       <c r="P28">
-        <v>24.61027307933333</v>
+        <v>24.36748230033333</v>
       </c>
       <c r="Q28">
-        <v>49.41027307933334</v>
+        <v>49.16748230033333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07527462858410601</v>
+        <v>0.07562688153526882</v>
       </c>
       <c r="T28">
-        <v>0.5745153722015599</v>
+        <v>0.5813814378677963</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.898619908418118</v>
+        <v>4.717189541439669</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06767500852074625</v>
+        <v>0.06764116188925402</v>
       </c>
       <c r="C29">
-        <v>384.2311054628693</v>
+        <v>379.0250149807973</v>
       </c>
       <c r="D29">
-        <v>33.49710546286931</v>
+        <v>33.54901498079728</v>
       </c>
       <c r="E29">
-        <v>-111.734</v>
+        <v>-106.476</v>
       </c>
       <c r="F29">
-        <v>141.966</v>
+        <v>147.224</v>
       </c>
       <c r="G29">
         <v>492.7</v>
@@ -3665,28 +3665,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M29">
-        <v>7.850719800000001</v>
+        <v>8.1414872</v>
       </c>
       <c r="N29">
-        <v>29.18261353333333</v>
+        <v>28.89184613333333</v>
       </c>
       <c r="O29">
-        <v>4.815131233</v>
+        <v>4.767154612</v>
       </c>
       <c r="P29">
-        <v>24.36748230033333</v>
+        <v>24.12469152133333</v>
       </c>
       <c r="Q29">
-        <v>49.16748230033333</v>
+        <v>48.92469152133333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07562688153526882</v>
+        <v>0.07598891929063059</v>
       </c>
       <c r="T29">
-        <v>0.5813814378677963</v>
+        <v>0.5884382275803171</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.717189541439669</v>
+        <v>4.548718486388252</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06764116188925402</v>
+        <v>0.06821269025776182</v>
       </c>
       <c r="C30">
-        <v>379.0250149807973</v>
+        <v>372.9115079632772</v>
       </c>
       <c r="D30">
-        <v>33.54901498079728</v>
+        <v>32.69350796327723</v>
       </c>
       <c r="E30">
-        <v>-106.476</v>
+        <v>-101.218</v>
       </c>
       <c r="F30">
-        <v>147.224</v>
+        <v>152.482</v>
       </c>
       <c r="G30">
         <v>492.7</v>
@@ -3747,45 +3747,45 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M30">
-        <v>8.1414872</v>
+        <v>8.8134596</v>
       </c>
       <c r="N30">
-        <v>28.89184613333333</v>
+        <v>28.21987373333333</v>
       </c>
       <c r="O30">
-        <v>4.767154612</v>
+        <v>4.656279166</v>
       </c>
       <c r="P30">
-        <v>24.12469152133333</v>
+        <v>23.56359456733333</v>
       </c>
       <c r="Q30">
-        <v>48.92469152133333</v>
+        <v>48.36359456733333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07598891929063059</v>
+        <v>0.07636115529262229</v>
       </c>
       <c r="T30">
-        <v>0.5884382275803171</v>
+        <v>0.5956938001016412</v>
       </c>
       <c r="U30">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V30">
         <v>0.165</v>
       </c>
       <c r="W30">
-        <v>0.0461755</v>
+        <v>0.048263</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.548718486388252</v>
+        <v>4.201906517315099</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06821269025776182</v>
+        <v>0.06819971862626961</v>
       </c>
       <c r="C31">
-        <v>372.9115079632772</v>
+        <v>367.6724407072354</v>
       </c>
       <c r="D31">
-        <v>32.69350796327723</v>
+        <v>32.71244070723544</v>
       </c>
       <c r="E31">
-        <v>-101.218</v>
+        <v>-95.96000000000001</v>
       </c>
       <c r="F31">
-        <v>152.482</v>
+        <v>157.74</v>
       </c>
       <c r="G31">
         <v>492.7</v>
@@ -3829,28 +3829,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M31">
-        <v>8.8134596</v>
+        <v>9.117372</v>
       </c>
       <c r="N31">
-        <v>28.21987373333333</v>
+        <v>27.91596133333333</v>
       </c>
       <c r="O31">
-        <v>4.656279166</v>
+        <v>4.60613362</v>
       </c>
       <c r="P31">
-        <v>23.56359456733333</v>
+        <v>23.30982771333333</v>
       </c>
       <c r="Q31">
-        <v>48.36359456733333</v>
+        <v>48.10982771333333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07636115529262229</v>
+        <v>0.07674402660895659</v>
       </c>
       <c r="T31">
-        <v>0.5956938001016412</v>
+        <v>0.6031566746950031</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.201906517315099</v>
+        <v>4.061842966737929</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06819971862626961</v>
+        <v>0.0690927219947774</v>
       </c>
       <c r="C32">
-        <v>367.6724407072354</v>
+        <v>361.1603013348503</v>
       </c>
       <c r="D32">
-        <v>32.71244070723544</v>
+        <v>31.45830133485027</v>
       </c>
       <c r="E32">
-        <v>-95.96000000000001</v>
+        <v>-90.702</v>
       </c>
       <c r="F32">
-        <v>157.74</v>
+        <v>162.998</v>
       </c>
       <c r="G32">
         <v>492.7</v>
@@ -3911,45 +3911,45 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M32">
-        <v>9.117372</v>
+        <v>9.9917774</v>
       </c>
       <c r="N32">
-        <v>27.91596133333333</v>
+        <v>27.04155593333333</v>
       </c>
       <c r="O32">
-        <v>4.60613362</v>
+        <v>4.461856729</v>
       </c>
       <c r="P32">
-        <v>23.30982771333333</v>
+        <v>22.57969920433333</v>
       </c>
       <c r="Q32">
-        <v>48.10982771333333</v>
+        <v>47.37969920433333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07674402660895659</v>
+        <v>0.07713799564460494</v>
       </c>
       <c r="T32">
-        <v>0.6031566746950031</v>
+        <v>0.6108358644939698</v>
       </c>
       <c r="U32">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V32">
         <v>0.165</v>
       </c>
       <c r="W32">
-        <v>0.048263</v>
+        <v>0.05118549999999999</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.061842966737929</v>
+        <v>3.706380942126806</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0690927219947774</v>
+        <v>0.06910897536328518</v>
       </c>
       <c r="C33">
-        <v>361.1603013348503</v>
+        <v>355.8803654343546</v>
       </c>
       <c r="D33">
-        <v>31.45830133485027</v>
+        <v>31.43636543435462</v>
       </c>
       <c r="E33">
-        <v>-90.702</v>
+        <v>-85.44399999999999</v>
       </c>
       <c r="F33">
-        <v>162.998</v>
+        <v>168.256</v>
       </c>
       <c r="G33">
         <v>492.7</v>
@@ -3993,28 +3993,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M33">
-        <v>9.9917774</v>
+        <v>10.3140928</v>
       </c>
       <c r="N33">
-        <v>27.04155593333333</v>
+        <v>26.71924053333333</v>
       </c>
       <c r="O33">
-        <v>4.461856729</v>
+        <v>4.408674688</v>
       </c>
       <c r="P33">
-        <v>22.57969920433333</v>
+        <v>22.31056584533333</v>
       </c>
       <c r="Q33">
-        <v>47.37969920433333</v>
+        <v>47.11056584533333</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07713799564460494</v>
+        <v>0.07754355200483116</v>
       </c>
       <c r="T33">
-        <v>0.6108358644939698</v>
+        <v>0.6187409128164354</v>
       </c>
       <c r="U33">
         <v>0.0613</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.706380942126806</v>
+        <v>3.590556537685343</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06910897536328518</v>
+        <v>0.06989676873179299</v>
       </c>
       <c r="C34">
-        <v>355.8803654343546</v>
+        <v>349.5946193288572</v>
       </c>
       <c r="D34">
-        <v>31.43636543435462</v>
+        <v>30.4086193288572</v>
       </c>
       <c r="E34">
-        <v>-85.44399999999999</v>
+        <v>-80.18600000000001</v>
       </c>
       <c r="F34">
-        <v>168.256</v>
+        <v>173.514</v>
       </c>
       <c r="G34">
         <v>492.7</v>
@@ -4075,45 +4075,45 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M34">
-        <v>10.3140928</v>
+        <v>11.1222474</v>
       </c>
       <c r="N34">
-        <v>26.71924053333333</v>
+        <v>25.91108593333333</v>
       </c>
       <c r="O34">
-        <v>4.408674688</v>
+        <v>4.275329179</v>
       </c>
       <c r="P34">
-        <v>22.31056584533333</v>
+        <v>21.63575675433333</v>
       </c>
       <c r="Q34">
-        <v>47.11056584533333</v>
+        <v>46.43575675433333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07754355200483116</v>
+        <v>0.07796121452506416</v>
       </c>
       <c r="T34">
-        <v>0.6187409128164354</v>
+        <v>0.6268819327306164</v>
       </c>
       <c r="U34">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V34">
         <v>0.165</v>
       </c>
       <c r="W34">
-        <v>0.05118549999999999</v>
+        <v>0.0535235</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.590556537685343</v>
+        <v>3.329662792191921</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06989676873179299</v>
+        <v>0.06993640210030076</v>
       </c>
       <c r="C35">
-        <v>349.5946193288572</v>
+        <v>344.2866866168206</v>
       </c>
       <c r="D35">
-        <v>30.4086193288572</v>
+        <v>30.35868661682062</v>
       </c>
       <c r="E35">
-        <v>-80.18600000000001</v>
+        <v>-74.928</v>
       </c>
       <c r="F35">
-        <v>173.514</v>
+        <v>178.772</v>
       </c>
       <c r="G35">
         <v>492.7</v>
@@ -4157,28 +4157,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M35">
-        <v>11.1222474</v>
+        <v>11.4592852</v>
       </c>
       <c r="N35">
-        <v>25.91108593333333</v>
+        <v>25.57404813333333</v>
       </c>
       <c r="O35">
-        <v>4.275329179</v>
+        <v>4.219717942</v>
       </c>
       <c r="P35">
-        <v>21.63575675433333</v>
+        <v>21.35433019133333</v>
       </c>
       <c r="Q35">
-        <v>46.43575675433333</v>
+        <v>46.15433019133333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07796121452506416</v>
+        <v>0.0783915334853042</v>
       </c>
       <c r="T35">
-        <v>0.6268819327306164</v>
+        <v>0.6352696502179545</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.329662792191921</v>
+        <v>3.231731533598041</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06993640210030076</v>
+        <v>0.06997603546880857</v>
       </c>
       <c r="C36">
-        <v>344.2866866168206</v>
+        <v>338.9789176207563</v>
       </c>
       <c r="D36">
-        <v>30.35868661682062</v>
+        <v>30.30891762075632</v>
       </c>
       <c r="E36">
-        <v>-74.928</v>
+        <v>-69.66999999999999</v>
       </c>
       <c r="F36">
-        <v>178.772</v>
+        <v>184.03</v>
       </c>
       <c r="G36">
         <v>492.7</v>
@@ -4239,28 +4239,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M36">
-        <v>11.4592852</v>
+        <v>11.796323</v>
       </c>
       <c r="N36">
-        <v>25.57404813333333</v>
+        <v>25.23701033333333</v>
       </c>
       <c r="O36">
-        <v>4.219717942</v>
+        <v>4.164106705</v>
       </c>
       <c r="P36">
-        <v>21.35433019133333</v>
+        <v>21.07290362833333</v>
       </c>
       <c r="Q36">
-        <v>46.15433019133333</v>
+        <v>45.87290362833333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.0783915334853042</v>
+        <v>0.07883509302893627</v>
       </c>
       <c r="T36">
-        <v>0.6352696502179545</v>
+        <v>0.6439154513202876</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.231731533598041</v>
+        <v>3.139396346923811</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06997603546880857</v>
+        <v>0.07001566883731636</v>
       </c>
       <c r="C37">
-        <v>338.9789176207563</v>
+        <v>333.671311536811</v>
       </c>
       <c r="D37">
-        <v>30.30891762075632</v>
+        <v>30.25931153681102</v>
       </c>
       <c r="E37">
-        <v>-69.66999999999999</v>
+        <v>-64.41199999999998</v>
       </c>
       <c r="F37">
-        <v>184.03</v>
+        <v>189.288</v>
       </c>
       <c r="G37">
         <v>492.7</v>
@@ -4321,28 +4321,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M37">
-        <v>11.796323</v>
+        <v>12.1333608</v>
       </c>
       <c r="N37">
-        <v>25.23701033333333</v>
+        <v>24.89997253333333</v>
       </c>
       <c r="O37">
-        <v>4.164106705</v>
+        <v>4.108495467999999</v>
       </c>
       <c r="P37">
-        <v>21.07290362833333</v>
+        <v>20.79147706533333</v>
       </c>
       <c r="Q37">
-        <v>45.87290362833333</v>
+        <v>45.59147706533334</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07883509302893627</v>
+        <v>0.07929251380830681</v>
       </c>
       <c r="T37">
-        <v>0.6439154513202876</v>
+        <v>0.6528314337070685</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.139396346923811</v>
+        <v>3.052190892842594</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07001566883731636</v>
+        <v>0.07246511220582415</v>
       </c>
       <c r="C38">
-        <v>333.671311536811</v>
+        <v>325.6337068830844</v>
       </c>
       <c r="D38">
-        <v>30.25931153681102</v>
+        <v>27.47970688308433</v>
       </c>
       <c r="E38">
-        <v>-64.41200000000001</v>
+        <v>-59.154</v>
       </c>
       <c r="F38">
-        <v>189.288</v>
+        <v>194.546</v>
       </c>
       <c r="G38">
         <v>492.7</v>
@@ -4403,45 +4403,45 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M38">
-        <v>12.1333608</v>
+        <v>13.9878574</v>
       </c>
       <c r="N38">
-        <v>24.89997253333333</v>
+        <v>23.04547593333333</v>
       </c>
       <c r="O38">
-        <v>4.108495468</v>
+        <v>3.802503529</v>
       </c>
       <c r="P38">
-        <v>20.79147706533333</v>
+        <v>19.24297240433333</v>
       </c>
       <c r="Q38">
-        <v>45.59147706533334</v>
+        <v>44.04297240433333</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07929251380830681</v>
+        <v>0.07976445588226055</v>
       </c>
       <c r="T38">
-        <v>0.6528314337070685</v>
+        <v>0.6620304631537474</v>
       </c>
       <c r="U38">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V38">
         <v>0.165</v>
       </c>
       <c r="W38">
-        <v>0.0535235</v>
+        <v>0.0600365</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.052190892842594</v>
+        <v>2.647534377447494</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07246511220582415</v>
+        <v>0.07256987557433195</v>
       </c>
       <c r="C39">
-        <v>325.6337068830844</v>
+        <v>320.2681656040565</v>
       </c>
       <c r="D39">
-        <v>27.47970688308433</v>
+        <v>27.37216560405653</v>
       </c>
       <c r="E39">
-        <v>-59.154</v>
+        <v>-53.89600000000002</v>
       </c>
       <c r="F39">
-        <v>194.546</v>
+        <v>199.804</v>
       </c>
       <c r="G39">
         <v>492.7</v>
@@ -4485,28 +4485,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M39">
-        <v>13.9878574</v>
+        <v>14.3659076</v>
       </c>
       <c r="N39">
-        <v>23.04547593333333</v>
+        <v>22.66742573333333</v>
       </c>
       <c r="O39">
-        <v>3.802503529</v>
+        <v>3.740125246</v>
       </c>
       <c r="P39">
-        <v>19.24297240433333</v>
+        <v>18.92730048733333</v>
       </c>
       <c r="Q39">
-        <v>44.04297240433333</v>
+        <v>43.72730048733334</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.07976445588226055</v>
+        <v>0.08025162189408377</v>
       </c>
       <c r="T39">
-        <v>0.6620304631537474</v>
+        <v>0.6715262354858028</v>
       </c>
       <c r="U39">
         <v>0.07190000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.647534377447494</v>
+        <v>2.577862420146245</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07256987557433195</v>
+        <v>0.07267463894283974</v>
       </c>
       <c r="C40">
-        <v>320.2681656040565</v>
+        <v>314.9034627650665</v>
       </c>
       <c r="D40">
-        <v>27.37216560405653</v>
+        <v>27.26546276506646</v>
       </c>
       <c r="E40">
-        <v>-53.89600000000002</v>
+        <v>-48.63800000000001</v>
       </c>
       <c r="F40">
-        <v>199.804</v>
+        <v>205.062</v>
       </c>
       <c r="G40">
         <v>492.7</v>
@@ -4567,28 +4567,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M40">
-        <v>14.3659076</v>
+        <v>14.7439578</v>
       </c>
       <c r="N40">
-        <v>22.66742573333333</v>
+        <v>22.28937553333333</v>
       </c>
       <c r="O40">
-        <v>3.740125246</v>
+        <v>3.677746963</v>
       </c>
       <c r="P40">
-        <v>18.92730048733333</v>
+        <v>18.61162857033333</v>
       </c>
       <c r="Q40">
-        <v>43.72730048733334</v>
+        <v>43.41162857033333</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08025162189408377</v>
+        <v>0.08075476056203235</v>
       </c>
       <c r="T40">
-        <v>0.6715262354858028</v>
+        <v>0.6813333446156307</v>
       </c>
       <c r="U40">
         <v>0.07190000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.577862420146245</v>
+        <v>2.511763383732238</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07267463894283974</v>
+        <v>0.07408200231134753</v>
       </c>
       <c r="C41">
-        <v>314.9034627650665</v>
+        <v>308.2886842350834</v>
       </c>
       <c r="D41">
-        <v>27.26546276506646</v>
+        <v>25.9086842350834</v>
       </c>
       <c r="E41">
-        <v>-48.63800000000001</v>
+        <v>-43.38</v>
       </c>
       <c r="F41">
-        <v>205.062</v>
+        <v>210.32</v>
       </c>
       <c r="G41">
         <v>492.7</v>
@@ -4649,45 +4649,45 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M41">
-        <v>14.7439578</v>
+        <v>15.942256</v>
       </c>
       <c r="N41">
-        <v>22.28937553333333</v>
+        <v>21.09107733333333</v>
       </c>
       <c r="O41">
-        <v>3.677746963</v>
+        <v>3.48002776</v>
       </c>
       <c r="P41">
-        <v>18.61162857033333</v>
+        <v>17.61104957333333</v>
       </c>
       <c r="Q41">
-        <v>43.41162857033333</v>
+        <v>42.41104957333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08075476056203235</v>
+        <v>0.08127467051891255</v>
       </c>
       <c r="T41">
-        <v>0.6813333446156307</v>
+        <v>0.6914673573831195</v>
       </c>
       <c r="U41">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V41">
         <v>0.165</v>
       </c>
       <c r="W41">
-        <v>0.0600365</v>
+        <v>0.063293</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.511763383732238</v>
+        <v>2.322966920951045</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07408200231134753</v>
+        <v>0.07421933067985531</v>
       </c>
       <c r="C42">
-        <v>308.2886842350834</v>
+        <v>302.9054878546243</v>
       </c>
       <c r="D42">
-        <v>25.9086842350834</v>
+        <v>25.78348785462432</v>
       </c>
       <c r="E42">
-        <v>-43.38</v>
+        <v>-38.12199999999999</v>
       </c>
       <c r="F42">
-        <v>210.32</v>
+        <v>215.578</v>
       </c>
       <c r="G42">
         <v>492.7</v>
@@ -4731,28 +4731,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M42">
-        <v>15.942256</v>
+        <v>16.3408124</v>
       </c>
       <c r="N42">
-        <v>21.09107733333333</v>
+        <v>20.69252093333333</v>
       </c>
       <c r="O42">
-        <v>3.48002776</v>
+        <v>3.414265954</v>
       </c>
       <c r="P42">
-        <v>17.61104957333333</v>
+        <v>17.27825497933333</v>
       </c>
       <c r="Q42">
-        <v>42.41104957333333</v>
+        <v>42.07825497933333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08127467051891255</v>
+        <v>0.08181220454212765</v>
       </c>
       <c r="T42">
-        <v>0.6914673573831195</v>
+        <v>0.7019448960071333</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.322966920951045</v>
+        <v>2.266309191171752</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07421933067985531</v>
+        <v>0.0743566590483631</v>
       </c>
       <c r="C43">
-        <v>302.9054878546243</v>
+        <v>297.5234956076489</v>
       </c>
       <c r="D43">
-        <v>25.78348785462432</v>
+        <v>25.65949560764896</v>
       </c>
       <c r="E43">
-        <v>-38.12199999999999</v>
+        <v>-32.86399999999998</v>
       </c>
       <c r="F43">
-        <v>215.578</v>
+        <v>220.836</v>
       </c>
       <c r="G43">
         <v>492.7</v>
@@ -4813,28 +4813,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M43">
-        <v>16.3408124</v>
+        <v>16.7393688</v>
       </c>
       <c r="N43">
-        <v>20.69252093333333</v>
+        <v>20.29396453333333</v>
       </c>
       <c r="O43">
-        <v>3.414265954</v>
+        <v>3.348504148</v>
       </c>
       <c r="P43">
-        <v>17.27825497933333</v>
+        <v>16.94546038533333</v>
       </c>
       <c r="Q43">
-        <v>42.07825497933333</v>
+        <v>41.74546038533333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08181220454212765</v>
+        <v>0.08236827422131569</v>
       </c>
       <c r="T43">
-        <v>0.7019448960071333</v>
+        <v>0.7127837290664579</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.266309191171752</v>
+        <v>2.212349448524805</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0743566590483631</v>
+        <v>0.0744939874168709</v>
       </c>
       <c r="C44">
-        <v>297.5234956076489</v>
+        <v>292.1426902053416</v>
       </c>
       <c r="D44">
-        <v>25.65949560764896</v>
+        <v>25.53669020534159</v>
       </c>
       <c r="E44">
-        <v>-32.864</v>
+        <v>-27.60600000000002</v>
       </c>
       <c r="F44">
-        <v>220.836</v>
+        <v>226.094</v>
       </c>
       <c r="G44">
         <v>492.7</v>
@@ -4895,28 +4895,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M44">
-        <v>16.7393688</v>
+        <v>17.1379252</v>
       </c>
       <c r="N44">
-        <v>20.29396453333333</v>
+        <v>19.89540813333333</v>
       </c>
       <c r="O44">
-        <v>3.348504148</v>
+        <v>3.282742342</v>
       </c>
       <c r="P44">
-        <v>16.94546038533333</v>
+        <v>16.61266579133333</v>
       </c>
       <c r="Q44">
-        <v>41.74546038533333</v>
+        <v>41.41266579133334</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08236827422131568</v>
+        <v>0.08294385511731735</v>
       </c>
       <c r="T44">
-        <v>0.7127837290664578</v>
+        <v>0.7240028720576885</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.212349448524805</v>
+        <v>2.16089946134981</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0744939874168709</v>
+        <v>0.07463131578537868</v>
       </c>
       <c r="C45">
-        <v>292.1426902053416</v>
+        <v>286.7630546882846</v>
       </c>
       <c r="D45">
-        <v>25.53669020534159</v>
+        <v>25.41505468828458</v>
       </c>
       <c r="E45">
-        <v>-27.60600000000002</v>
+        <v>-22.34800000000001</v>
       </c>
       <c r="F45">
-        <v>226.094</v>
+        <v>231.352</v>
       </c>
       <c r="G45">
         <v>492.7</v>
@@ -4977,28 +4977,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M45">
-        <v>17.1379252</v>
+        <v>17.5364816</v>
       </c>
       <c r="N45">
-        <v>19.89540813333333</v>
+        <v>19.49685173333333</v>
       </c>
       <c r="O45">
-        <v>3.282742342</v>
+        <v>3.216980536</v>
       </c>
       <c r="P45">
-        <v>16.61266579133333</v>
+        <v>16.27987119733333</v>
       </c>
       <c r="Q45">
-        <v>41.41266579133334</v>
+        <v>41.07987119733333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08294385511731735</v>
+        <v>0.0835399924738905</v>
       </c>
       <c r="T45">
-        <v>0.7240028720576885</v>
+        <v>0.7356226987271776</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.16089946134981</v>
+        <v>2.111788109955496</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07463131578537868</v>
+        <v>0.07476864415388648</v>
       </c>
       <c r="C46">
-        <v>286.7630546882846</v>
+        <v>281.3845724186506</v>
       </c>
       <c r="D46">
-        <v>25.41505468828458</v>
+        <v>25.29457241865063</v>
       </c>
       <c r="E46">
-        <v>-22.34800000000001</v>
+        <v>-17.09</v>
       </c>
       <c r="F46">
-        <v>231.352</v>
+        <v>236.61</v>
       </c>
       <c r="G46">
         <v>492.7</v>
@@ -5059,28 +5059,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M46">
-        <v>17.5364816</v>
+        <v>17.935038</v>
       </c>
       <c r="N46">
-        <v>19.49685173333333</v>
+        <v>19.09829533333333</v>
       </c>
       <c r="O46">
-        <v>3.216980536</v>
+        <v>3.15121873</v>
       </c>
       <c r="P46">
-        <v>16.27987119733333</v>
+        <v>15.94707660333333</v>
       </c>
       <c r="Q46">
-        <v>41.07987119733333</v>
+        <v>40.74707660333333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.0835399924738905</v>
+        <v>0.08415780755252086</v>
       </c>
       <c r="T46">
-        <v>0.7356226987271776</v>
+        <v>0.7476650645482844</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.111788109955496</v>
+        <v>2.064859485289818</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07476864415388648</v>
+        <v>0.07490597252239427</v>
       </c>
       <c r="C47">
-        <v>281.3845724186506</v>
+        <v>276.0072270726161</v>
       </c>
       <c r="D47">
-        <v>25.29457241865063</v>
+        <v>25.17522707261615</v>
       </c>
       <c r="E47">
-        <v>-17.09</v>
+        <v>-11.83199999999999</v>
       </c>
       <c r="F47">
-        <v>236.61</v>
+        <v>241.868</v>
       </c>
       <c r="G47">
         <v>492.7</v>
@@ -5141,28 +5141,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M47">
-        <v>17.935038</v>
+        <v>18.3335944</v>
       </c>
       <c r="N47">
-        <v>19.09829533333333</v>
+        <v>18.69973893333333</v>
       </c>
       <c r="O47">
-        <v>3.15121873</v>
+        <v>3.085456923999999</v>
       </c>
       <c r="P47">
-        <v>15.94707660333333</v>
+        <v>15.61428200933333</v>
       </c>
       <c r="Q47">
-        <v>40.74707660333333</v>
+        <v>40.41428200933333</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08415780755252086</v>
+        <v>0.08479850467110049</v>
       </c>
       <c r="T47">
-        <v>0.7476650645482844</v>
+        <v>0.7601534439183211</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.064859485289818</v>
+        <v>2.019971235609605</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07490597252239427</v>
+        <v>0.08061609089090206</v>
       </c>
       <c r="C48">
-        <v>276.0072270726161</v>
+        <v>266.6202877557595</v>
       </c>
       <c r="D48">
-        <v>25.17522707261615</v>
+        <v>21.0462877557595</v>
       </c>
       <c r="E48">
-        <v>-11.83199999999999</v>
+        <v>-6.573999999999984</v>
       </c>
       <c r="F48">
-        <v>241.868</v>
+        <v>247.126</v>
       </c>
       <c r="G48">
         <v>492.7</v>
@@ -5223,45 +5223,45 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M48">
-        <v>18.3335944</v>
+        <v>22.24134</v>
       </c>
       <c r="N48">
-        <v>18.69973893333333</v>
+        <v>14.79199333333333</v>
       </c>
       <c r="O48">
-        <v>3.085456923999999</v>
+        <v>2.4406789</v>
       </c>
       <c r="P48">
-        <v>15.61428200933333</v>
+        <v>12.35131443333333</v>
       </c>
       <c r="Q48">
-        <v>40.41428200933333</v>
+        <v>37.15131443333333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08479850467110049</v>
+        <v>0.08546337903943785</v>
       </c>
       <c r="T48">
-        <v>0.7601534439183211</v>
+        <v>0.773113082887227</v>
       </c>
       <c r="U48">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V48">
         <v>0.165</v>
       </c>
       <c r="W48">
-        <v>0.063293</v>
+        <v>0.07514999999999999</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.019971235609605</v>
+        <v>1.665067542393279</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08061609089090206</v>
+        <v>0.08087198925940985</v>
       </c>
       <c r="C49">
-        <v>266.6202877557595</v>
+        <v>261.2087261582119</v>
       </c>
       <c r="D49">
-        <v>21.0462877557595</v>
+        <v>20.89272615821199</v>
       </c>
       <c r="E49">
-        <v>-6.573999999999984</v>
+        <v>-1.316000000000003</v>
       </c>
       <c r="F49">
-        <v>247.126</v>
+        <v>252.384</v>
       </c>
       <c r="G49">
         <v>492.7</v>
@@ -5305,28 +5305,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M49">
-        <v>22.24134</v>
+        <v>22.71456</v>
       </c>
       <c r="N49">
-        <v>14.79199333333333</v>
+        <v>14.31877333333333</v>
       </c>
       <c r="O49">
-        <v>2.4406789</v>
+        <v>2.3625976</v>
       </c>
       <c r="P49">
-        <v>12.35131443333333</v>
+        <v>11.95617573333333</v>
       </c>
       <c r="Q49">
-        <v>37.15131443333333</v>
+        <v>36.75617573333334</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08546337903943785</v>
+        <v>0.08615382549886509</v>
       </c>
       <c r="T49">
-        <v>0.773113082887227</v>
+        <v>0.7865711695087833</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.665067542393279</v>
+        <v>1.630378635260086</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08087198925940983</v>
+        <v>0.08112788762791763</v>
       </c>
       <c r="C50">
-        <v>261.2087261582121</v>
+        <v>255.7993892146088</v>
       </c>
       <c r="D50">
-        <v>20.89272615821199</v>
+        <v>20.74138921460878</v>
       </c>
       <c r="E50">
-        <v>-1.316000000000031</v>
+        <v>3.942000000000007</v>
       </c>
       <c r="F50">
-        <v>252.384</v>
+        <v>257.642</v>
       </c>
       <c r="G50">
         <v>492.7</v>
@@ -5387,28 +5387,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M50">
-        <v>22.71456</v>
+        <v>23.18778</v>
       </c>
       <c r="N50">
-        <v>14.31877333333334</v>
+        <v>13.84555333333333</v>
       </c>
       <c r="O50">
-        <v>2.3625976</v>
+        <v>2.2845163</v>
       </c>
       <c r="P50">
-        <v>11.95617573333334</v>
+        <v>11.56103703333333</v>
       </c>
       <c r="Q50">
-        <v>36.75617573333334</v>
+        <v>36.36103703333333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08615382549886508</v>
+        <v>0.08687134829003458</v>
       </c>
       <c r="T50">
-        <v>0.7865711695087831</v>
+        <v>0.8005570242331456</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.630378635260086</v>
+        <v>1.597105601887431</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08112788762791763</v>
+        <v>0.08138378599642543</v>
       </c>
       <c r="C51">
-        <v>255.7993892146088</v>
+        <v>250.3922289296089</v>
       </c>
       <c r="D51">
-        <v>20.74138921460878</v>
+        <v>20.59222892960885</v>
       </c>
       <c r="E51">
-        <v>3.942000000000007</v>
+        <v>9.199999999999989</v>
       </c>
       <c r="F51">
-        <v>257.642</v>
+        <v>262.9</v>
       </c>
       <c r="G51">
         <v>492.7</v>
@@ -5469,28 +5469,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M51">
-        <v>23.18778</v>
+        <v>23.661</v>
       </c>
       <c r="N51">
-        <v>13.84555333333333</v>
+        <v>13.37233333333333</v>
       </c>
       <c r="O51">
-        <v>2.2845163</v>
+        <v>2.206435</v>
       </c>
       <c r="P51">
-        <v>11.56103703333333</v>
+        <v>11.16589833333333</v>
       </c>
       <c r="Q51">
-        <v>36.36103703333333</v>
+        <v>35.96589833333334</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08687134829003458</v>
+        <v>0.08761757199285086</v>
       </c>
       <c r="T51">
-        <v>0.8005570242331456</v>
+        <v>0.8151023131464823</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.597105601887431</v>
+        <v>1.565163489849682</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08138378599642543</v>
+        <v>0.08163968436493321</v>
       </c>
       <c r="C52">
-        <v>250.3922289296089</v>
+        <v>244.9871986786343</v>
       </c>
       <c r="D52">
-        <v>20.59222892960885</v>
+        <v>20.44519867863427</v>
       </c>
       <c r="E52">
-        <v>9.199999999999989</v>
+        <v>14.45799999999997</v>
       </c>
       <c r="F52">
-        <v>262.9</v>
+        <v>268.158</v>
       </c>
       <c r="G52">
         <v>492.7</v>
@@ -5551,28 +5551,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M52">
-        <v>23.661</v>
+        <v>24.13422</v>
       </c>
       <c r="N52">
-        <v>13.37233333333333</v>
+        <v>12.89911333333334</v>
       </c>
       <c r="O52">
-        <v>2.206435</v>
+        <v>2.1283537</v>
       </c>
       <c r="P52">
-        <v>11.16589833333333</v>
+        <v>10.77075963333334</v>
       </c>
       <c r="Q52">
-        <v>35.96589833333334</v>
+        <v>35.57075963333334</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08761757199285086</v>
+        <v>0.08839425380598616</v>
       </c>
       <c r="T52">
-        <v>0.8151023131464823</v>
+        <v>0.830241287321588</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.565163489849682</v>
+        <v>1.534474009656551</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08163968436493321</v>
+        <v>0.08189558273344102</v>
       </c>
       <c r="C53">
-        <v>244.9871986786343</v>
+        <v>239.5842531592803</v>
       </c>
       <c r="D53">
-        <v>20.44519867863427</v>
+        <v>20.30025315928036</v>
       </c>
       <c r="E53">
-        <v>14.45799999999997</v>
+        <v>19.71600000000001</v>
       </c>
       <c r="F53">
-        <v>268.158</v>
+        <v>273.416</v>
       </c>
       <c r="G53">
         <v>492.7</v>
@@ -5633,28 +5633,28 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M53">
-        <v>24.13422</v>
+        <v>24.60744</v>
       </c>
       <c r="N53">
-        <v>12.89911333333334</v>
+        <v>12.42589333333333</v>
       </c>
       <c r="O53">
-        <v>2.1283537</v>
+        <v>2.0502724</v>
       </c>
       <c r="P53">
-        <v>10.77075963333334</v>
+        <v>10.37562093333333</v>
       </c>
       <c r="Q53">
-        <v>35.57075963333334</v>
+        <v>35.17562093333333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08839425380598616</v>
+        <v>0.08920329736133545</v>
       </c>
       <c r="T53">
-        <v>0.830241287321588</v>
+        <v>0.8460110520873232</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.534474009656551</v>
+        <v>1.504964894086233</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08189558273344102</v>
+        <v>0.108693460855995</v>
       </c>
       <c r="C54">
-        <v>239.5842531592803</v>
+        <v>225.6766463064317</v>
       </c>
       <c r="D54">
-        <v>20.30025315928036</v>
+        <v>11.65064630643165</v>
       </c>
       <c r="E54">
-        <v>19.71600000000001</v>
+        <v>24.97399999999999</v>
       </c>
       <c r="F54">
-        <v>273.416</v>
+        <v>278.674</v>
       </c>
       <c r="G54">
         <v>492.7</v>
@@ -5715,45 +5715,45 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M54">
-        <v>24.60744</v>
+        <v>40.9093432</v>
       </c>
       <c r="N54">
-        <v>12.42589333333333</v>
+        <v>-3.876009866666671</v>
       </c>
       <c r="O54">
-        <v>2.0502724</v>
+        <v>-0.6395416280000007</v>
       </c>
       <c r="P54">
-        <v>10.37562093333333</v>
+        <v>-3.23646823866667</v>
       </c>
       <c r="Q54">
-        <v>35.17562093333333</v>
+        <v>21.56353176133333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.08920329736133545</v>
+        <v>0.09044851014495511</v>
       </c>
       <c r="T54">
-        <v>0.8460110520873232</v>
+        <v>0.870282566953406</v>
       </c>
       <c r="U54">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.165</v>
+        <v>0.1493668566157767</v>
       </c>
       <c r="W54">
-        <v>0.07514999999999999</v>
+        <v>0.124872945448804</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.504964894086233</v>
+        <v>0.9052536764592527</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.108693460855995</v>
+        <v>0.109703460855995</v>
       </c>
       <c r="C55">
-        <v>225.6766463064317</v>
+        <v>220.2345067839101</v>
       </c>
       <c r="D55">
-        <v>11.65064630643165</v>
+        <v>11.46650678391012</v>
       </c>
       <c r="E55">
-        <v>24.97399999999999</v>
+        <v>30.23200000000003</v>
       </c>
       <c r="F55">
-        <v>278.674</v>
+        <v>283.932</v>
       </c>
       <c r="G55">
         <v>492.7</v>
@@ -5797,37 +5797,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M55">
-        <v>40.9093432</v>
+        <v>41.6812176</v>
       </c>
       <c r="N55">
-        <v>-3.876009866666671</v>
+        <v>-4.647884266666672</v>
       </c>
       <c r="O55">
-        <v>-0.6395416280000007</v>
+        <v>-0.766900904000001</v>
       </c>
       <c r="P55">
-        <v>-3.23646823866667</v>
+        <v>-3.880983362666671</v>
       </c>
       <c r="Q55">
-        <v>21.56353176133333</v>
+        <v>20.91901663733333</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09044851014495511</v>
+        <v>0.09141912993071501</v>
       </c>
       <c r="T55">
-        <v>0.870282566953406</v>
+        <v>0.8892017531915234</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1493668566157767</v>
+        <v>0.1466008037154845</v>
       </c>
       <c r="W55">
-        <v>0.124872945448804</v>
+        <v>0.1252790020145669</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.9052536764592527</v>
+        <v>0.888489719487785</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.109703460855995</v>
+        <v>0.110713460855995</v>
       </c>
       <c r="C56">
-        <v>220.2345067839101</v>
+        <v>214.7980973800818</v>
       </c>
       <c r="D56">
-        <v>11.46650678391012</v>
+        <v>11.28809738008183</v>
       </c>
       <c r="E56">
-        <v>30.23200000000003</v>
+        <v>35.49000000000001</v>
       </c>
       <c r="F56">
-        <v>283.932</v>
+        <v>289.19</v>
       </c>
       <c r="G56">
         <v>492.7</v>
@@ -5879,37 +5879,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M56">
-        <v>41.6812176</v>
+        <v>42.45309200000001</v>
       </c>
       <c r="N56">
-        <v>-4.647884266666672</v>
+        <v>-5.419758666666674</v>
       </c>
       <c r="O56">
-        <v>-0.766900904000001</v>
+        <v>-0.8942601800000012</v>
       </c>
       <c r="P56">
-        <v>-3.880983362666671</v>
+        <v>-4.525498486666672</v>
       </c>
       <c r="Q56">
-        <v>20.91901663733333</v>
+        <v>20.27450151333333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09141912993071501</v>
+        <v>0.09243288837361979</v>
       </c>
       <c r="T56">
-        <v>0.8892017531915234</v>
+        <v>0.9089617921513352</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1466008037154845</v>
+        <v>0.1439353345570212</v>
       </c>
       <c r="W56">
-        <v>0.1252790020145669</v>
+        <v>0.1256702928870293</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.888489719487785</v>
+        <v>0.8723353609516434</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.110713460855995</v>
+        <v>0.111723460855995</v>
       </c>
       <c r="C57">
-        <v>214.7980973800818</v>
+        <v>209.3671547249808</v>
       </c>
       <c r="D57">
-        <v>11.28809738008183</v>
+        <v>11.11515472498083</v>
       </c>
       <c r="E57">
-        <v>35.49000000000001</v>
+        <v>40.74799999999999</v>
       </c>
       <c r="F57">
-        <v>289.19</v>
+        <v>294.448</v>
       </c>
       <c r="G57">
         <v>492.7</v>
@@ -5961,37 +5961,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M57">
-        <v>42.45309200000001</v>
+        <v>43.2249664</v>
       </c>
       <c r="N57">
-        <v>-5.419758666666674</v>
+        <v>-6.191633066666668</v>
       </c>
       <c r="O57">
-        <v>-0.8942601800000012</v>
+        <v>-1.021619456</v>
       </c>
       <c r="P57">
-        <v>-4.525498486666672</v>
+        <v>-5.170013610666668</v>
       </c>
       <c r="Q57">
-        <v>20.27450151333333</v>
+        <v>19.62998638933333</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09243288837361979</v>
+        <v>0.09349272674574752</v>
       </c>
       <c r="T57">
-        <v>0.9089617921513352</v>
+        <v>0.9296200147002291</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1439353345570212</v>
+        <v>0.1413650607256458</v>
       </c>
       <c r="W57">
-        <v>0.1256702928870293</v>
+        <v>0.1260476090854752</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8723353609516434</v>
+        <v>0.8567579437917928</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.111723460855995</v>
+        <v>0.112733460855995</v>
       </c>
       <c r="C58">
-        <v>209.3671547249808</v>
+        <v>203.9414313452443</v>
       </c>
       <c r="D58">
-        <v>11.11515472498083</v>
+        <v>10.94743134524429</v>
       </c>
       <c r="E58">
-        <v>40.74799999999999</v>
+        <v>46.00600000000003</v>
       </c>
       <c r="F58">
-        <v>294.448</v>
+        <v>299.706</v>
       </c>
       <c r="G58">
         <v>492.7</v>
@@ -6043,37 +6043,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M58">
-        <v>43.2249664</v>
+        <v>43.99684080000001</v>
       </c>
       <c r="N58">
-        <v>-6.191633066666668</v>
+        <v>-6.963507466666677</v>
       </c>
       <c r="O58">
-        <v>-1.021619456</v>
+        <v>-1.148978732000002</v>
       </c>
       <c r="P58">
-        <v>-5.170013610666668</v>
+        <v>-5.814528734666675</v>
       </c>
       <c r="Q58">
-        <v>19.62998638933333</v>
+        <v>18.98547126533332</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09349272674574752</v>
+        <v>0.09460185992588119</v>
       </c>
       <c r="T58">
-        <v>0.9296200147002291</v>
+        <v>0.9512390848095369</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1413650607256458</v>
+        <v>0.1388849719409853</v>
       </c>
       <c r="W58">
-        <v>0.1260476090854752</v>
+        <v>0.1264116861190634</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8567579437917928</v>
+        <v>0.8417271026726384</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.112733460855995</v>
+        <v>0.113743460855995</v>
       </c>
       <c r="C59">
-        <v>203.9414313452443</v>
+        <v>198.5206944825736</v>
       </c>
       <c r="D59">
-        <v>10.94743134524429</v>
+        <v>10.78469448257355</v>
       </c>
       <c r="E59">
-        <v>46.00600000000003</v>
+        <v>51.26400000000001</v>
       </c>
       <c r="F59">
-        <v>299.706</v>
+        <v>304.964</v>
       </c>
       <c r="G59">
         <v>492.7</v>
@@ -6125,37 +6125,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M59">
-        <v>43.99684080000001</v>
+        <v>44.7687152</v>
       </c>
       <c r="N59">
-        <v>-6.963507466666677</v>
+        <v>-7.735381866666671</v>
       </c>
       <c r="O59">
-        <v>-1.148978732000002</v>
+        <v>-1.276338008000001</v>
       </c>
       <c r="P59">
-        <v>-5.814528734666675</v>
+        <v>-6.459043858666671</v>
       </c>
       <c r="Q59">
-        <v>18.98547126533332</v>
+        <v>18.34095614133333</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09460185992588119</v>
+        <v>0.09576380897173548</v>
       </c>
       <c r="T59">
-        <v>0.9512390848095369</v>
+        <v>0.973887634447859</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1388849719409853</v>
+        <v>0.1364904034592442</v>
       </c>
       <c r="W59">
-        <v>0.1264116861190634</v>
+        <v>0.1267632087721829</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8417271026726384</v>
+        <v>0.827214566419662</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.113743460855995</v>
+        <v>0.114753460855995</v>
       </c>
       <c r="C60">
-        <v>198.5206944825736</v>
+        <v>193.1047250160352</v>
       </c>
       <c r="D60">
-        <v>10.78469448257355</v>
+        <v>10.62672501603514</v>
       </c>
       <c r="E60">
-        <v>51.26399999999995</v>
+        <v>56.52199999999999</v>
       </c>
       <c r="F60">
-        <v>304.9639999999999</v>
+        <v>310.222</v>
       </c>
       <c r="G60">
         <v>492.7</v>
@@ -6207,37 +6207,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M60">
-        <v>44.7687152</v>
+        <v>45.5405896</v>
       </c>
       <c r="N60">
-        <v>-7.735381866666664</v>
+        <v>-8.507256266666673</v>
       </c>
       <c r="O60">
-        <v>-1.276338008</v>
+        <v>-1.403697284000001</v>
       </c>
       <c r="P60">
-        <v>-6.459043858666664</v>
+        <v>-7.103558982666671</v>
       </c>
       <c r="Q60">
-        <v>18.34095614133334</v>
+        <v>17.69644101733333</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09576380897173548</v>
+        <v>0.09698243845885096</v>
       </c>
       <c r="T60">
-        <v>0.9738876344478589</v>
+        <v>0.9976409913856114</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1364904034592442</v>
+        <v>0.1341770067904435</v>
       </c>
       <c r="W60">
-        <v>0.1267632087721829</v>
+        <v>0.1271028154031629</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8272145664196621</v>
+        <v>0.8131939805481423</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.114753460855995</v>
+        <v>0.1486486185320756</v>
       </c>
       <c r="C61">
-        <v>193.1047250160352</v>
+        <v>184.3445436047552</v>
       </c>
       <c r="D61">
-        <v>10.62672501603514</v>
+        <v>7.124543604755159</v>
       </c>
       <c r="E61">
-        <v>56.52199999999999</v>
+        <v>61.77999999999997</v>
       </c>
       <c r="F61">
-        <v>310.222</v>
+        <v>315.48</v>
       </c>
       <c r="G61">
         <v>492.7</v>
@@ -6289,45 +6289,45 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M61">
-        <v>45.5405896</v>
+        <v>63.348384</v>
       </c>
       <c r="N61">
-        <v>-8.507256266666673</v>
+        <v>-26.31505066666666</v>
       </c>
       <c r="O61">
-        <v>-1.403697284000001</v>
+        <v>-4.34198336</v>
       </c>
       <c r="P61">
-        <v>-7.103558982666671</v>
+        <v>-21.97306730666666</v>
       </c>
       <c r="Q61">
-        <v>17.69644101733333</v>
+        <v>2.826932693333337</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09698243845885096</v>
+        <v>0.09947489361052367</v>
       </c>
       <c r="T61">
-        <v>0.9976409913856114</v>
+        <v>1.046223581496047</v>
       </c>
       <c r="U61">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1341770067904435</v>
+        <v>0.09645865630921226</v>
       </c>
       <c r="W61">
-        <v>0.1271028154031629</v>
+        <v>0.1814311018131102</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.8131939805481423</v>
+        <v>0.5845979170255288</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1486486185320756</v>
+        <v>0.1501986185320756</v>
       </c>
       <c r="C62">
-        <v>184.3445436047552</v>
+        <v>178.9807659350633</v>
       </c>
       <c r="D62">
-        <v>7.124543604755159</v>
+        <v>7.018765935063315</v>
       </c>
       <c r="E62">
-        <v>61.77999999999997</v>
+        <v>67.03799999999995</v>
       </c>
       <c r="F62">
-        <v>315.48</v>
+        <v>320.7379999999999</v>
       </c>
       <c r="G62">
         <v>492.7</v>
@@ -6371,37 +6371,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M62">
-        <v>63.348384</v>
+        <v>64.40419039999999</v>
       </c>
       <c r="N62">
-        <v>-26.31505066666666</v>
+        <v>-27.37085706666666</v>
       </c>
       <c r="O62">
-        <v>-4.34198336</v>
+        <v>-4.516191415999999</v>
       </c>
       <c r="P62">
-        <v>-21.97306730666666</v>
+        <v>-22.85466565066666</v>
       </c>
       <c r="Q62">
-        <v>2.826932693333337</v>
+        <v>1.94533434933334</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09947489361052367</v>
+        <v>0.1008511729338704</v>
       </c>
       <c r="T62">
-        <v>1.046223581496047</v>
+        <v>1.073049827175432</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.09645865630921226</v>
+        <v>0.09487736686152025</v>
       </c>
       <c r="W62">
-        <v>0.1814311018131102</v>
+        <v>0.1817486247342067</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5845979170255288</v>
+        <v>0.5750143446152742</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1501986185320756</v>
+        <v>0.1517486185320756</v>
       </c>
       <c r="C63">
-        <v>178.9807659350633</v>
+        <v>173.6200832634997</v>
       </c>
       <c r="D63">
-        <v>7.018765935063315</v>
+        <v>6.916083263499697</v>
       </c>
       <c r="E63">
-        <v>67.03799999999995</v>
+        <v>72.29599999999999</v>
       </c>
       <c r="F63">
-        <v>320.7379999999999</v>
+        <v>325.996</v>
       </c>
       <c r="G63">
         <v>492.7</v>
@@ -6453,37 +6453,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M63">
-        <v>64.40419039999999</v>
+        <v>65.4599968</v>
       </c>
       <c r="N63">
-        <v>-27.37085706666666</v>
+        <v>-28.42666346666667</v>
       </c>
       <c r="O63">
-        <v>-4.516191415999999</v>
+        <v>-4.690399472</v>
       </c>
       <c r="P63">
-        <v>-22.85466565066666</v>
+        <v>-23.73626399466667</v>
       </c>
       <c r="Q63">
-        <v>1.94533434933334</v>
+        <v>1.063736005333332</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1008511729338704</v>
+        <v>0.1022998880110775</v>
       </c>
       <c r="T63">
-        <v>1.073049827175432</v>
+        <v>1.101287980522154</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.09487736686152025</v>
+        <v>0.09334708675085056</v>
       </c>
       <c r="W63">
-        <v>0.1817486247342067</v>
+        <v>0.1820559049804292</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5750143446152742</v>
+        <v>0.5657399197021246</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1517486185320756</v>
+        <v>0.1532986185320756</v>
       </c>
       <c r="C64">
-        <v>173.6200832634997</v>
+        <v>168.2623617116807</v>
       </c>
       <c r="D64">
-        <v>6.916083263499697</v>
+        <v>6.81636171168063</v>
       </c>
       <c r="E64">
-        <v>72.29599999999999</v>
+        <v>77.55399999999997</v>
       </c>
       <c r="F64">
-        <v>325.996</v>
+        <v>331.254</v>
       </c>
       <c r="G64">
         <v>492.7</v>
@@ -6535,37 +6535,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M64">
-        <v>65.4599968</v>
+        <v>66.51580319999999</v>
       </c>
       <c r="N64">
-        <v>-28.42666346666667</v>
+        <v>-29.48246986666666</v>
       </c>
       <c r="O64">
-        <v>-4.690399472</v>
+        <v>-4.864607528</v>
       </c>
       <c r="P64">
-        <v>-23.73626399466667</v>
+        <v>-24.61786233866666</v>
       </c>
       <c r="Q64">
-        <v>1.063736005333332</v>
+        <v>0.1821376613333392</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1022998880110775</v>
+        <v>0.1038269120113769</v>
       </c>
       <c r="T64">
-        <v>1.101287980522154</v>
+        <v>1.131052520536266</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.09334708675085056</v>
+        <v>0.09186538696115452</v>
       </c>
       <c r="W64">
-        <v>0.1820559049804292</v>
+        <v>0.1823534302982002</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5657399197021246</v>
+        <v>0.556759920976694</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1532986185320756</v>
+        <v>0.1548486185320756</v>
       </c>
       <c r="C65">
-        <v>168.2623617116807</v>
+        <v>162.907475012928</v>
       </c>
       <c r="D65">
-        <v>6.81636171168063</v>
+        <v>6.719475012928025</v>
       </c>
       <c r="E65">
-        <v>77.55399999999997</v>
+        <v>82.81200000000001</v>
       </c>
       <c r="F65">
-        <v>331.254</v>
+        <v>336.512</v>
       </c>
       <c r="G65">
         <v>492.7</v>
@@ -6617,37 +6617,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M65">
-        <v>66.51580319999999</v>
+        <v>67.5716096</v>
       </c>
       <c r="N65">
-        <v>-29.48246986666666</v>
+        <v>-30.53827626666667</v>
       </c>
       <c r="O65">
-        <v>-4.864607528</v>
+        <v>-5.038815584000001</v>
       </c>
       <c r="P65">
-        <v>-24.61786233866666</v>
+        <v>-25.49946068266667</v>
       </c>
       <c r="Q65">
-        <v>0.1821376613333392</v>
+        <v>-0.6994606826666683</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1038269120113769</v>
+        <v>0.1054387706783596</v>
       </c>
       <c r="T65">
-        <v>1.131052520536266</v>
+        <v>1.162470646106718</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.09186538696115452</v>
+        <v>0.09042999028988648</v>
       </c>
       <c r="W65">
-        <v>0.1823534302982002</v>
+        <v>0.1826416579497908</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.556759920976694</v>
+        <v>0.5480605472114332</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1548486185320756</v>
+        <v>0.1563986185320756</v>
       </c>
       <c r="C66">
-        <v>162.907475012928</v>
+        <v>157.5553039788928</v>
       </c>
       <c r="D66">
-        <v>6.719475012928025</v>
+        <v>6.625303978892747</v>
       </c>
       <c r="E66">
-        <v>82.81200000000001</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="F66">
-        <v>336.512</v>
+        <v>341.77</v>
       </c>
       <c r="G66">
         <v>492.7</v>
@@ -6699,37 +6699,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M66">
-        <v>67.5716096</v>
+        <v>68.627416</v>
       </c>
       <c r="N66">
-        <v>-30.53827626666667</v>
+        <v>-31.59408266666667</v>
       </c>
       <c r="O66">
-        <v>-5.038815584000001</v>
+        <v>-5.21302364</v>
       </c>
       <c r="P66">
-        <v>-25.49946068266667</v>
+        <v>-26.38105902666667</v>
       </c>
       <c r="Q66">
-        <v>-0.6994606826666683</v>
+        <v>-1.581059026666665</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1054387706783596</v>
+        <v>0.1071427355548842</v>
       </c>
       <c r="T66">
-        <v>1.162470646106718</v>
+        <v>1.195684093138339</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.09042999028988648</v>
+        <v>0.08903875967004207</v>
       </c>
       <c r="W66">
-        <v>0.1826416579497908</v>
+        <v>0.1829210170582556</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5480605472114332</v>
+        <v>0.5396288464851035</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1563986185320756</v>
+        <v>0.1579486185320756</v>
       </c>
       <c r="C67">
-        <v>157.5553039788928</v>
+        <v>152.2057360104087</v>
       </c>
       <c r="D67">
-        <v>6.625303978892747</v>
+        <v>6.53373601040862</v>
       </c>
       <c r="E67">
-        <v>88.06999999999999</v>
+        <v>93.32799999999997</v>
       </c>
       <c r="F67">
-        <v>341.77</v>
+        <v>347.028</v>
       </c>
       <c r="G67">
         <v>492.7</v>
@@ -6781,37 +6781,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M67">
-        <v>68.627416</v>
+        <v>69.68322239999999</v>
       </c>
       <c r="N67">
-        <v>-31.59408266666667</v>
+        <v>-32.64988906666666</v>
       </c>
       <c r="O67">
-        <v>-5.21302364</v>
+        <v>-5.387231695999999</v>
       </c>
       <c r="P67">
-        <v>-26.38105902666667</v>
+        <v>-27.26265737066666</v>
       </c>
       <c r="Q67">
-        <v>-1.581059026666665</v>
+        <v>-2.462657370666658</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1071427355548842</v>
+        <v>0.1089469336594396</v>
       </c>
       <c r="T67">
-        <v>1.195684093138339</v>
+        <v>1.23085127234829</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.08903875967004207</v>
+        <v>0.08768968755382932</v>
       </c>
       <c r="W67">
-        <v>0.1829210170582556</v>
+        <v>0.1831919107391911</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5396288464851035</v>
+        <v>0.5314526518413898</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1579486185320756</v>
+        <v>0.1594986185320756</v>
       </c>
       <c r="C68">
-        <v>152.2057360104087</v>
+        <v>146.8586646483562</v>
       </c>
       <c r="D68">
-        <v>6.53373601040862</v>
+        <v>6.444664648356174</v>
       </c>
       <c r="E68">
-        <v>93.32799999999997</v>
+        <v>98.58600000000001</v>
       </c>
       <c r="F68">
-        <v>347.028</v>
+        <v>352.286</v>
       </c>
       <c r="G68">
         <v>492.7</v>
@@ -6863,37 +6863,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M68">
-        <v>69.68322239999999</v>
+        <v>70.7390288</v>
       </c>
       <c r="N68">
-        <v>-32.64988906666666</v>
+        <v>-33.70569546666667</v>
       </c>
       <c r="O68">
-        <v>-5.387231695999999</v>
+        <v>-5.561439752000001</v>
       </c>
       <c r="P68">
-        <v>-27.26265737066666</v>
+        <v>-28.14425571466667</v>
       </c>
       <c r="Q68">
-        <v>-2.462657370666658</v>
+        <v>-3.344255714666666</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1089469336594396</v>
+        <v>0.1108604771036651</v>
       </c>
       <c r="T68">
-        <v>1.23085127234829</v>
+        <v>1.268149795752784</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.08768968755382932</v>
+        <v>0.08638088624705574</v>
       </c>
       <c r="W68">
-        <v>0.1831919107391911</v>
+        <v>0.1834547180415912</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5314526518413898</v>
+        <v>0.5235205227094287</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1594986185320756</v>
+        <v>0.1610486185320756</v>
       </c>
       <c r="C69">
-        <v>146.8586646483562</v>
+        <v>141.5139891607695</v>
       </c>
       <c r="D69">
-        <v>6.444664648356174</v>
+        <v>6.357989160769553</v>
       </c>
       <c r="E69">
-        <v>98.58600000000001</v>
+        <v>103.844</v>
       </c>
       <c r="F69">
-        <v>352.286</v>
+        <v>357.544</v>
       </c>
       <c r="G69">
         <v>492.7</v>
@@ -6945,37 +6945,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M69">
-        <v>70.7390288</v>
+        <v>71.79483519999999</v>
       </c>
       <c r="N69">
-        <v>-33.70569546666667</v>
+        <v>-34.76150186666666</v>
       </c>
       <c r="O69">
-        <v>-5.561439752000001</v>
+        <v>-5.735647808</v>
       </c>
       <c r="P69">
-        <v>-28.14425571466667</v>
+        <v>-29.02585405866666</v>
       </c>
       <c r="Q69">
-        <v>-3.344255714666666</v>
+        <v>-4.225854058666663</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1108604771036651</v>
+        <v>0.1128936170131546</v>
       </c>
       <c r="T69">
-        <v>1.268149795752784</v>
+        <v>1.307779476870058</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.08638088624705574</v>
+        <v>0.08511057909636376</v>
       </c>
       <c r="W69">
-        <v>0.1834547180415912</v>
+        <v>0.1837097957174502</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5235205227094287</v>
+        <v>0.5158216914931136</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1610486185320756</v>
+        <v>0.1625986185320756</v>
       </c>
       <c r="C70">
-        <v>141.5139891607695</v>
+        <v>136.1716141628197</v>
       </c>
       <c r="D70">
-        <v>6.357989160769553</v>
+        <v>6.273614162819674</v>
       </c>
       <c r="E70">
-        <v>103.844</v>
+        <v>109.102</v>
       </c>
       <c r="F70">
-        <v>357.544</v>
+        <v>362.802</v>
       </c>
       <c r="G70">
         <v>492.7</v>
@@ -7027,37 +7027,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M70">
-        <v>71.79483519999999</v>
+        <v>72.8506416</v>
       </c>
       <c r="N70">
-        <v>-34.76150186666666</v>
+        <v>-35.81730826666667</v>
       </c>
       <c r="O70">
-        <v>-5.735647808</v>
+        <v>-5.909855864000001</v>
       </c>
       <c r="P70">
-        <v>-29.02585405866666</v>
+        <v>-29.90745240266667</v>
       </c>
       <c r="Q70">
-        <v>-4.225854058666663</v>
+        <v>-5.10745240266667</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1128936170131546</v>
+        <v>0.1150579272393854</v>
       </c>
       <c r="T70">
-        <v>1.307779476870058</v>
+        <v>1.349965911607802</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.08511057909636376</v>
+        <v>0.08387709244279325</v>
       </c>
       <c r="W70">
-        <v>0.1837097957174502</v>
+        <v>0.1839574798374871</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5158216914931136</v>
+        <v>0.5083460148048076</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1625986185320756</v>
+        <v>0.1641486185320756</v>
       </c>
       <c r="C71">
-        <v>136.1716141628197</v>
+        <v>130.8314492666597</v>
       </c>
       <c r="D71">
-        <v>6.273614162819674</v>
+        <v>6.191449266659647</v>
       </c>
       <c r="E71">
-        <v>109.102</v>
+        <v>114.36</v>
       </c>
       <c r="F71">
-        <v>362.802</v>
+        <v>368.06</v>
       </c>
       <c r="G71">
         <v>492.7</v>
@@ -7109,37 +7109,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M71">
-        <v>72.8506416</v>
+        <v>73.906448</v>
       </c>
       <c r="N71">
-        <v>-35.81730826666667</v>
+        <v>-36.87311466666667</v>
       </c>
       <c r="O71">
-        <v>-5.909855864000001</v>
+        <v>-6.08406392</v>
       </c>
       <c r="P71">
-        <v>-29.90745240266667</v>
+        <v>-30.78905074666667</v>
       </c>
       <c r="Q71">
-        <v>-5.10745240266667</v>
+        <v>-5.989050746666667</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1150579272393854</v>
+        <v>0.1173665248140316</v>
       </c>
       <c r="T71">
-        <v>1.349965911607802</v>
+        <v>1.394964775328062</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.08387709244279325</v>
+        <v>0.08267884826503907</v>
       </c>
       <c r="W71">
-        <v>0.1839574798374871</v>
+        <v>0.1841980872683802</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5083460148048076</v>
+        <v>0.5010839288790246</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1641486185320756</v>
+        <v>0.190744385514429</v>
       </c>
       <c r="C72">
-        <v>130.8314492666597</v>
+        <v>124.4373835860559</v>
       </c>
       <c r="D72">
-        <v>6.191449266659647</v>
+        <v>5.055383586055892</v>
       </c>
       <c r="E72">
-        <v>114.36</v>
+        <v>119.618</v>
       </c>
       <c r="F72">
-        <v>368.06</v>
+        <v>373.318</v>
       </c>
       <c r="G72">
         <v>492.7</v>
@@ -7191,45 +7191,45 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M72">
-        <v>73.906448</v>
+        <v>88.02838439999999</v>
       </c>
       <c r="N72">
-        <v>-36.87311466666667</v>
+        <v>-50.99505106666666</v>
       </c>
       <c r="O72">
-        <v>-6.08406392</v>
+        <v>-8.414183425999999</v>
       </c>
       <c r="P72">
-        <v>-30.78905074666667</v>
+        <v>-42.58086764066666</v>
       </c>
       <c r="Q72">
-        <v>-5.989050746666667</v>
+        <v>-17.78086764066666</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1173665248140316</v>
+        <v>0.1205093945743546</v>
       </c>
       <c r="T72">
-        <v>1.394964775328062</v>
+        <v>1.456225156777167</v>
       </c>
       <c r="U72">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08267884826503907</v>
+        <v>0.06941511015621912</v>
       </c>
       <c r="W72">
-        <v>0.1841980872683802</v>
+        <v>0.2194319170251635</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.5010839288790246</v>
+        <v>0.4206976373104189</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.190744385514429</v>
+        <v>0.1926443855144289</v>
       </c>
       <c r="C73">
-        <v>124.4373835860559</v>
+        <v>119.1139726493023</v>
       </c>
       <c r="D73">
-        <v>5.055383586055892</v>
+        <v>4.989972649302288</v>
       </c>
       <c r="E73">
-        <v>119.6179999999999</v>
+        <v>124.876</v>
       </c>
       <c r="F73">
-        <v>373.3179999999999</v>
+        <v>378.576</v>
       </c>
       <c r="G73">
         <v>492.7</v>
@@ -7273,37 +7273,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M73">
-        <v>88.02838439999999</v>
+        <v>89.26822079999999</v>
       </c>
       <c r="N73">
-        <v>-50.99505106666666</v>
+        <v>-52.23488746666666</v>
       </c>
       <c r="O73">
-        <v>-8.414183425999999</v>
+        <v>-8.618756432</v>
       </c>
       <c r="P73">
-        <v>-42.58086764066666</v>
+        <v>-43.61613103466667</v>
       </c>
       <c r="Q73">
-        <v>-17.78086764066666</v>
+        <v>-18.81613103466666</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1205093945743546</v>
+        <v>0.1231775872377244</v>
       </c>
       <c r="T73">
-        <v>1.456225156777167</v>
+        <v>1.508233198090637</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.06941511015621912</v>
+        <v>0.06845101140404941</v>
       </c>
       <c r="W73">
-        <v>0.2194319170251635</v>
+        <v>0.2196592515109252</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4206976373104189</v>
+        <v>0.4148546145699964</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1926443855144289</v>
+        <v>0.1945443855144289</v>
       </c>
       <c r="C74">
-        <v>119.1139726493023</v>
+        <v>113.7922327777039</v>
       </c>
       <c r="D74">
-        <v>4.989972649302288</v>
+        <v>4.926232777703877</v>
       </c>
       <c r="E74">
-        <v>124.876</v>
+        <v>130.134</v>
       </c>
       <c r="F74">
-        <v>378.576</v>
+        <v>383.8339999999999</v>
       </c>
       <c r="G74">
         <v>492.7</v>
@@ -7355,37 +7355,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M74">
-        <v>89.26822079999999</v>
+        <v>90.5080572</v>
       </c>
       <c r="N74">
-        <v>-52.23488746666666</v>
+        <v>-53.47472386666666</v>
       </c>
       <c r="O74">
-        <v>-8.618756432</v>
+        <v>-8.823329438</v>
       </c>
       <c r="P74">
-        <v>-43.61613103466667</v>
+        <v>-44.65139442866666</v>
       </c>
       <c r="Q74">
-        <v>-18.81613103466666</v>
+        <v>-19.85139442866666</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1231775872377244</v>
+        <v>0.1260434238020846</v>
       </c>
       <c r="T74">
-        <v>1.508233198090637</v>
+        <v>1.564093686908809</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06845101140404941</v>
+        <v>0.0675133263163227</v>
       </c>
       <c r="W74">
-        <v>0.2196592515109252</v>
+        <v>0.2198803576546111</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4148546145699964</v>
+        <v>0.40917167464438</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1945443855144289</v>
+        <v>0.1964443855144289</v>
       </c>
       <c r="C75">
-        <v>113.7922327777039</v>
+        <v>108.4721007424098</v>
       </c>
       <c r="D75">
-        <v>4.926232777703877</v>
+        <v>4.864100742409798</v>
       </c>
       <c r="E75">
-        <v>130.134</v>
+        <v>135.392</v>
       </c>
       <c r="F75">
-        <v>383.8339999999999</v>
+        <v>389.092</v>
       </c>
       <c r="G75">
         <v>492.7</v>
@@ -7437,37 +7437,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M75">
-        <v>90.5080572</v>
+        <v>91.7478936</v>
       </c>
       <c r="N75">
-        <v>-53.47472386666666</v>
+        <v>-54.71456026666667</v>
       </c>
       <c r="O75">
-        <v>-8.823329438</v>
+        <v>-9.027902444</v>
       </c>
       <c r="P75">
-        <v>-44.65139442866666</v>
+        <v>-45.68665782266667</v>
       </c>
       <c r="Q75">
-        <v>-19.85139442866666</v>
+        <v>-20.88665782266667</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1260434238020846</v>
+        <v>0.129129709332934</v>
       </c>
       <c r="T75">
-        <v>1.564093686908809</v>
+        <v>1.624251136405301</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0675133263163227</v>
+        <v>0.06660098406880482</v>
       </c>
       <c r="W75">
-        <v>0.2198803576546111</v>
+        <v>0.2200954879565758</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.40917167464438</v>
+        <v>0.4036423276897262</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1964443855144289</v>
+        <v>0.198344385514429</v>
       </c>
       <c r="C76">
-        <v>108.4721007424098</v>
+        <v>103.1535164647295</v>
       </c>
       <c r="D76">
-        <v>4.864100742409798</v>
+        <v>4.803516464729488</v>
       </c>
       <c r="E76">
-        <v>135.392</v>
+        <v>140.65</v>
       </c>
       <c r="F76">
-        <v>389.092</v>
+        <v>394.35</v>
       </c>
       <c r="G76">
         <v>492.7</v>
@@ -7519,37 +7519,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M76">
-        <v>91.7478936</v>
+        <v>92.98773</v>
       </c>
       <c r="N76">
-        <v>-54.71456026666667</v>
+        <v>-55.95439666666667</v>
       </c>
       <c r="O76">
-        <v>-9.027902444</v>
+        <v>-9.232475450000001</v>
       </c>
       <c r="P76">
-        <v>-45.68665782266667</v>
+        <v>-46.72192121666667</v>
       </c>
       <c r="Q76">
-        <v>-20.88665782266667</v>
+        <v>-21.92192121666666</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.129129709332934</v>
+        <v>0.1324628977062514</v>
       </c>
       <c r="T76">
-        <v>1.624251136405301</v>
+        <v>1.689221181861514</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06660098406880482</v>
+        <v>0.06571297094788743</v>
       </c>
       <c r="W76">
-        <v>0.2200954879565758</v>
+        <v>0.2203048814504882</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4036423276897262</v>
+        <v>0.3982604299871965</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.198344385514429</v>
+        <v>0.200244385514429</v>
       </c>
       <c r="C77">
-        <v>103.1535164647295</v>
+        <v>97.83642282236377</v>
       </c>
       <c r="D77">
-        <v>4.803516464729488</v>
+        <v>4.744422822363745</v>
       </c>
       <c r="E77">
-        <v>140.65</v>
+        <v>145.908</v>
       </c>
       <c r="F77">
-        <v>394.35</v>
+        <v>399.6079999999999</v>
       </c>
       <c r="G77">
         <v>492.7</v>
@@ -7601,37 +7601,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M77">
-        <v>92.98773</v>
+        <v>94.22756639999999</v>
       </c>
       <c r="N77">
-        <v>-55.95439666666667</v>
+        <v>-57.19423306666665</v>
       </c>
       <c r="O77">
-        <v>-9.232475450000001</v>
+        <v>-9.437048455999998</v>
       </c>
       <c r="P77">
-        <v>-46.72192121666667</v>
+        <v>-47.75718461066666</v>
       </c>
       <c r="Q77">
-        <v>-21.92192121666666</v>
+        <v>-22.95718461066665</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1324628977062514</v>
+        <v>0.1360738517773452</v>
       </c>
       <c r="T77">
-        <v>1.689221181861514</v>
+        <v>1.75960539777241</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06571297094788743</v>
+        <v>0.06484832659330997</v>
       </c>
       <c r="W77">
-        <v>0.2203048814504882</v>
+        <v>0.2205087645892975</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3982604299871965</v>
+        <v>0.3930201611715756</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.200244385514429</v>
+        <v>0.2021443855144289</v>
       </c>
       <c r="C78">
-        <v>97.83642282236377</v>
+        <v>92.52076546976468</v>
       </c>
       <c r="D78">
-        <v>4.744422822363745</v>
+        <v>4.686765469764672</v>
       </c>
       <c r="E78">
-        <v>145.908</v>
+        <v>151.166</v>
       </c>
       <c r="F78">
-        <v>399.6079999999999</v>
+        <v>404.866</v>
       </c>
       <c r="G78">
         <v>492.7</v>
@@ -7683,37 +7683,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M78">
-        <v>94.22756639999999</v>
+        <v>95.4674028</v>
       </c>
       <c r="N78">
-        <v>-57.19423306666665</v>
+        <v>-58.43406946666667</v>
       </c>
       <c r="O78">
-        <v>-9.437048455999998</v>
+        <v>-9.641621462000002</v>
       </c>
       <c r="P78">
-        <v>-47.75718461066666</v>
+        <v>-48.79244800466667</v>
       </c>
       <c r="Q78">
-        <v>-22.95718461066665</v>
+        <v>-23.99244800466667</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1360738517773452</v>
+        <v>0.139998801854621</v>
       </c>
       <c r="T78">
-        <v>1.75960539777241</v>
+        <v>1.836109980284254</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06484832659330997</v>
+        <v>0.06400614053365658</v>
       </c>
       <c r="W78">
-        <v>0.2205087645892975</v>
+        <v>0.2207073520621638</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3930201611715756</v>
+        <v>0.3879160032342823</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2021443855144289</v>
+        <v>0.204044385514429</v>
       </c>
       <c r="C79">
-        <v>92.52076546976468</v>
+        <v>87.20649267143693</v>
       </c>
       <c r="D79">
-        <v>4.686765469764672</v>
+        <v>4.630492671436919</v>
       </c>
       <c r="E79">
-        <v>151.166</v>
+        <v>156.424</v>
       </c>
       <c r="F79">
-        <v>404.866</v>
+        <v>410.124</v>
       </c>
       <c r="G79">
         <v>492.7</v>
@@ -7765,37 +7765,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M79">
-        <v>95.4674028</v>
+        <v>96.70723919999999</v>
       </c>
       <c r="N79">
-        <v>-58.43406946666667</v>
+        <v>-59.67390586666666</v>
       </c>
       <c r="O79">
-        <v>-9.641621462000002</v>
+        <v>-9.846194467999998</v>
       </c>
       <c r="P79">
-        <v>-48.79244800466667</v>
+        <v>-49.82771139866666</v>
       </c>
       <c r="Q79">
-        <v>-23.99244800466667</v>
+        <v>-25.02771139866666</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.139998801854621</v>
+        <v>0.1442805655752857</v>
       </c>
       <c r="T79">
-        <v>1.836109980284254</v>
+        <v>1.919569524842629</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06400614053365658</v>
+        <v>0.06318554898835331</v>
       </c>
       <c r="W79">
-        <v>0.2207073520621638</v>
+        <v>0.2209008475485463</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3879160032342823</v>
+        <v>0.3829427211415352</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.204044385514429</v>
+        <v>0.205944385514429</v>
       </c>
       <c r="C80">
-        <v>87.20649267143693</v>
+        <v>81.89355514710553</v>
       </c>
       <c r="D80">
-        <v>4.630492671436919</v>
+        <v>4.575555147105555</v>
       </c>
       <c r="E80">
-        <v>156.424</v>
+        <v>161.682</v>
       </c>
       <c r="F80">
-        <v>410.124</v>
+        <v>415.382</v>
       </c>
       <c r="G80">
         <v>492.7</v>
@@ -7847,37 +7847,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M80">
-        <v>96.70723919999999</v>
+        <v>97.94707560000001</v>
       </c>
       <c r="N80">
-        <v>-59.67390586666666</v>
+        <v>-60.91374226666667</v>
       </c>
       <c r="O80">
-        <v>-9.846194467999998</v>
+        <v>-10.050767474</v>
       </c>
       <c r="P80">
-        <v>-49.82771139866666</v>
+        <v>-50.86297479266667</v>
       </c>
       <c r="Q80">
-        <v>-25.02771139866666</v>
+        <v>-26.06297479266667</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1442805655752857</v>
+        <v>0.1489701163169659</v>
       </c>
       <c r="T80">
-        <v>1.919569524842629</v>
+        <v>2.010977597454183</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06318554898835331</v>
+        <v>0.06238573191255135</v>
       </c>
       <c r="W80">
-        <v>0.2209008475485463</v>
+        <v>0.2210894444150204</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3829427211415352</v>
+        <v>0.3780953449245537</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.205944385514429</v>
+        <v>0.207844385514429</v>
       </c>
       <c r="C81">
-        <v>81.89355514710553</v>
+        <v>76.58190592777652</v>
       </c>
       <c r="D81">
-        <v>4.575555147105555</v>
+        <v>4.521905927776531</v>
       </c>
       <c r="E81">
-        <v>161.682</v>
+        <v>166.94</v>
       </c>
       <c r="F81">
-        <v>415.382</v>
+        <v>420.64</v>
       </c>
       <c r="G81">
         <v>492.7</v>
@@ -7929,37 +7929,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M81">
-        <v>97.94707560000001</v>
+        <v>99.18691200000001</v>
       </c>
       <c r="N81">
-        <v>-60.91374226666667</v>
+        <v>-62.15357866666668</v>
       </c>
       <c r="O81">
-        <v>-10.050767474</v>
+        <v>-10.25534048</v>
       </c>
       <c r="P81">
-        <v>-50.86297479266667</v>
+        <v>-51.89823818666667</v>
       </c>
       <c r="Q81">
-        <v>-26.06297479266667</v>
+        <v>-27.09823818666667</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1489701163169659</v>
+        <v>0.1541286221328142</v>
       </c>
       <c r="T81">
-        <v>2.010977597454183</v>
+        <v>2.111526477326893</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06238573191255135</v>
+        <v>0.06160591026364445</v>
       </c>
       <c r="W81">
-        <v>0.2210894444150204</v>
+        <v>0.2212733263598326</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3780953449245537</v>
+        <v>0.3733691531129967</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.207844385514429</v>
+        <v>0.2097443855144289</v>
       </c>
       <c r="C82">
-        <v>76.58190592777652</v>
+        <v>71.27150022180609</v>
       </c>
       <c r="D82">
-        <v>4.521905927776531</v>
+        <v>4.469500221806078</v>
       </c>
       <c r="E82">
-        <v>166.94</v>
+        <v>172.198</v>
       </c>
       <c r="F82">
-        <v>420.64</v>
+        <v>425.898</v>
       </c>
       <c r="G82">
         <v>492.7</v>
@@ -8011,37 +8011,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M82">
-        <v>99.18691200000001</v>
+        <v>100.4267484</v>
       </c>
       <c r="N82">
-        <v>-62.15357866666668</v>
+        <v>-63.39341506666666</v>
       </c>
       <c r="O82">
-        <v>-10.25534048</v>
+        <v>-10.459913486</v>
       </c>
       <c r="P82">
-        <v>-51.89823818666667</v>
+        <v>-52.93350158066666</v>
       </c>
       <c r="Q82">
-        <v>-27.09823818666667</v>
+        <v>-28.13350158066666</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1541286221328142</v>
+        <v>0.159830128560857</v>
       </c>
       <c r="T82">
-        <v>2.111526477326893</v>
+        <v>2.222659449817781</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06160591026364445</v>
+        <v>0.06084534347026613</v>
       </c>
       <c r="W82">
-        <v>0.2212733263598326</v>
+        <v>0.2214526680097113</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3733691531129967</v>
+        <v>0.3687596573955524</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2097443855144289</v>
+        <v>0.211644385514429</v>
       </c>
       <c r="C83">
-        <v>71.27150022180609</v>
+        <v>65.96229529017637</v>
       </c>
       <c r="D83">
-        <v>4.469500221806078</v>
+        <v>4.418295290176407</v>
       </c>
       <c r="E83">
-        <v>172.198</v>
+        <v>177.456</v>
       </c>
       <c r="F83">
-        <v>425.898</v>
+        <v>431.156</v>
       </c>
       <c r="G83">
         <v>492.7</v>
@@ -8093,37 +8093,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M83">
-        <v>100.4267484</v>
+        <v>101.6665848</v>
       </c>
       <c r="N83">
-        <v>-63.39341506666666</v>
+        <v>-64.63325146666668</v>
       </c>
       <c r="O83">
-        <v>-10.459913486</v>
+        <v>-10.664486492</v>
       </c>
       <c r="P83">
-        <v>-52.93350158066666</v>
+        <v>-53.96876497466668</v>
       </c>
       <c r="Q83">
-        <v>-28.13350158066666</v>
+        <v>-29.16876497466668</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.159830128560857</v>
+        <v>0.1661651357031269</v>
       </c>
       <c r="T83">
-        <v>2.222659449817781</v>
+        <v>2.346140530363214</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06084534347026613</v>
+        <v>0.0601033270864824</v>
       </c>
       <c r="W83">
-        <v>0.2214526680097113</v>
+        <v>0.2216276354730075</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3687596573955524</v>
+        <v>0.3642625884029236</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.211644385514429</v>
+        <v>0.2135443855144289</v>
       </c>
       <c r="C84">
-        <v>65.96229529017637</v>
+        <v>60.65425033024769</v>
       </c>
       <c r="D84">
-        <v>4.418295290176407</v>
+        <v>4.368250330247698</v>
       </c>
       <c r="E84">
-        <v>177.456</v>
+        <v>182.714</v>
       </c>
       <c r="F84">
-        <v>431.156</v>
+        <v>436.414</v>
       </c>
       <c r="G84">
         <v>492.7</v>
@@ -8175,37 +8175,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M84">
-        <v>101.6665848</v>
+        <v>102.9064212</v>
       </c>
       <c r="N84">
-        <v>-64.63325146666668</v>
+        <v>-65.87308786666667</v>
       </c>
       <c r="O84">
-        <v>-10.664486492</v>
+        <v>-10.869059498</v>
       </c>
       <c r="P84">
-        <v>-53.96876497466668</v>
+        <v>-55.00402836866667</v>
       </c>
       <c r="Q84">
-        <v>-29.16876497466668</v>
+        <v>-30.20402836866667</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1661651357031269</v>
+        <v>0.1732454378033109</v>
       </c>
       <c r="T84">
-        <v>2.346140530363214</v>
+        <v>2.484148796855168</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0601033270864824</v>
+        <v>0.05937919061556093</v>
       </c>
       <c r="W84">
-        <v>0.2216276354730075</v>
+        <v>0.2217983868528507</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3642625884029236</v>
+        <v>0.359873882518551</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2135443855144289</v>
+        <v>0.215444385514429</v>
       </c>
       <c r="C85">
-        <v>60.65425033024769</v>
+        <v>55.3473263673219</v>
       </c>
       <c r="D85">
-        <v>4.368250330247698</v>
+        <v>4.319326367321942</v>
       </c>
       <c r="E85">
-        <v>182.714</v>
+        <v>187.972</v>
       </c>
       <c r="F85">
-        <v>436.414</v>
+        <v>441.672</v>
       </c>
       <c r="G85">
         <v>492.7</v>
@@ -8257,37 +8257,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M85">
-        <v>102.9064212</v>
+        <v>104.1462576</v>
       </c>
       <c r="N85">
-        <v>-65.87308786666667</v>
+        <v>-67.11292426666668</v>
       </c>
       <c r="O85">
-        <v>-10.869059498</v>
+        <v>-11.073632504</v>
       </c>
       <c r="P85">
-        <v>-55.00402836866667</v>
+        <v>-56.03929176266668</v>
       </c>
       <c r="Q85">
-        <v>-30.20402836866667</v>
+        <v>-31.23929176266668</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1732454378033109</v>
+        <v>0.1812107776660178</v>
       </c>
       <c r="T85">
-        <v>2.484148796855168</v>
+        <v>2.639408096658617</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05937919061556093</v>
+        <v>0.0586722954891852</v>
       </c>
       <c r="W85">
-        <v>0.2217983868528507</v>
+        <v>0.2219650727236502</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.359873882518551</v>
+        <v>0.3555896696314254</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.215444385514429</v>
+        <v>0.217344385514429</v>
       </c>
       <c r="C86">
-        <v>55.34732636732195</v>
+        <v>50.0414861534129</v>
       </c>
       <c r="D86">
-        <v>4.319326367321942</v>
+        <v>4.271486153412864</v>
       </c>
       <c r="E86">
-        <v>187.972</v>
+        <v>193.23</v>
       </c>
       <c r="F86">
-        <v>441.672</v>
+        <v>446.9299999999999</v>
       </c>
       <c r="G86">
         <v>492.7</v>
@@ -8339,37 +8339,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M86">
-        <v>104.1462576</v>
+        <v>105.386094</v>
       </c>
       <c r="N86">
-        <v>-67.11292426666667</v>
+        <v>-68.35276066666665</v>
       </c>
       <c r="O86">
-        <v>-11.073632504</v>
+        <v>-11.27820551</v>
       </c>
       <c r="P86">
-        <v>-56.03929176266666</v>
+        <v>-57.07455515666665</v>
       </c>
       <c r="Q86">
-        <v>-31.23929176266666</v>
+        <v>-32.27455515666665</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1812107776660177</v>
+        <v>0.1902381628437523</v>
       </c>
       <c r="T86">
-        <v>2.639408096658614</v>
+        <v>2.815368636435856</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05867229548918521</v>
+        <v>0.05798203318931244</v>
       </c>
       <c r="W86">
-        <v>0.2219650727236502</v>
+        <v>0.2221278365739602</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3555896696314255</v>
+        <v>0.3514062617534087</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.217344385514429</v>
+        <v>0.2192443855144289</v>
       </c>
       <c r="C87">
-        <v>50.0414861534129</v>
+        <v>44.73669407266948</v>
       </c>
       <c r="D87">
-        <v>4.271486153412864</v>
+        <v>4.224694072669443</v>
       </c>
       <c r="E87">
-        <v>193.23</v>
+        <v>198.4879999999999</v>
       </c>
       <c r="F87">
-        <v>446.9299999999999</v>
+        <v>452.1879999999999</v>
       </c>
       <c r="G87">
         <v>492.7</v>
@@ -8421,37 +8421,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M87">
-        <v>105.386094</v>
+        <v>106.6259304</v>
       </c>
       <c r="N87">
-        <v>-68.35276066666665</v>
+        <v>-69.59259706666666</v>
       </c>
       <c r="O87">
-        <v>-11.27820551</v>
+        <v>-11.482778516</v>
       </c>
       <c r="P87">
-        <v>-57.07455515666665</v>
+        <v>-58.10981855066666</v>
       </c>
       <c r="Q87">
-        <v>-32.27455515666665</v>
+        <v>-33.30981855066666</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1902381628437523</v>
+        <v>0.2005551744754488</v>
       </c>
       <c r="T87">
-        <v>2.815368636435856</v>
+        <v>3.016466396181274</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05798203318931244</v>
+        <v>0.05730782350106462</v>
       </c>
       <c r="W87">
-        <v>0.2221278365739602</v>
+        <v>0.222286815218449</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3514062617534087</v>
+        <v>0.3473201424306946</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2192443855144289</v>
+        <v>0.2211443855144289</v>
       </c>
       <c r="C88">
-        <v>44.73669407266948</v>
+        <v>39.43291605294831</v>
       </c>
       <c r="D88">
-        <v>4.224694072669443</v>
+        <v>4.178916052948296</v>
       </c>
       <c r="E88">
-        <v>198.4879999999999</v>
+        <v>203.746</v>
       </c>
       <c r="F88">
-        <v>452.1879999999999</v>
+        <v>457.446</v>
       </c>
       <c r="G88">
         <v>492.7</v>
@@ -8503,37 +8503,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M88">
-        <v>106.6259304</v>
+        <v>107.8657668</v>
       </c>
       <c r="N88">
-        <v>-69.59259706666666</v>
+        <v>-70.83243346666667</v>
       </c>
       <c r="O88">
-        <v>-11.482778516</v>
+        <v>-11.687351522</v>
       </c>
       <c r="P88">
-        <v>-58.10981855066666</v>
+        <v>-59.14508194466667</v>
       </c>
       <c r="Q88">
-        <v>-33.30981855066666</v>
+        <v>-34.34508194466667</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2005551744754488</v>
+        <v>0.212459418665868</v>
       </c>
       <c r="T88">
-        <v>3.016466396181274</v>
+        <v>3.248502272810603</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05730782350106462</v>
+        <v>0.05664911288610985</v>
       </c>
       <c r="W88">
-        <v>0.222286815218449</v>
+        <v>0.2224421391814553</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3473201424306946</v>
+        <v>0.3433279568855142</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2211443855144289</v>
+        <v>0.223044385514429</v>
       </c>
       <c r="C89">
-        <v>39.43291605294831</v>
+        <v>34.1301194830736</v>
       </c>
       <c r="D89">
-        <v>4.178916052948296</v>
+        <v>4.13411948307356</v>
       </c>
       <c r="E89">
-        <v>203.746</v>
+        <v>209.004</v>
       </c>
       <c r="F89">
-        <v>457.446</v>
+        <v>462.704</v>
       </c>
       <c r="G89">
         <v>492.7</v>
@@ -8585,37 +8585,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M89">
-        <v>107.8657668</v>
+        <v>109.1056032</v>
       </c>
       <c r="N89">
-        <v>-70.83243346666667</v>
+        <v>-72.07226986666666</v>
       </c>
       <c r="O89">
-        <v>-11.687351522</v>
+        <v>-11.891924528</v>
       </c>
       <c r="P89">
-        <v>-59.14508194466667</v>
+        <v>-60.18034533866666</v>
       </c>
       <c r="Q89">
-        <v>-34.34508194466667</v>
+        <v>-35.38034533866666</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.212459418665868</v>
+        <v>0.2263477035546903</v>
       </c>
       <c r="T89">
-        <v>3.248502272810603</v>
+        <v>3.51921079554482</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05664911288610985</v>
+        <v>0.05600537296694951</v>
       </c>
       <c r="W89">
-        <v>0.2224421391814553</v>
+        <v>0.2225939330543933</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3433279568855142</v>
+        <v>0.3394265028299971</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.223044385514429</v>
+        <v>0.224944385514429</v>
       </c>
       <c r="C90">
-        <v>34.1301194830736</v>
+        <v>28.828273135362</v>
       </c>
       <c r="D90">
-        <v>4.13411948307356</v>
+        <v>4.090273135361998</v>
       </c>
       <c r="E90">
-        <v>209.004</v>
+        <v>214.262</v>
       </c>
       <c r="F90">
-        <v>462.704</v>
+        <v>467.962</v>
       </c>
       <c r="G90">
         <v>492.7</v>
@@ -8667,37 +8667,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M90">
-        <v>109.1056032</v>
+        <v>110.3454396</v>
       </c>
       <c r="N90">
-        <v>-72.07226986666666</v>
+        <v>-73.31210626666667</v>
       </c>
       <c r="O90">
-        <v>-11.891924528</v>
+        <v>-12.096497534</v>
       </c>
       <c r="P90">
-        <v>-60.18034533866666</v>
+        <v>-61.21560873266667</v>
       </c>
       <c r="Q90">
-        <v>-35.38034533866666</v>
+        <v>-36.41560873266667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2263477035546903</v>
+        <v>0.2427611311505713</v>
       </c>
       <c r="T90">
-        <v>3.51921079554482</v>
+        <v>3.839139049685259</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05600537296694951</v>
+        <v>0.05537609911338828</v>
       </c>
       <c r="W90">
-        <v>0.2225939330543933</v>
+        <v>0.2227423158290631</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3394265028299971</v>
+        <v>0.3356127218993229</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.224944385514429</v>
+        <v>0.226844385514429</v>
       </c>
       <c r="C91">
-        <v>28.828273135362</v>
+        <v>23.52734709302655</v>
       </c>
       <c r="D91">
-        <v>4.090273135361998</v>
+        <v>4.047347093026547</v>
       </c>
       <c r="E91">
-        <v>214.262</v>
+        <v>219.52</v>
       </c>
       <c r="F91">
-        <v>467.962</v>
+        <v>473.22</v>
       </c>
       <c r="G91">
         <v>492.7</v>
@@ -8749,37 +8749,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M91">
-        <v>110.3454396</v>
+        <v>111.585276</v>
       </c>
       <c r="N91">
-        <v>-73.31210626666667</v>
+        <v>-74.55194266666666</v>
       </c>
       <c r="O91">
-        <v>-12.096497534</v>
+        <v>-12.30107054</v>
       </c>
       <c r="P91">
-        <v>-61.21560873266667</v>
+        <v>-62.25087212666666</v>
       </c>
       <c r="Q91">
-        <v>-36.41560873266667</v>
+        <v>-37.45087212666667</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2427611311505713</v>
+        <v>0.2624572442656284</v>
       </c>
       <c r="T91">
-        <v>3.839139049685259</v>
+        <v>4.223052954653784</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05537609911338828</v>
+        <v>0.05476080912323953</v>
       </c>
       <c r="W91">
-        <v>0.2227423158290631</v>
+        <v>0.2228874012087401</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3356127218993229</v>
+        <v>0.3318836916559971</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.226844385514429</v>
+        <v>0.2287443855144289</v>
       </c>
       <c r="C92">
-        <v>23.52734709302655</v>
+        <v>18.22731268210367</v>
       </c>
       <c r="D92">
-        <v>4.047347093026547</v>
+        <v>4.005312682103649</v>
       </c>
       <c r="E92">
-        <v>219.52</v>
+        <v>224.778</v>
       </c>
       <c r="F92">
-        <v>473.22</v>
+        <v>478.478</v>
       </c>
       <c r="G92">
         <v>492.7</v>
@@ -8831,37 +8831,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M92">
-        <v>111.585276</v>
+        <v>112.8251124</v>
       </c>
       <c r="N92">
-        <v>-74.55194266666666</v>
+        <v>-75.79177906666666</v>
       </c>
       <c r="O92">
-        <v>-12.30107054</v>
+        <v>-12.505643546</v>
       </c>
       <c r="P92">
-        <v>-62.25087212666666</v>
+        <v>-63.28613552066666</v>
       </c>
       <c r="Q92">
-        <v>-37.45087212666667</v>
+        <v>-38.48613552066666</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2624572442656284</v>
+        <v>0.2865302714062539</v>
       </c>
       <c r="T92">
-        <v>4.223052954653784</v>
+        <v>4.692281060726429</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05476080912323953</v>
+        <v>0.05415904199001711</v>
       </c>
       <c r="W92">
-        <v>0.2228874012087401</v>
+        <v>0.223029297898754</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3318836916559971</v>
+        <v>0.3282366181213158</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2287443855144289</v>
+        <v>0.230644385514429</v>
       </c>
       <c r="C93">
-        <v>18.22731268210367</v>
+        <v>12.92814240757883</v>
       </c>
       <c r="D93">
-        <v>4.005312682103649</v>
+        <v>3.964142407578852</v>
       </c>
       <c r="E93">
-        <v>224.778</v>
+        <v>230.036</v>
       </c>
       <c r="F93">
-        <v>478.478</v>
+        <v>483.736</v>
       </c>
       <c r="G93">
         <v>492.7</v>
@@ -8913,37 +8913,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M93">
-        <v>112.8251124</v>
+        <v>114.0649488</v>
       </c>
       <c r="N93">
-        <v>-75.79177906666666</v>
+        <v>-77.03161546666666</v>
       </c>
       <c r="O93">
-        <v>-12.505643546</v>
+        <v>-12.710216552</v>
       </c>
       <c r="P93">
-        <v>-63.28613552066666</v>
+        <v>-64.32139891466666</v>
       </c>
       <c r="Q93">
-        <v>-38.48613552066666</v>
+        <v>-39.52139891466666</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2865302714062539</v>
+        <v>0.3166215553320356</v>
       </c>
       <c r="T93">
-        <v>4.692281060726429</v>
+        <v>5.278816193317233</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05415904199001711</v>
+        <v>0.05357035675099518</v>
       </c>
       <c r="W93">
-        <v>0.223029297898754</v>
+        <v>0.2231681098781153</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3282366181213158</v>
+        <v>0.3246688287939102</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.230644385514429</v>
+        <v>0.2325443855144289</v>
       </c>
       <c r="C94">
-        <v>12.92814240757883</v>
+        <v>7.629809893411675</v>
       </c>
       <c r="D94">
-        <v>3.964142407578852</v>
+        <v>3.923809893411683</v>
       </c>
       <c r="E94">
-        <v>230.036</v>
+        <v>235.294</v>
       </c>
       <c r="F94">
-        <v>483.736</v>
+        <v>488.994</v>
       </c>
       <c r="G94">
         <v>492.7</v>
@@ -8995,37 +8995,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M94">
-        <v>114.0649488</v>
+        <v>115.3047852</v>
       </c>
       <c r="N94">
-        <v>-77.03161546666666</v>
+        <v>-78.27145186666667</v>
       </c>
       <c r="O94">
-        <v>-12.710216552</v>
+        <v>-12.914789558</v>
       </c>
       <c r="P94">
-        <v>-64.32139891466666</v>
+        <v>-65.35666230866667</v>
       </c>
       <c r="Q94">
-        <v>-39.52139891466666</v>
+        <v>-40.55666230866667</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3166215553320356</v>
+        <v>0.3553103489508979</v>
       </c>
       <c r="T94">
-        <v>5.278816193317233</v>
+        <v>6.032932792362552</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05357035675099518</v>
+        <v>0.05299433140958663</v>
       </c>
       <c r="W94">
-        <v>0.2231681098781153</v>
+        <v>0.2233039366536195</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3246688287939102</v>
+        <v>0.3211777661187069</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2325443855144289</v>
+        <v>0.2344443855144289</v>
       </c>
       <c r="C95">
-        <v>7.629809893411675</v>
+        <v>2.332289826184876</v>
       </c>
       <c r="D95">
-        <v>3.923809893411683</v>
+        <v>3.884289826184917</v>
       </c>
       <c r="E95">
-        <v>235.294</v>
+        <v>240.552</v>
       </c>
       <c r="F95">
-        <v>488.994</v>
+        <v>494.252</v>
       </c>
       <c r="G95">
         <v>492.7</v>
@@ -9077,37 +9077,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M95">
-        <v>115.3047852</v>
+        <v>116.5446216</v>
       </c>
       <c r="N95">
-        <v>-78.27145186666667</v>
+        <v>-79.51128826666668</v>
       </c>
       <c r="O95">
-        <v>-12.914789558</v>
+        <v>-13.119362564</v>
       </c>
       <c r="P95">
-        <v>-65.35666230866667</v>
+        <v>-66.39192570266668</v>
       </c>
       <c r="Q95">
-        <v>-40.55666230866667</v>
+        <v>-41.59192570266669</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3553103489508979</v>
+        <v>0.4068954071093809</v>
       </c>
       <c r="T95">
-        <v>6.032932792362552</v>
+        <v>7.038421591089646</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05299433140958663</v>
+        <v>0.05243056192650592</v>
       </c>
       <c r="W95">
-        <v>0.2233039366536195</v>
+        <v>0.2234368734977299</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3211777661187069</v>
+        <v>0.3177609813727631</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2344443855144289</v>
+        <v>0.2363443855144289</v>
       </c>
       <c r="C96">
-        <v>2.332289826184876</v>
+        <v>-2.96444209787478</v>
       </c>
       <c r="D96">
-        <v>3.884289826184917</v>
+        <v>3.845557902125195</v>
       </c>
       <c r="E96">
-        <v>240.552</v>
+        <v>245.81</v>
       </c>
       <c r="F96">
-        <v>494.252</v>
+        <v>499.51</v>
       </c>
       <c r="G96">
         <v>492.7</v>
@@ -9159,37 +9159,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M96">
-        <v>116.5446216</v>
+        <v>117.784458</v>
       </c>
       <c r="N96">
-        <v>-79.51128826666668</v>
+        <v>-80.75112466666667</v>
       </c>
       <c r="O96">
-        <v>-13.119362564</v>
+        <v>-13.32393557</v>
       </c>
       <c r="P96">
-        <v>-66.39192570266668</v>
+        <v>-67.42718909666667</v>
       </c>
       <c r="Q96">
-        <v>-41.59192570266669</v>
+        <v>-42.62718909666667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4068954071093809</v>
+        <v>0.4791144885312573</v>
       </c>
       <c r="T96">
-        <v>7.038421591089646</v>
+        <v>8.44610590930758</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05243056192650592</v>
+        <v>0.05187866127464797</v>
       </c>
       <c r="W96">
-        <v>0.2234368734977299</v>
+        <v>0.223567011671438</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3177609813727631</v>
+        <v>0.3144161289372603</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2363443855144289</v>
+        <v>0.2382443855144289</v>
       </c>
       <c r="C97">
-        <v>-2.96444209787478</v>
+        <v>-8.260409222737962</v>
       </c>
       <c r="D97">
-        <v>3.845557902125195</v>
+        <v>3.807590777262047</v>
       </c>
       <c r="E97">
-        <v>245.81</v>
+        <v>251.068</v>
       </c>
       <c r="F97">
-        <v>499.51</v>
+        <v>504.768</v>
       </c>
       <c r="G97">
         <v>492.7</v>
@@ -9241,37 +9241,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M97">
-        <v>117.784458</v>
+        <v>119.0242944</v>
       </c>
       <c r="N97">
-        <v>-80.75112466666667</v>
+        <v>-81.99096106666667</v>
       </c>
       <c r="O97">
-        <v>-13.32393557</v>
+        <v>-13.528508576</v>
       </c>
       <c r="P97">
-        <v>-67.42718909666667</v>
+        <v>-68.46245249066666</v>
       </c>
       <c r="Q97">
-        <v>-42.62718909666667</v>
+        <v>-43.66245249066667</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4791144885312573</v>
+        <v>0.5874431106640718</v>
       </c>
       <c r="T97">
-        <v>8.44610590930758</v>
+        <v>10.55763238663448</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05187866127464797</v>
+        <v>0.05133825855303705</v>
       </c>
       <c r="W97">
-        <v>0.223567011671438</v>
+        <v>0.2236944386331939</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3144161289372603</v>
+        <v>0.3111409609274972</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2382443855144289</v>
+        <v>0.240144385514429</v>
       </c>
       <c r="C98">
-        <v>-8.260409222737906</v>
+        <v>-13.55563397948941</v>
       </c>
       <c r="D98">
-        <v>3.807590777262047</v>
+        <v>3.770366020510528</v>
       </c>
       <c r="E98">
-        <v>251.0679999999999</v>
+        <v>256.326</v>
       </c>
       <c r="F98">
-        <v>504.7679999999999</v>
+        <v>510.026</v>
       </c>
       <c r="G98">
         <v>492.7</v>
@@ -9323,37 +9323,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M98">
-        <v>119.0242944</v>
+        <v>120.2641308</v>
       </c>
       <c r="N98">
-        <v>-81.99096106666666</v>
+        <v>-83.23079746666666</v>
       </c>
       <c r="O98">
-        <v>-13.528508576</v>
+        <v>-13.733081582</v>
       </c>
       <c r="P98">
-        <v>-68.46245249066666</v>
+        <v>-69.49771588466666</v>
       </c>
       <c r="Q98">
-        <v>-43.66245249066667</v>
+        <v>-44.69771588466666</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5874431106640704</v>
+        <v>0.7679908142187606</v>
       </c>
       <c r="T98">
-        <v>10.55763238663445</v>
+        <v>14.07684318217927</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05133825855303706</v>
+        <v>0.05080899815558307</v>
       </c>
       <c r="W98">
-        <v>0.2236944386331939</v>
+        <v>0.2238192382349135</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3111409609274973</v>
+        <v>0.3079333221550489</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.240144385514429</v>
+        <v>0.2420443855144289</v>
       </c>
       <c r="C99">
-        <v>-13.55563397948941</v>
+        <v>-18.8501379305207</v>
       </c>
       <c r="D99">
-        <v>3.770366020510528</v>
+        <v>3.733862069479314</v>
       </c>
       <c r="E99">
-        <v>256.326</v>
+        <v>261.584</v>
       </c>
       <c r="F99">
-        <v>510.026</v>
+        <v>515.284</v>
       </c>
       <c r="G99">
         <v>492.7</v>
@@ -9405,37 +9405,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M99">
-        <v>120.2641308</v>
+        <v>121.5039672</v>
       </c>
       <c r="N99">
-        <v>-83.23079746666666</v>
+        <v>-84.47063386666667</v>
       </c>
       <c r="O99">
-        <v>-13.733081582</v>
+        <v>-13.937654588</v>
       </c>
       <c r="P99">
-        <v>-69.49771588466666</v>
+        <v>-70.53297927866667</v>
       </c>
       <c r="Q99">
-        <v>-44.69771588466666</v>
+        <v>-45.73297927866668</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7679908142187606</v>
+        <v>1.129086221328141</v>
       </c>
       <c r="T99">
-        <v>14.07684318217927</v>
+        <v>21.1152647732689</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05080899815558307</v>
+        <v>0.05029053899073017</v>
       </c>
       <c r="W99">
-        <v>0.2238192382349135</v>
+        <v>0.2239414909059858</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3079333221550489</v>
+        <v>0.3047911453983646</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2420443855144289</v>
+        <v>0.2439443855144289</v>
       </c>
       <c r="C100">
-        <v>-18.8501379305207</v>
+        <v>-24.14394181117859</v>
       </c>
       <c r="D100">
-        <v>3.733862069479314</v>
+        <v>3.698058188821317</v>
       </c>
       <c r="E100">
-        <v>261.584</v>
+        <v>266.8419999999999</v>
       </c>
       <c r="F100">
-        <v>515.284</v>
+        <v>520.5419999999999</v>
       </c>
       <c r="G100">
         <v>492.7</v>
@@ -9487,37 +9487,37 @@
         <v>37.03333333333333</v>
       </c>
       <c r="M100">
-        <v>121.5039672</v>
+        <v>122.7438036</v>
       </c>
       <c r="N100">
-        <v>-84.47063386666667</v>
+        <v>-85.71047026666665</v>
       </c>
       <c r="O100">
-        <v>-13.937654588</v>
+        <v>-14.142227594</v>
       </c>
       <c r="P100">
-        <v>-70.53297927866667</v>
+        <v>-71.56824267266666</v>
       </c>
       <c r="Q100">
-        <v>-45.73297927866668</v>
+        <v>-46.76824267266666</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.129086221328141</v>
+        <v>2.212372442656282</v>
       </c>
       <c r="T100">
-        <v>21.1152647732689</v>
+        <v>42.2305295465378</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05029053899073017</v>
+        <v>0.04978255374839957</v>
       </c>
       <c r="W100">
-        <v>0.2239414909059858</v>
+        <v>0.2240612738261274</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3047911453983646</v>
+        <v>0.3017124469599974</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2439443855144289</v>
-      </c>
-      <c r="C101">
-        <v>-24.14394181117859</v>
-      </c>
-      <c r="D101">
-        <v>3.698058188821317</v>
-      </c>
-      <c r="E101">
-        <v>266.8419999999999</v>
-      </c>
-      <c r="F101">
-        <v>520.5419999999999</v>
-      </c>
-      <c r="G101">
-        <v>492.7</v>
-      </c>
-      <c r="H101">
-        <v>272.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>61.83333333333334</v>
-      </c>
-      <c r="K101">
-        <v>24.8</v>
-      </c>
-      <c r="L101">
-        <v>37.03333333333333</v>
-      </c>
-      <c r="M101">
-        <v>122.7438036</v>
-      </c>
-      <c r="N101">
-        <v>-85.71047026666665</v>
-      </c>
-      <c r="O101">
-        <v>-14.142227594</v>
-      </c>
-      <c r="P101">
-        <v>-71.56824267266666</v>
-      </c>
-      <c r="Q101">
-        <v>-46.76824267266666</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.212372442656282</v>
-      </c>
-      <c r="T101">
-        <v>42.2305295465378</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04978255374839957</v>
-      </c>
-      <c r="W101">
-        <v>0.2240612738261274</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3017124469599974</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
